--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -1381,10 +1381,10 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="2" t="n"/>
+      <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="28" t="n"/>
       <c r="AE2" s="5" t="n"/>
-      <c r="AF2" s="2" t="n"/>
+      <c r="AF2" s="2" t="inlineStr"/>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
@@ -1396,10 +1396,10 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="2" t="n"/>
+      <c r="AR2" s="2" t="inlineStr"/>
       <c r="AS2" s="28" t="n"/>
       <c r="AT2" s="5" t="n"/>
-      <c r="AU2" s="2" t="n"/>
+      <c r="AU2" s="2" t="inlineStr"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
@@ -1411,10 +1411,10 @@
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="2" t="n"/>
+      <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="28" t="n"/>
       <c r="BI2" s="5" t="n"/>
-      <c r="BJ2" s="2" t="n"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
       <c r="BK2" s="4" t="n"/>
       <c r="BL2" s="4" t="n"/>
       <c r="BM2" s="4" t="n"/>
@@ -1426,10 +1426,10 @@
       <c r="BS2" s="4" t="n"/>
       <c r="BT2" s="4" t="n"/>
       <c r="BU2" s="4" t="n"/>
-      <c r="BV2" s="2" t="n"/>
+      <c r="BV2" s="2" t="inlineStr"/>
       <c r="BW2" s="28" t="n"/>
       <c r="BX2" s="5" t="n"/>
-      <c r="BY2" s="2" t="n"/>
+      <c r="BY2" s="2" t="inlineStr"/>
       <c r="BZ2" s="4" t="n"/>
       <c r="CA2" s="4" t="n"/>
       <c r="CB2" s="4" t="n"/>
@@ -1441,22 +1441,12 @@
       <c r="CH2" s="4" t="n"/>
       <c r="CI2" s="4" t="n"/>
       <c r="CJ2" s="4" t="n"/>
-      <c r="CK2" s="2" t="n"/>
+      <c r="CK2" s="2" t="inlineStr"/>
       <c r="CL2" s="28" t="n"/>
-      <c r="CN2" s="2" t="n"/>
+      <c r="CN2" s="2" t="inlineStr"/>
       <c r="CP2" s="11" t="n"/>
       <c r="CQ2" s="7" t="n"/>
       <c r="CR2" s="12" t="n"/>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,10 +1483,10 @@
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="2" t="n"/>
+      <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="28" t="n"/>
       <c r="AE3" s="5" t="n"/>
-      <c r="AF3" s="2" t="n"/>
+      <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
@@ -1508,10 +1498,10 @@
       <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="2" t="n"/>
+      <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="28" t="n"/>
       <c r="AT3" s="5" t="n"/>
-      <c r="AU3" s="2" t="n"/>
+      <c r="AU3" s="2" t="inlineStr"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
@@ -1523,10 +1513,10 @@
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="2" t="n"/>
+      <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="28" t="n"/>
       <c r="BI3" s="5" t="n"/>
-      <c r="BJ3" s="2" t="n"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
       <c r="BK3" s="4" t="n"/>
       <c r="BL3" s="4" t="n"/>
       <c r="BM3" s="4" t="n"/>
@@ -1538,10 +1528,10 @@
       <c r="BS3" s="4" t="n"/>
       <c r="BT3" s="4" t="n"/>
       <c r="BU3" s="4" t="n"/>
-      <c r="BV3" s="2" t="n"/>
+      <c r="BV3" s="2" t="inlineStr"/>
       <c r="BW3" s="28" t="n"/>
       <c r="BX3" s="5" t="n"/>
-      <c r="BY3" s="2" t="n"/>
+      <c r="BY3" s="2" t="inlineStr"/>
       <c r="BZ3" s="4" t="n"/>
       <c r="CA3" s="4" t="n"/>
       <c r="CB3" s="4" t="n"/>
@@ -1553,22 +1543,12 @@
       <c r="CH3" s="4" t="n"/>
       <c r="CI3" s="4" t="n"/>
       <c r="CJ3" s="4" t="n"/>
-      <c r="CK3" s="2" t="n"/>
+      <c r="CK3" s="2" t="inlineStr"/>
       <c r="CL3" s="28" t="n"/>
-      <c r="CN3" s="2" t="n"/>
+      <c r="CN3" s="2" t="inlineStr"/>
       <c r="CP3" s="11" t="n"/>
       <c r="CQ3" s="7" t="n"/>
       <c r="CR3" s="12" t="n"/>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1640,7 +1620,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>AI+C1&gt;</t>
+          <t>_</t>
         </is>
       </c>
       <c r="AD4" s="28" t="n">
@@ -1720,7 +1700,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AZ4" s="4" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="BA4" s="4" t="n">
         <v>0</v>
@@ -2024,7 +2004,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AZ5" s="4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="BA5" s="4" t="n">
         <v>0</v>
@@ -2318,10 +2298,10 @@
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="2" t="n"/>
+      <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="28" t="n"/>
       <c r="AE7" s="5" t="n"/>
-      <c r="AF7" s="2" t="n"/>
+      <c r="AF7" s="2" t="inlineStr"/>
       <c r="AG7" s="4" t="n"/>
       <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="n"/>
@@ -2333,10 +2313,10 @@
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="2" t="n"/>
+      <c r="AR7" s="2" t="inlineStr"/>
       <c r="AS7" s="28" t="n"/>
       <c r="AT7" s="5" t="n"/>
-      <c r="AU7" s="2" t="n"/>
+      <c r="AU7" s="2" t="inlineStr"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
@@ -2348,10 +2328,10 @@
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="2" t="n"/>
+      <c r="BG7" s="2" t="inlineStr"/>
       <c r="BH7" s="28" t="n"/>
       <c r="BI7" s="5" t="n"/>
-      <c r="BJ7" s="2" t="n"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
       <c r="BK7" s="4" t="n"/>
       <c r="BL7" s="4" t="n"/>
       <c r="BM7" s="4" t="n"/>
@@ -2363,10 +2343,10 @@
       <c r="BS7" s="4" t="n"/>
       <c r="BT7" s="4" t="n"/>
       <c r="BU7" s="4" t="n"/>
-      <c r="BV7" s="2" t="n"/>
+      <c r="BV7" s="2" t="inlineStr"/>
       <c r="BW7" s="28" t="n"/>
       <c r="BX7" s="5" t="n"/>
-      <c r="BY7" s="2" t="n"/>
+      <c r="BY7" s="2" t="inlineStr"/>
       <c r="BZ7" s="4" t="n"/>
       <c r="CA7" s="4" t="n"/>
       <c r="CB7" s="4" t="n"/>
@@ -2378,22 +2358,12 @@
       <c r="CH7" s="4" t="n"/>
       <c r="CI7" s="4" t="n"/>
       <c r="CJ7" s="4" t="n"/>
-      <c r="CK7" s="2" t="n"/>
+      <c r="CK7" s="2" t="inlineStr"/>
       <c r="CL7" s="28" t="n"/>
-      <c r="CN7" s="2" t="n"/>
+      <c r="CN7" s="2" t="inlineStr"/>
       <c r="CP7" s="11" t="n"/>
       <c r="CQ7" s="7" t="n"/>
       <c r="CR7" s="12" t="n"/>
-      <c r="CS7" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2431,10 +2401,10 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="2" t="n"/>
+      <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="28" t="n"/>
       <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="2" t="n"/>
+      <c r="AF8" s="2" t="inlineStr"/>
       <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="n"/>
@@ -2446,10 +2416,10 @@
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="2" t="n"/>
+      <c r="AR8" s="2" t="inlineStr"/>
       <c r="AS8" s="28" t="n"/>
       <c r="AT8" s="5" t="n"/>
-      <c r="AU8" s="2" t="n"/>
+      <c r="AU8" s="2" t="inlineStr"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -2461,10 +2431,10 @@
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="2" t="n"/>
+      <c r="BG8" s="2" t="inlineStr"/>
       <c r="BH8" s="28" t="n"/>
       <c r="BI8" s="5" t="n"/>
-      <c r="BJ8" s="2" t="n"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
       <c r="BK8" s="4" t="n"/>
       <c r="BL8" s="4" t="n"/>
       <c r="BM8" s="4" t="n"/>
@@ -2476,10 +2446,10 @@
       <c r="BS8" s="4" t="n"/>
       <c r="BT8" s="4" t="n"/>
       <c r="BU8" s="4" t="n"/>
-      <c r="BV8" s="2" t="n"/>
+      <c r="BV8" s="2" t="inlineStr"/>
       <c r="BW8" s="28" t="n"/>
       <c r="BX8" s="5" t="n"/>
-      <c r="BY8" s="2" t="n"/>
+      <c r="BY8" s="2" t="inlineStr"/>
       <c r="BZ8" s="4" t="n"/>
       <c r="CA8" s="4" t="n"/>
       <c r="CB8" s="4" t="n"/>
@@ -2491,22 +2461,12 @@
       <c r="CH8" s="4" t="n"/>
       <c r="CI8" s="4" t="n"/>
       <c r="CJ8" s="4" t="n"/>
-      <c r="CK8" s="2" t="n"/>
+      <c r="CK8" s="2" t="inlineStr"/>
       <c r="CL8" s="28" t="n"/>
-      <c r="CN8" s="2" t="n"/>
+      <c r="CN8" s="2" t="inlineStr"/>
       <c r="CP8" s="11" t="n"/>
       <c r="CQ8" s="7" t="n"/>
       <c r="CR8" s="12" t="n"/>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2631,7 +2591,7 @@
         <v>95.3</v>
       </c>
       <c r="AZ9" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="BA9" s="4" t="n">
         <v>1</v>
@@ -2758,10 +2718,10 @@
       <c r="Z10" s="4" t="n"/>
       <c r="AA10" s="4" t="n"/>
       <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="2" t="n"/>
+      <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="28" t="n"/>
       <c r="AE10" s="5" t="n"/>
-      <c r="AF10" s="2" t="n"/>
+      <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="4" t="n"/>
       <c r="AH10" s="4" t="n"/>
       <c r="AI10" s="4" t="n"/>
@@ -2773,10 +2733,10 @@
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="2" t="n"/>
+      <c r="AR10" s="2" t="inlineStr"/>
       <c r="AS10" s="28" t="n"/>
       <c r="AT10" s="5" t="n"/>
-      <c r="AU10" s="2" t="n"/>
+      <c r="AU10" s="2" t="inlineStr"/>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
@@ -2788,10 +2748,10 @@
       <c r="BD10" s="4" t="n"/>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="2" t="n"/>
+      <c r="BG10" s="2" t="inlineStr"/>
       <c r="BH10" s="28" t="n"/>
       <c r="BI10" s="5" t="n"/>
-      <c r="BJ10" s="2" t="n"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
       <c r="BM10" s="4" t="n"/>
@@ -2803,10 +2763,10 @@
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
       <c r="BU10" s="4" t="n"/>
-      <c r="BV10" s="2" t="n"/>
+      <c r="BV10" s="2" t="inlineStr"/>
       <c r="BW10" s="28" t="n"/>
       <c r="BX10" s="5" t="n"/>
-      <c r="BY10" s="2" t="n"/>
+      <c r="BY10" s="2" t="inlineStr"/>
       <c r="BZ10" s="4" t="n"/>
       <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
@@ -2818,22 +2778,12 @@
       <c r="CH10" s="4" t="n"/>
       <c r="CI10" s="4" t="n"/>
       <c r="CJ10" s="4" t="n"/>
-      <c r="CK10" s="2" t="n"/>
+      <c r="CK10" s="2" t="inlineStr"/>
       <c r="CL10" s="28" t="n"/>
-      <c r="CN10" s="2" t="n"/>
+      <c r="CN10" s="2" t="inlineStr"/>
       <c r="CP10" s="11" t="n"/>
       <c r="CQ10" s="7" t="n"/>
       <c r="CR10" s="12" t="n"/>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,10 +2821,10 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="2" t="n"/>
+      <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="28" t="n"/>
       <c r="AE11" s="5" t="n"/>
-      <c r="AF11" s="2" t="n"/>
+      <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="n"/>
@@ -2886,10 +2836,10 @@
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="2" t="n"/>
+      <c r="AR11" s="2" t="inlineStr"/>
       <c r="AS11" s="28" t="n"/>
       <c r="AT11" s="5" t="n"/>
-      <c r="AU11" s="2" t="n"/>
+      <c r="AU11" s="2" t="inlineStr"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -2901,10 +2851,10 @@
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="2" t="n"/>
+      <c r="BG11" s="2" t="inlineStr"/>
       <c r="BH11" s="28" t="n"/>
       <c r="BI11" s="5" t="n"/>
-      <c r="BJ11" s="2" t="n"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
       <c r="BK11" s="4" t="n"/>
       <c r="BL11" s="4" t="n"/>
       <c r="BM11" s="4" t="n"/>
@@ -2916,10 +2866,10 @@
       <c r="BS11" s="4" t="n"/>
       <c r="BT11" s="4" t="n"/>
       <c r="BU11" s="4" t="n"/>
-      <c r="BV11" s="2" t="n"/>
+      <c r="BV11" s="2" t="inlineStr"/>
       <c r="BW11" s="28" t="n"/>
       <c r="BX11" s="5" t="n"/>
-      <c r="BY11" s="2" t="n"/>
+      <c r="BY11" s="2" t="inlineStr"/>
       <c r="BZ11" s="4" t="n"/>
       <c r="CA11" s="4" t="n"/>
       <c r="CB11" s="4" t="n"/>
@@ -2931,22 +2881,12 @@
       <c r="CH11" s="4" t="n"/>
       <c r="CI11" s="4" t="n"/>
       <c r="CJ11" s="4" t="n"/>
-      <c r="CK11" s="2" t="n"/>
+      <c r="CK11" s="2" t="inlineStr"/>
       <c r="CL11" s="28" t="n"/>
-      <c r="CN11" s="2" t="n"/>
+      <c r="CN11" s="2" t="inlineStr"/>
       <c r="CP11" s="11" t="n"/>
       <c r="CQ11" s="7" t="n"/>
       <c r="CR11" s="12" t="n"/>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU11" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3074,7 +3014,7 @@
         <v>98.8</v>
       </c>
       <c r="AZ12" s="4" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="BA12" s="4" t="n">
         <v>0</v>
@@ -3262,10 +3202,10 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="2" t="n"/>
+      <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="28" t="n"/>
       <c r="AE13" s="5" t="n"/>
-      <c r="AF13" s="2" t="n"/>
+      <c r="AF13" s="2" t="inlineStr"/>
       <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
       <c r="AI13" s="4" t="n"/>
@@ -3277,10 +3217,10 @@
       <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="2" t="n"/>
+      <c r="AR13" s="2" t="inlineStr"/>
       <c r="AS13" s="28" t="n"/>
       <c r="AT13" s="5" t="n"/>
-      <c r="AU13" s="2" t="n"/>
+      <c r="AU13" s="2" t="inlineStr"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -3292,10 +3232,10 @@
       <c r="BD13" s="4" t="n"/>
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="2" t="n"/>
+      <c r="BG13" s="2" t="inlineStr"/>
       <c r="BH13" s="28" t="n"/>
       <c r="BI13" s="5" t="n"/>
-      <c r="BJ13" s="2" t="n"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
       <c r="BK13" s="4" t="n"/>
       <c r="BL13" s="4" t="n"/>
       <c r="BM13" s="4" t="n"/>
@@ -3307,10 +3247,10 @@
       <c r="BS13" s="4" t="n"/>
       <c r="BT13" s="4" t="n"/>
       <c r="BU13" s="4" t="n"/>
-      <c r="BV13" s="2" t="n"/>
+      <c r="BV13" s="2" t="inlineStr"/>
       <c r="BW13" s="28" t="n"/>
       <c r="BX13" s="5" t="n"/>
-      <c r="BY13" s="2" t="n"/>
+      <c r="BY13" s="2" t="inlineStr"/>
       <c r="BZ13" s="4" t="n"/>
       <c r="CA13" s="4" t="n"/>
       <c r="CB13" s="4" t="n"/>
@@ -3322,22 +3262,12 @@
       <c r="CH13" s="4" t="n"/>
       <c r="CI13" s="4" t="n"/>
       <c r="CJ13" s="4" t="n"/>
-      <c r="CK13" s="2" t="n"/>
+      <c r="CK13" s="2" t="inlineStr"/>
       <c r="CL13" s="28" t="n"/>
-      <c r="CN13" s="2" t="n"/>
+      <c r="CN13" s="2" t="inlineStr"/>
       <c r="CP13" s="11" t="n"/>
       <c r="CQ13" s="7" t="n"/>
       <c r="CR13" s="12" t="n"/>
-      <c r="CS13" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU13" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3549,10 +3479,10 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="2" t="n"/>
+      <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="28" t="n"/>
       <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="2" t="n"/>
+      <c r="AF15" s="2" t="inlineStr"/>
       <c r="AG15" s="4" t="n"/>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
@@ -3564,10 +3494,10 @@
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="2" t="n"/>
+      <c r="AR15" s="2" t="inlineStr"/>
       <c r="AS15" s="28" t="n"/>
       <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="2" t="n"/>
+      <c r="AU15" s="2" t="inlineStr"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
@@ -3579,10 +3509,10 @@
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
       <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="2" t="n"/>
+      <c r="BG15" s="2" t="inlineStr"/>
       <c r="BH15" s="28" t="n"/>
       <c r="BI15" s="5" t="n"/>
-      <c r="BJ15" s="2" t="n"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
       <c r="BK15" s="4" t="n"/>
       <c r="BL15" s="4" t="n"/>
       <c r="BM15" s="4" t="n"/>
@@ -3594,10 +3524,10 @@
       <c r="BS15" s="4" t="n"/>
       <c r="BT15" s="4" t="n"/>
       <c r="BU15" s="4" t="n"/>
-      <c r="BV15" s="2" t="n"/>
+      <c r="BV15" s="2" t="inlineStr"/>
       <c r="BW15" s="28" t="n"/>
       <c r="BX15" s="5" t="n"/>
-      <c r="BY15" s="2" t="n"/>
+      <c r="BY15" s="2" t="inlineStr"/>
       <c r="BZ15" s="4" t="n"/>
       <c r="CA15" s="4" t="n"/>
       <c r="CB15" s="4" t="n"/>
@@ -3609,22 +3539,12 @@
       <c r="CH15" s="4" t="n"/>
       <c r="CI15" s="4" t="n"/>
       <c r="CJ15" s="4" t="n"/>
-      <c r="CK15" s="2" t="n"/>
+      <c r="CK15" s="2" t="inlineStr"/>
       <c r="CL15" s="28" t="n"/>
-      <c r="CN15" s="2" t="n"/>
+      <c r="CN15" s="2" t="inlineStr"/>
       <c r="CP15" s="11" t="n"/>
       <c r="CQ15" s="7" t="n"/>
       <c r="CR15" s="12" t="n"/>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU15" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,10 +3581,10 @@
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="2" t="n"/>
+      <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="28" t="n"/>
       <c r="AE16" s="5" t="n"/>
-      <c r="AF16" s="2" t="n"/>
+      <c r="AF16" s="2" t="inlineStr"/>
       <c r="AG16" s="4" t="n"/>
       <c r="AH16" s="4" t="n"/>
       <c r="AI16" s="4" t="n"/>
@@ -3676,10 +3596,10 @@
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="2" t="n"/>
+      <c r="AR16" s="2" t="inlineStr"/>
       <c r="AS16" s="28" t="n"/>
       <c r="AT16" s="5" t="n"/>
-      <c r="AU16" s="2" t="n"/>
+      <c r="AU16" s="2" t="inlineStr"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -3691,10 +3611,10 @@
       <c r="BD16" s="4" t="n"/>
       <c r="BE16" s="4" t="n"/>
       <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="2" t="n"/>
+      <c r="BG16" s="2" t="inlineStr"/>
       <c r="BH16" s="28" t="n"/>
       <c r="BI16" s="5" t="n"/>
-      <c r="BJ16" s="2" t="n"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
       <c r="BK16" s="4" t="n"/>
       <c r="BL16" s="4" t="n"/>
       <c r="BM16" s="4" t="n"/>
@@ -3706,10 +3626,10 @@
       <c r="BS16" s="4" t="n"/>
       <c r="BT16" s="4" t="n"/>
       <c r="BU16" s="4" t="n"/>
-      <c r="BV16" s="2" t="n"/>
+      <c r="BV16" s="2" t="inlineStr"/>
       <c r="BW16" s="28" t="n"/>
       <c r="BX16" s="5" t="n"/>
-      <c r="BY16" s="2" t="n"/>
+      <c r="BY16" s="2" t="inlineStr"/>
       <c r="BZ16" s="4" t="n"/>
       <c r="CA16" s="4" t="n"/>
       <c r="CB16" s="4" t="n"/>
@@ -3721,22 +3641,12 @@
       <c r="CH16" s="4" t="n"/>
       <c r="CI16" s="4" t="n"/>
       <c r="CJ16" s="4" t="n"/>
-      <c r="CK16" s="2" t="n"/>
+      <c r="CK16" s="2" t="inlineStr"/>
       <c r="CL16" s="28" t="n"/>
-      <c r="CN16" s="2" t="n"/>
+      <c r="CN16" s="2" t="inlineStr"/>
       <c r="CP16" s="11" t="n"/>
       <c r="CQ16" s="7" t="n"/>
       <c r="CR16" s="12" t="n"/>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU16" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3773,10 +3683,10 @@
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="2" t="n"/>
+      <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="28" t="n"/>
       <c r="AE17" s="5" t="n"/>
-      <c r="AF17" s="2" t="n"/>
+      <c r="AF17" s="2" t="inlineStr"/>
       <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
@@ -3788,10 +3698,10 @@
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="2" t="n"/>
+      <c r="AR17" s="2" t="inlineStr"/>
       <c r="AS17" s="28" t="n"/>
       <c r="AT17" s="5" t="n"/>
-      <c r="AU17" s="2" t="n"/>
+      <c r="AU17" s="2" t="inlineStr"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
@@ -3803,10 +3713,10 @@
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="2" t="n"/>
+      <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="28" t="n"/>
       <c r="BI17" s="5" t="n"/>
-      <c r="BJ17" s="2" t="n"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
       <c r="BK17" s="4" t="n"/>
       <c r="BL17" s="4" t="n"/>
       <c r="BM17" s="4" t="n"/>
@@ -3818,10 +3728,10 @@
       <c r="BS17" s="4" t="n"/>
       <c r="BT17" s="4" t="n"/>
       <c r="BU17" s="4" t="n"/>
-      <c r="BV17" s="2" t="n"/>
+      <c r="BV17" s="2" t="inlineStr"/>
       <c r="BW17" s="28" t="n"/>
       <c r="BX17" s="5" t="n"/>
-      <c r="BY17" s="2" t="n"/>
+      <c r="BY17" s="2" t="inlineStr"/>
       <c r="BZ17" s="4" t="n"/>
       <c r="CA17" s="4" t="n"/>
       <c r="CB17" s="4" t="n"/>
@@ -3833,22 +3743,12 @@
       <c r="CH17" s="4" t="n"/>
       <c r="CI17" s="4" t="n"/>
       <c r="CJ17" s="4" t="n"/>
-      <c r="CK17" s="2" t="n"/>
+      <c r="CK17" s="2" t="inlineStr"/>
       <c r="CL17" s="28" t="n"/>
-      <c r="CN17" s="2" t="n"/>
+      <c r="CN17" s="2" t="inlineStr"/>
       <c r="CP17" s="11" t="n"/>
       <c r="CQ17" s="7" t="n"/>
       <c r="CR17" s="12" t="n"/>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU17" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3886,10 +3786,10 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="2" t="n"/>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="28" t="n"/>
       <c r="AE18" s="5" t="n"/>
-      <c r="AF18" s="2" t="n"/>
+      <c r="AF18" s="2" t="inlineStr"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
@@ -3901,10 +3801,10 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="2" t="n"/>
+      <c r="AR18" s="2" t="inlineStr"/>
       <c r="AS18" s="28" t="n"/>
       <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="2" t="n"/>
+      <c r="AU18" s="2" t="inlineStr"/>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
@@ -3916,10 +3816,10 @@
       <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="2" t="n"/>
+      <c r="BG18" s="2" t="inlineStr"/>
       <c r="BH18" s="28" t="n"/>
       <c r="BI18" s="5" t="n"/>
-      <c r="BJ18" s="2" t="n"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
       <c r="BK18" s="4" t="n"/>
       <c r="BL18" s="4" t="n"/>
       <c r="BM18" s="4" t="n"/>
@@ -3931,10 +3831,10 @@
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
       <c r="BU18" s="4" t="n"/>
-      <c r="BV18" s="2" t="n"/>
+      <c r="BV18" s="2" t="inlineStr"/>
       <c r="BW18" s="28" t="n"/>
       <c r="BX18" s="5" t="n"/>
-      <c r="BY18" s="2" t="n"/>
+      <c r="BY18" s="2" t="inlineStr"/>
       <c r="BZ18" s="4" t="n"/>
       <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
@@ -3946,22 +3846,12 @@
       <c r="CH18" s="4" t="n"/>
       <c r="CI18" s="4" t="n"/>
       <c r="CJ18" s="4" t="n"/>
-      <c r="CK18" s="2" t="n"/>
+      <c r="CK18" s="2" t="inlineStr"/>
       <c r="CL18" s="28" t="n"/>
-      <c r="CN18" s="2" t="n"/>
+      <c r="CN18" s="2" t="inlineStr"/>
       <c r="CP18" s="11" t="n"/>
       <c r="CQ18" s="7" t="n"/>
       <c r="CR18" s="12" t="n"/>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU18" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4113,7 +4003,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="AZ19" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA19" s="4" t="n">
         <v>0</v>
@@ -4300,10 +4190,10 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="2" t="n"/>
+      <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="28" t="n"/>
       <c r="AE20" s="5" t="n"/>
-      <c r="AF20" s="2" t="n"/>
+      <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -4315,10 +4205,10 @@
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="2" t="n"/>
+      <c r="AR20" s="2" t="inlineStr"/>
       <c r="AS20" s="28" t="n"/>
       <c r="AT20" s="5" t="n"/>
-      <c r="AU20" s="2" t="n"/>
+      <c r="AU20" s="2" t="inlineStr"/>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
@@ -4330,10 +4220,10 @@
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="2" t="n"/>
+      <c r="BG20" s="2" t="inlineStr"/>
       <c r="BH20" s="28" t="n"/>
       <c r="BI20" s="5" t="n"/>
-      <c r="BJ20" s="2" t="n"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
       <c r="BK20" s="4" t="n"/>
       <c r="BL20" s="4" t="n"/>
       <c r="BM20" s="4" t="n"/>
@@ -4345,10 +4235,10 @@
       <c r="BS20" s="4" t="n"/>
       <c r="BT20" s="4" t="n"/>
       <c r="BU20" s="4" t="n"/>
-      <c r="BV20" s="2" t="n"/>
+      <c r="BV20" s="2" t="inlineStr"/>
       <c r="BW20" s="28" t="n"/>
       <c r="BX20" s="5" t="n"/>
-      <c r="BY20" s="2" t="n"/>
+      <c r="BY20" s="2" t="inlineStr"/>
       <c r="BZ20" s="4" t="n"/>
       <c r="CA20" s="4" t="n"/>
       <c r="CB20" s="4" t="n"/>
@@ -4360,22 +4250,12 @@
       <c r="CH20" s="4" t="n"/>
       <c r="CI20" s="4" t="n"/>
       <c r="CJ20" s="4" t="n"/>
-      <c r="CK20" s="2" t="n"/>
+      <c r="CK20" s="2" t="inlineStr"/>
       <c r="CL20" s="28" t="n"/>
-      <c r="CN20" s="2" t="n"/>
+      <c r="CN20" s="2" t="inlineStr"/>
       <c r="CP20" s="11" t="n"/>
       <c r="CQ20" s="7" t="n"/>
       <c r="CR20" s="12" t="n"/>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU20" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4527,7 +4407,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="AZ21" s="4" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="BA21" s="4" t="n">
         <v>1</v>
@@ -4704,10 +4584,10 @@
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
       <c r="AB22" s="4" t="n"/>
-      <c r="AC22" s="2" t="n"/>
+      <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="28" t="n"/>
       <c r="AE22" s="5" t="n"/>
-      <c r="AF22" s="2" t="n"/>
+      <c r="AF22" s="2" t="inlineStr"/>
       <c r="AG22" s="4" t="n"/>
       <c r="AH22" s="4" t="n"/>
       <c r="AI22" s="4" t="n"/>
@@ -4719,10 +4599,10 @@
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
-      <c r="AR22" s="2" t="n"/>
+      <c r="AR22" s="2" t="inlineStr"/>
       <c r="AS22" s="28" t="n"/>
       <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="2" t="n"/>
+      <c r="AU22" s="2" t="inlineStr"/>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
@@ -4734,10 +4614,10 @@
       <c r="BD22" s="4" t="n"/>
       <c r="BE22" s="4" t="n"/>
       <c r="BF22" s="4" t="n"/>
-      <c r="BG22" s="2" t="n"/>
+      <c r="BG22" s="2" t="inlineStr"/>
       <c r="BH22" s="28" t="n"/>
       <c r="BI22" s="5" t="n"/>
-      <c r="BJ22" s="2" t="n"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
       <c r="BK22" s="4" t="n"/>
       <c r="BL22" s="4" t="n"/>
       <c r="BM22" s="4" t="n"/>
@@ -4749,10 +4629,10 @@
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
       <c r="BU22" s="4" t="n"/>
-      <c r="BV22" s="2" t="n"/>
+      <c r="BV22" s="2" t="inlineStr"/>
       <c r="BW22" s="28" t="n"/>
       <c r="BX22" s="5" t="n"/>
-      <c r="BY22" s="2" t="n"/>
+      <c r="BY22" s="2" t="inlineStr"/>
       <c r="BZ22" s="4" t="n"/>
       <c r="CA22" s="4" t="n"/>
       <c r="CB22" s="4" t="n"/>
@@ -4764,22 +4644,12 @@
       <c r="CH22" s="4" t="n"/>
       <c r="CI22" s="4" t="n"/>
       <c r="CJ22" s="4" t="n"/>
-      <c r="CK22" s="2" t="n"/>
+      <c r="CK22" s="2" t="inlineStr"/>
       <c r="CL22" s="28" t="n"/>
-      <c r="CN22" s="2" t="n"/>
+      <c r="CN22" s="2" t="inlineStr"/>
       <c r="CP22" s="11" t="n"/>
       <c r="CQ22" s="7" t="n"/>
       <c r="CR22" s="12" t="n"/>
-      <c r="CS22" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU22" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4817,10 +4687,10 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="2" t="n"/>
+      <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="28" t="n"/>
       <c r="AE23" s="5" t="n"/>
-      <c r="AF23" s="2" t="n"/>
+      <c r="AF23" s="2" t="inlineStr"/>
       <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
       <c r="AI23" s="4" t="n"/>
@@ -4832,10 +4702,10 @@
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
-      <c r="AR23" s="2" t="n"/>
+      <c r="AR23" s="2" t="inlineStr"/>
       <c r="AS23" s="28" t="n"/>
       <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="2" t="n"/>
+      <c r="AU23" s="2" t="inlineStr"/>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
@@ -4847,10 +4717,10 @@
       <c r="BD23" s="4" t="n"/>
       <c r="BE23" s="4" t="n"/>
       <c r="BF23" s="4" t="n"/>
-      <c r="BG23" s="2" t="n"/>
+      <c r="BG23" s="2" t="inlineStr"/>
       <c r="BH23" s="28" t="n"/>
       <c r="BI23" s="5" t="n"/>
-      <c r="BJ23" s="2" t="n"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
       <c r="BK23" s="4" t="n"/>
       <c r="BL23" s="4" t="n"/>
       <c r="BM23" s="4" t="n"/>
@@ -4862,10 +4732,10 @@
       <c r="BS23" s="4" t="n"/>
       <c r="BT23" s="4" t="n"/>
       <c r="BU23" s="4" t="n"/>
-      <c r="BV23" s="2" t="n"/>
+      <c r="BV23" s="2" t="inlineStr"/>
       <c r="BW23" s="28" t="n"/>
       <c r="BX23" s="5" t="n"/>
-      <c r="BY23" s="2" t="n"/>
+      <c r="BY23" s="2" t="inlineStr"/>
       <c r="BZ23" s="4" t="n"/>
       <c r="CA23" s="4" t="n"/>
       <c r="CB23" s="4" t="n"/>
@@ -4877,23 +4747,13 @@
       <c r="CH23" s="4" t="n"/>
       <c r="CI23" s="4" t="n"/>
       <c r="CJ23" s="4" t="n"/>
-      <c r="CK23" s="2" t="n"/>
+      <c r="CK23" s="2" t="inlineStr"/>
       <c r="CL23" s="28" t="n"/>
       <c r="CM23" s="5" t="n"/>
-      <c r="CN23" s="2" t="n"/>
+      <c r="CN23" s="2" t="inlineStr"/>
       <c r="CP23" s="11" t="n"/>
       <c r="CQ23" s="7" t="n"/>
       <c r="CR23" s="12" t="n"/>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU23" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5047,7 +4907,7 @@
         <v>99.8</v>
       </c>
       <c r="AZ24" s="4" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="BA24" s="4" t="n">
         <v>0</v>
@@ -5351,7 +5211,7 @@
         <v>96.3</v>
       </c>
       <c r="AZ25" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="BA25" s="4" t="n">
         <v>0</v>
@@ -5532,10 +5392,10 @@
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
       <c r="AB26" s="4" t="n"/>
-      <c r="AC26" s="2" t="n"/>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="28" t="n"/>
       <c r="AE26" s="5" t="n"/>
-      <c r="AF26" s="2" t="n"/>
+      <c r="AF26" s="2" t="inlineStr"/>
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
@@ -5547,10 +5407,10 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="2" t="n"/>
+      <c r="AR26" s="2" t="inlineStr"/>
       <c r="AS26" s="28" t="n"/>
       <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="2" t="n"/>
+      <c r="AU26" s="2" t="inlineStr"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
       <c r="AX26" s="4" t="n"/>
@@ -5562,10 +5422,10 @@
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
-      <c r="BG26" s="2" t="n"/>
+      <c r="BG26" s="2" t="inlineStr"/>
       <c r="BH26" s="28" t="n"/>
       <c r="BI26" s="5" t="n"/>
-      <c r="BJ26" s="2" t="n"/>
+      <c r="BJ26" s="2" t="inlineStr"/>
       <c r="BK26" s="4" t="n"/>
       <c r="BL26" s="4" t="n"/>
       <c r="BM26" s="4" t="n"/>
@@ -5577,10 +5437,10 @@
       <c r="BS26" s="4" t="n"/>
       <c r="BT26" s="4" t="n"/>
       <c r="BU26" s="4" t="n"/>
-      <c r="BV26" s="2" t="n"/>
+      <c r="BV26" s="2" t="inlineStr"/>
       <c r="BW26" s="28" t="n"/>
       <c r="BX26" s="5" t="n"/>
-      <c r="BY26" s="2" t="n"/>
+      <c r="BY26" s="2" t="inlineStr"/>
       <c r="BZ26" s="4" t="n"/>
       <c r="CA26" s="4" t="n"/>
       <c r="CB26" s="4" t="n"/>
@@ -5592,23 +5452,13 @@
       <c r="CH26" s="4" t="n"/>
       <c r="CI26" s="4" t="n"/>
       <c r="CJ26" s="4" t="n"/>
-      <c r="CK26" s="2" t="n"/>
+      <c r="CK26" s="2" t="inlineStr"/>
       <c r="CL26" s="28" t="n"/>
       <c r="CM26" s="5" t="n"/>
-      <c r="CN26" s="2" t="n"/>
+      <c r="CN26" s="2" t="inlineStr"/>
       <c r="CP26" s="11" t="n"/>
       <c r="CQ26" s="7" t="n"/>
       <c r="CR26" s="12" t="n"/>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU26" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5646,10 +5496,10 @@
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="2" t="n"/>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="28" t="n"/>
       <c r="AE27" s="5" t="n"/>
-      <c r="AF27" s="2" t="n"/>
+      <c r="AF27" s="2" t="inlineStr"/>
       <c r="AG27" s="4" t="n"/>
       <c r="AH27" s="4" t="n"/>
       <c r="AI27" s="4" t="n"/>
@@ -5661,10 +5511,10 @@
       <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
-      <c r="AR27" s="2" t="n"/>
+      <c r="AR27" s="2" t="inlineStr"/>
       <c r="AS27" s="28" t="n"/>
       <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="2" t="n"/>
+      <c r="AU27" s="2" t="inlineStr"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
@@ -5676,10 +5526,10 @@
       <c r="BD27" s="4" t="n"/>
       <c r="BE27" s="4" t="n"/>
       <c r="BF27" s="4" t="n"/>
-      <c r="BG27" s="2" t="n"/>
+      <c r="BG27" s="2" t="inlineStr"/>
       <c r="BH27" s="28" t="n"/>
       <c r="BI27" s="5" t="n"/>
-      <c r="BJ27" s="2" t="n"/>
+      <c r="BJ27" s="2" t="inlineStr"/>
       <c r="BK27" s="4" t="n"/>
       <c r="BL27" s="4" t="n"/>
       <c r="BM27" s="4" t="n"/>
@@ -5691,10 +5541,10 @@
       <c r="BS27" s="4" t="n"/>
       <c r="BT27" s="4" t="n"/>
       <c r="BU27" s="4" t="n"/>
-      <c r="BV27" s="2" t="n"/>
+      <c r="BV27" s="2" t="inlineStr"/>
       <c r="BW27" s="28" t="n"/>
       <c r="BX27" s="5" t="n"/>
-      <c r="BY27" s="2" t="n"/>
+      <c r="BY27" s="2" t="inlineStr"/>
       <c r="BZ27" s="4" t="n"/>
       <c r="CA27" s="4" t="n"/>
       <c r="CB27" s="4" t="n"/>
@@ -5706,22 +5556,12 @@
       <c r="CH27" s="4" t="n"/>
       <c r="CI27" s="4" t="n"/>
       <c r="CJ27" s="4" t="n"/>
-      <c r="CK27" s="2" t="n"/>
+      <c r="CK27" s="2" t="inlineStr"/>
       <c r="CL27" s="28" t="n"/>
-      <c r="CN27" s="2" t="n"/>
+      <c r="CN27" s="2" t="inlineStr"/>
       <c r="CP27" s="11" t="n"/>
       <c r="CQ27" s="7" t="n"/>
       <c r="CR27" s="12" t="n"/>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU27" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5881,10 +5721,10 @@
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
-      <c r="AC29" s="2" t="n"/>
+      <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="28" t="n"/>
       <c r="AE29" s="5" t="n"/>
-      <c r="AF29" s="2" t="n"/>
+      <c r="AF29" s="2" t="inlineStr"/>
       <c r="AG29" s="4" t="n"/>
       <c r="AH29" s="4" t="n"/>
       <c r="AI29" s="4" t="n"/>
@@ -5896,10 +5736,10 @@
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
-      <c r="AR29" s="2" t="n"/>
+      <c r="AR29" s="2" t="inlineStr"/>
       <c r="AS29" s="28" t="n"/>
       <c r="AT29" s="5" t="n"/>
-      <c r="AU29" s="2" t="n"/>
+      <c r="AU29" s="2" t="inlineStr"/>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
@@ -5911,10 +5751,10 @@
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
-      <c r="BG29" s="2" t="n"/>
+      <c r="BG29" s="2" t="inlineStr"/>
       <c r="BH29" s="28" t="n"/>
       <c r="BI29" s="5" t="n"/>
-      <c r="BJ29" s="2" t="n"/>
+      <c r="BJ29" s="2" t="inlineStr"/>
       <c r="BK29" s="4" t="n"/>
       <c r="BL29" s="4" t="n"/>
       <c r="BM29" s="4" t="n"/>
@@ -5926,10 +5766,10 @@
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
       <c r="BU29" s="4" t="n"/>
-      <c r="BV29" s="2" t="n"/>
+      <c r="BV29" s="2" t="inlineStr"/>
       <c r="BW29" s="28" t="n"/>
       <c r="BX29" s="5" t="n"/>
-      <c r="BY29" s="2" t="n"/>
+      <c r="BY29" s="2" t="inlineStr"/>
       <c r="BZ29" s="4" t="n"/>
       <c r="CA29" s="4" t="n"/>
       <c r="CB29" s="4" t="n"/>
@@ -5941,23 +5781,13 @@
       <c r="CH29" s="4" t="n"/>
       <c r="CI29" s="4" t="n"/>
       <c r="CJ29" s="4" t="n"/>
-      <c r="CK29" s="2" t="n"/>
+      <c r="CK29" s="2" t="inlineStr"/>
       <c r="CL29" s="28" t="n"/>
       <c r="CM29" s="5" t="n"/>
-      <c r="CN29" s="2" t="n"/>
+      <c r="CN29" s="2" t="inlineStr"/>
       <c r="CP29" s="11" t="n"/>
       <c r="CQ29" s="7" t="n"/>
       <c r="CR29" s="12" t="n"/>
-      <c r="CS29" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU29" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6085,7 +5915,7 @@
         <v>100</v>
       </c>
       <c r="AZ30" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA30" s="4" t="n">
         <v>0</v>
@@ -6387,7 +6217,7 @@
         <v>99.5</v>
       </c>
       <c r="AZ31" s="4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="BA31" s="4" t="n">
         <v>0</v>
@@ -6575,10 +6405,10 @@
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="2" t="n"/>
+      <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="28" t="n"/>
       <c r="AE32" s="5" t="n"/>
-      <c r="AF32" s="2" t="n"/>
+      <c r="AF32" s="2" t="inlineStr"/>
       <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="n"/>
@@ -6590,10 +6420,10 @@
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="2" t="n"/>
+      <c r="AR32" s="2" t="inlineStr"/>
       <c r="AS32" s="28" t="n"/>
       <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="2" t="n"/>
+      <c r="AU32" s="2" t="inlineStr"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
@@ -6605,10 +6435,10 @@
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="2" t="n"/>
+      <c r="BG32" s="2" t="inlineStr"/>
       <c r="BH32" s="28" t="n"/>
       <c r="BI32" s="5" t="n"/>
-      <c r="BJ32" s="2" t="n"/>
+      <c r="BJ32" s="2" t="inlineStr"/>
       <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
       <c r="BM32" s="4" t="n"/>
@@ -6620,10 +6450,10 @@
       <c r="BS32" s="4" t="n"/>
       <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
-      <c r="BV32" s="2" t="n"/>
+      <c r="BV32" s="2" t="inlineStr"/>
       <c r="BW32" s="28" t="n"/>
       <c r="BX32" s="5" t="n"/>
-      <c r="BY32" s="2" t="n"/>
+      <c r="BY32" s="2" t="inlineStr"/>
       <c r="BZ32" s="4" t="n"/>
       <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
@@ -6635,23 +6465,13 @@
       <c r="CH32" s="4" t="n"/>
       <c r="CI32" s="4" t="n"/>
       <c r="CJ32" s="4" t="n"/>
-      <c r="CK32" s="2" t="n"/>
+      <c r="CK32" s="2" t="inlineStr"/>
       <c r="CL32" s="28" t="n"/>
       <c r="CM32" s="5" t="n"/>
-      <c r="CN32" s="2" t="n"/>
+      <c r="CN32" s="2" t="inlineStr"/>
       <c r="CP32" s="11" t="n"/>
       <c r="CQ32" s="7" t="n"/>
       <c r="CR32" s="12" t="n"/>
-      <c r="CS32" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU32" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6688,10 +6508,10 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="2" t="n"/>
+      <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="28" t="n"/>
       <c r="AE33" s="5" t="n"/>
-      <c r="AF33" s="2" t="n"/>
+      <c r="AF33" s="2" t="inlineStr"/>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
@@ -6703,10 +6523,10 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="2" t="n"/>
+      <c r="AR33" s="2" t="inlineStr"/>
       <c r="AS33" s="28" t="n"/>
       <c r="AT33" s="5" t="n"/>
-      <c r="AU33" s="2" t="n"/>
+      <c r="AU33" s="2" t="inlineStr"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
@@ -6718,10 +6538,10 @@
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
-      <c r="BG33" s="2" t="n"/>
+      <c r="BG33" s="2" t="inlineStr"/>
       <c r="BH33" s="28" t="n"/>
       <c r="BI33" s="5" t="n"/>
-      <c r="BJ33" s="2" t="n"/>
+      <c r="BJ33" s="2" t="inlineStr"/>
       <c r="BK33" s="4" t="n"/>
       <c r="BL33" s="4" t="n"/>
       <c r="BM33" s="4" t="n"/>
@@ -6733,10 +6553,10 @@
       <c r="BS33" s="4" t="n"/>
       <c r="BT33" s="4" t="n"/>
       <c r="BU33" s="4" t="n"/>
-      <c r="BV33" s="2" t="n"/>
+      <c r="BV33" s="2" t="inlineStr"/>
       <c r="BW33" s="28" t="n"/>
       <c r="BX33" s="5" t="n"/>
-      <c r="BY33" s="2" t="n"/>
+      <c r="BY33" s="2" t="inlineStr"/>
       <c r="BZ33" s="4" t="n"/>
       <c r="CA33" s="4" t="n"/>
       <c r="CB33" s="4" t="n"/>
@@ -6748,22 +6568,12 @@
       <c r="CH33" s="4" t="n"/>
       <c r="CI33" s="4" t="n"/>
       <c r="CJ33" s="4" t="n"/>
-      <c r="CK33" s="2" t="n"/>
+      <c r="CK33" s="2" t="inlineStr"/>
       <c r="CL33" s="28" t="n"/>
-      <c r="CN33" s="2" t="n"/>
+      <c r="CN33" s="2" t="inlineStr"/>
       <c r="CP33" s="11" t="n"/>
       <c r="CQ33" s="7" t="n"/>
       <c r="CR33" s="12" t="n"/>
-      <c r="CS33" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU33" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6801,10 +6611,10 @@
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
-      <c r="AC34" s="2" t="n"/>
+      <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="28" t="n"/>
       <c r="AE34" s="5" t="n"/>
-      <c r="AF34" s="2" t="n"/>
+      <c r="AF34" s="2" t="inlineStr"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
       <c r="AI34" s="4" t="n"/>
@@ -6816,10 +6626,10 @@
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
-      <c r="AR34" s="2" t="n"/>
+      <c r="AR34" s="2" t="inlineStr"/>
       <c r="AS34" s="28" t="n"/>
       <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="2" t="n"/>
+      <c r="AU34" s="2" t="inlineStr"/>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -6831,10 +6641,10 @@
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
-      <c r="BG34" s="2" t="n"/>
+      <c r="BG34" s="2" t="inlineStr"/>
       <c r="BH34" s="28" t="n"/>
       <c r="BI34" s="5" t="n"/>
-      <c r="BJ34" s="2" t="n"/>
+      <c r="BJ34" s="2" t="inlineStr"/>
       <c r="BK34" s="4" t="n"/>
       <c r="BL34" s="4" t="n"/>
       <c r="BM34" s="4" t="n"/>
@@ -6846,10 +6656,10 @@
       <c r="BS34" s="4" t="n"/>
       <c r="BT34" s="4" t="n"/>
       <c r="BU34" s="4" t="n"/>
-      <c r="BV34" s="2" t="n"/>
+      <c r="BV34" s="2" t="inlineStr"/>
       <c r="BW34" s="28" t="n"/>
       <c r="BX34" s="5" t="n"/>
-      <c r="BY34" s="2" t="n"/>
+      <c r="BY34" s="2" t="inlineStr"/>
       <c r="BZ34" s="4" t="n"/>
       <c r="CA34" s="4" t="n"/>
       <c r="CB34" s="4" t="n"/>
@@ -6861,22 +6671,12 @@
       <c r="CH34" s="4" t="n"/>
       <c r="CI34" s="4" t="n"/>
       <c r="CJ34" s="4" t="n"/>
-      <c r="CK34" s="2" t="n"/>
+      <c r="CK34" s="2" t="inlineStr"/>
       <c r="CL34" s="28" t="n"/>
-      <c r="CN34" s="2" t="n"/>
+      <c r="CN34" s="2" t="inlineStr"/>
       <c r="CP34" s="11" t="n"/>
       <c r="CQ34" s="7" t="n"/>
       <c r="CR34" s="12" t="n"/>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,10 +6715,10 @@
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="2" t="n"/>
+      <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="28" t="n"/>
       <c r="AE35" s="5" t="n"/>
-      <c r="AF35" s="2" t="n"/>
+      <c r="AF35" s="2" t="inlineStr"/>
       <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="n"/>
@@ -6930,10 +6730,10 @@
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
-      <c r="AR35" s="2" t="n"/>
+      <c r="AR35" s="2" t="inlineStr"/>
       <c r="AS35" s="28" t="n"/>
       <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="2" t="n"/>
+      <c r="AU35" s="2" t="inlineStr"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
@@ -6945,10 +6745,10 @@
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
-      <c r="BG35" s="2" t="n"/>
+      <c r="BG35" s="2" t="inlineStr"/>
       <c r="BH35" s="28" t="n"/>
       <c r="BI35" s="5" t="n"/>
-      <c r="BJ35" s="2" t="n"/>
+      <c r="BJ35" s="2" t="inlineStr"/>
       <c r="BK35" s="4" t="n"/>
       <c r="BL35" s="4" t="n"/>
       <c r="BM35" s="4" t="n"/>
@@ -6960,10 +6760,10 @@
       <c r="BS35" s="4" t="n"/>
       <c r="BT35" s="4" t="n"/>
       <c r="BU35" s="4" t="n"/>
-      <c r="BV35" s="2" t="n"/>
+      <c r="BV35" s="2" t="inlineStr"/>
       <c r="BW35" s="28" t="n"/>
       <c r="BX35" s="5" t="n"/>
-      <c r="BY35" s="2" t="n"/>
+      <c r="BY35" s="2" t="inlineStr"/>
       <c r="BZ35" s="4" t="n"/>
       <c r="CA35" s="4" t="n"/>
       <c r="CB35" s="4" t="n"/>
@@ -6975,23 +6775,13 @@
       <c r="CH35" s="4" t="n"/>
       <c r="CI35" s="4" t="n"/>
       <c r="CJ35" s="4" t="n"/>
-      <c r="CK35" s="2" t="n"/>
+      <c r="CK35" s="2" t="inlineStr"/>
       <c r="CL35" s="28" t="n"/>
-      <c r="CN35" s="2" t="n"/>
+      <c r="CN35" s="2" t="inlineStr"/>
       <c r="CO35" s="6" t="n"/>
       <c r="CP35" s="11" t="n"/>
       <c r="CQ35" s="7" t="n"/>
       <c r="CR35" s="12" t="n"/>
-      <c r="CS35" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU35" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7295,10 +7085,10 @@
       <c r="Z37" s="4" t="n"/>
       <c r="AA37" s="4" t="n"/>
       <c r="AB37" s="4" t="n"/>
-      <c r="AC37" s="2" t="n"/>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="28" t="n"/>
       <c r="AE37" s="5" t="n"/>
-      <c r="AF37" s="2" t="n"/>
+      <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
@@ -7310,10 +7100,10 @@
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="2" t="n"/>
+      <c r="AR37" s="2" t="inlineStr"/>
       <c r="AS37" s="28" t="n"/>
       <c r="AT37" s="5" t="n"/>
-      <c r="AU37" s="2" t="n"/>
+      <c r="AU37" s="2" t="inlineStr"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
@@ -7325,10 +7115,10 @@
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="n"/>
-      <c r="BG37" s="2" t="n"/>
+      <c r="BG37" s="2" t="inlineStr"/>
       <c r="BH37" s="28" t="n"/>
       <c r="BI37" s="5" t="n"/>
-      <c r="BJ37" s="2" t="n"/>
+      <c r="BJ37" s="2" t="inlineStr"/>
       <c r="BK37" s="4" t="n"/>
       <c r="BL37" s="4" t="n"/>
       <c r="BM37" s="4" t="n"/>
@@ -7340,10 +7130,10 @@
       <c r="BS37" s="4" t="n"/>
       <c r="BT37" s="4" t="n"/>
       <c r="BU37" s="4" t="n"/>
-      <c r="BV37" s="2" t="n"/>
+      <c r="BV37" s="2" t="inlineStr"/>
       <c r="BW37" s="28" t="n"/>
       <c r="BX37" s="5" t="n"/>
-      <c r="BY37" s="2" t="n"/>
+      <c r="BY37" s="2" t="inlineStr"/>
       <c r="BZ37" s="4" t="n"/>
       <c r="CA37" s="4" t="n"/>
       <c r="CB37" s="4" t="n"/>
@@ -7355,23 +7145,13 @@
       <c r="CH37" s="4" t="n"/>
       <c r="CI37" s="4" t="n"/>
       <c r="CJ37" s="4" t="n"/>
-      <c r="CK37" s="2" t="n"/>
+      <c r="CK37" s="2" t="inlineStr"/>
       <c r="CL37" s="28" t="n"/>
       <c r="CM37" s="5" t="n"/>
-      <c r="CN37" s="2" t="n"/>
+      <c r="CN37" s="2" t="inlineStr"/>
       <c r="CP37" s="11" t="n"/>
       <c r="CQ37" s="7" t="n"/>
       <c r="CR37" s="12" t="n"/>
-      <c r="CS37" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU37" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7409,10 +7189,10 @@
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
-      <c r="AC38" s="2" t="n"/>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="28" t="n"/>
       <c r="AE38" s="5" t="n"/>
-      <c r="AF38" s="2" t="n"/>
+      <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
@@ -7424,10 +7204,10 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="2" t="n"/>
+      <c r="AR38" s="2" t="inlineStr"/>
       <c r="AS38" s="28" t="n"/>
       <c r="AT38" s="5" t="n"/>
-      <c r="AU38" s="2" t="n"/>
+      <c r="AU38" s="2" t="inlineStr"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
@@ -7439,10 +7219,10 @@
       <c r="BD38" s="4" t="n"/>
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
-      <c r="BG38" s="2" t="n"/>
+      <c r="BG38" s="2" t="inlineStr"/>
       <c r="BH38" s="28" t="n"/>
       <c r="BI38" s="5" t="n"/>
-      <c r="BJ38" s="2" t="n"/>
+      <c r="BJ38" s="2" t="inlineStr"/>
       <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
@@ -7454,10 +7234,10 @@
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
       <c r="BU38" s="4" t="n"/>
-      <c r="BV38" s="2" t="n"/>
+      <c r="BV38" s="2" t="inlineStr"/>
       <c r="BW38" s="28" t="n"/>
       <c r="BX38" s="5" t="n"/>
-      <c r="BY38" s="2" t="n"/>
+      <c r="BY38" s="2" t="inlineStr"/>
       <c r="BZ38" s="4" t="n"/>
       <c r="CA38" s="4" t="n"/>
       <c r="CB38" s="4" t="n"/>
@@ -7469,22 +7249,12 @@
       <c r="CH38" s="4" t="n"/>
       <c r="CI38" s="4" t="n"/>
       <c r="CJ38" s="4" t="n"/>
-      <c r="CK38" s="2" t="n"/>
+      <c r="CK38" s="2" t="inlineStr"/>
       <c r="CL38" s="28" t="n"/>
-      <c r="CN38" s="2" t="n"/>
+      <c r="CN38" s="2" t="inlineStr"/>
       <c r="CP38" s="11" t="n"/>
       <c r="CQ38" s="7" t="n"/>
       <c r="CR38" s="12" t="n"/>
-      <c r="CS38" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU38" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7522,10 +7292,10 @@
       <c r="Z39" s="4" t="n"/>
       <c r="AA39" s="4" t="n"/>
       <c r="AB39" s="4" t="n"/>
-      <c r="AC39" s="2" t="n"/>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="28" t="n"/>
       <c r="AE39" s="5" t="n"/>
-      <c r="AF39" s="2" t="n"/>
+      <c r="AF39" s="2" t="inlineStr"/>
       <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n"/>
       <c r="AI39" s="4" t="n"/>
@@ -7537,10 +7307,10 @@
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
-      <c r="AR39" s="2" t="n"/>
+      <c r="AR39" s="2" t="inlineStr"/>
       <c r="AS39" s="28" t="n"/>
       <c r="AT39" s="5" t="n"/>
-      <c r="AU39" s="2" t="n"/>
+      <c r="AU39" s="2" t="inlineStr"/>
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
@@ -7552,10 +7322,10 @@
       <c r="BD39" s="4" t="n"/>
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
-      <c r="BG39" s="2" t="n"/>
+      <c r="BG39" s="2" t="inlineStr"/>
       <c r="BH39" s="28" t="n"/>
       <c r="BI39" s="5" t="n"/>
-      <c r="BJ39" s="2" t="n"/>
+      <c r="BJ39" s="2" t="inlineStr"/>
       <c r="BK39" s="4" t="n"/>
       <c r="BL39" s="4" t="n"/>
       <c r="BM39" s="4" t="n"/>
@@ -7567,10 +7337,10 @@
       <c r="BS39" s="4" t="n"/>
       <c r="BT39" s="4" t="n"/>
       <c r="BU39" s="4" t="n"/>
-      <c r="BV39" s="2" t="n"/>
+      <c r="BV39" s="2" t="inlineStr"/>
       <c r="BW39" s="28" t="n"/>
       <c r="BX39" s="5" t="n"/>
-      <c r="BY39" s="2" t="n"/>
+      <c r="BY39" s="2" t="inlineStr"/>
       <c r="BZ39" s="4" t="n"/>
       <c r="CA39" s="4" t="n"/>
       <c r="CB39" s="4" t="n"/>
@@ -7582,23 +7352,13 @@
       <c r="CH39" s="4" t="n"/>
       <c r="CI39" s="4" t="n"/>
       <c r="CJ39" s="4" t="n"/>
-      <c r="CK39" s="2" t="n"/>
+      <c r="CK39" s="2" t="inlineStr"/>
       <c r="CL39" s="28" t="n"/>
       <c r="CM39" s="5" t="n"/>
-      <c r="CN39" s="2" t="n"/>
+      <c r="CN39" s="2" t="inlineStr"/>
       <c r="CP39" s="11" t="n"/>
       <c r="CQ39" s="7" t="n"/>
       <c r="CR39" s="12" t="n"/>
-      <c r="CS39" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU39" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7636,10 +7396,10 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="2" t="n"/>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="28" t="n"/>
       <c r="AE40" s="5" t="n"/>
-      <c r="AF40" s="2" t="n"/>
+      <c r="AF40" s="2" t="inlineStr"/>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -7651,10 +7411,10 @@
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="2" t="n"/>
+      <c r="AR40" s="2" t="inlineStr"/>
       <c r="AS40" s="28" t="n"/>
       <c r="AT40" s="5" t="n"/>
-      <c r="AU40" s="2" t="n"/>
+      <c r="AU40" s="2" t="inlineStr"/>
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
@@ -7666,10 +7426,10 @@
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
       <c r="BF40" s="4" t="n"/>
-      <c r="BG40" s="2" t="n"/>
+      <c r="BG40" s="2" t="inlineStr"/>
       <c r="BH40" s="28" t="n"/>
       <c r="BI40" s="5" t="n"/>
-      <c r="BJ40" s="2" t="n"/>
+      <c r="BJ40" s="2" t="inlineStr"/>
       <c r="BK40" s="4" t="n"/>
       <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="4" t="n"/>
@@ -7681,10 +7441,10 @@
       <c r="BS40" s="4" t="n"/>
       <c r="BT40" s="4" t="n"/>
       <c r="BU40" s="4" t="n"/>
-      <c r="BV40" s="2" t="n"/>
+      <c r="BV40" s="2" t="inlineStr"/>
       <c r="BW40" s="28" t="n"/>
       <c r="BX40" s="5" t="n"/>
-      <c r="BY40" s="2" t="n"/>
+      <c r="BY40" s="2" t="inlineStr"/>
       <c r="BZ40" s="4" t="n"/>
       <c r="CA40" s="4" t="n"/>
       <c r="CB40" s="4" t="n"/>
@@ -7696,22 +7456,12 @@
       <c r="CH40" s="4" t="n"/>
       <c r="CI40" s="4" t="n"/>
       <c r="CJ40" s="4" t="n"/>
-      <c r="CK40" s="2" t="n"/>
+      <c r="CK40" s="2" t="inlineStr"/>
       <c r="CL40" s="28" t="n"/>
-      <c r="CN40" s="2" t="n"/>
+      <c r="CN40" s="2" t="inlineStr"/>
       <c r="CP40" s="11" t="n"/>
       <c r="CQ40" s="7" t="n"/>
       <c r="CR40" s="12" t="n"/>
-      <c r="CS40" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU40" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8029,7 +7779,7 @@
         <v>88.3</v>
       </c>
       <c r="AZ42" s="4" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="BA42" s="4" t="n">
         <v>0</v>
@@ -8217,10 +7967,10 @@
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="4" t="n"/>
       <c r="AB43" s="4" t="n"/>
-      <c r="AC43" s="2" t="n"/>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="28" t="n"/>
       <c r="AE43" s="5" t="n"/>
-      <c r="AF43" s="2" t="n"/>
+      <c r="AF43" s="2" t="inlineStr"/>
       <c r="AG43" s="4" t="n"/>
       <c r="AH43" s="4" t="n"/>
       <c r="AI43" s="4" t="n"/>
@@ -8232,10 +7982,10 @@
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
-      <c r="AR43" s="2" t="n"/>
+      <c r="AR43" s="2" t="inlineStr"/>
       <c r="AS43" s="28" t="n"/>
       <c r="AT43" s="5" t="n"/>
-      <c r="AU43" s="2" t="n"/>
+      <c r="AU43" s="2" t="inlineStr"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
@@ -8247,10 +7997,10 @@
       <c r="BD43" s="4" t="n"/>
       <c r="BE43" s="4" t="n"/>
       <c r="BF43" s="4" t="n"/>
-      <c r="BG43" s="2" t="n"/>
+      <c r="BG43" s="2" t="inlineStr"/>
       <c r="BH43" s="28" t="n"/>
       <c r="BI43" s="5" t="n"/>
-      <c r="BJ43" s="2" t="n"/>
+      <c r="BJ43" s="2" t="inlineStr"/>
       <c r="BK43" s="4" t="n"/>
       <c r="BL43" s="4" t="n"/>
       <c r="BM43" s="4" t="n"/>
@@ -8262,10 +8012,10 @@
       <c r="BS43" s="4" t="n"/>
       <c r="BT43" s="4" t="n"/>
       <c r="BU43" s="4" t="n"/>
-      <c r="BV43" s="2" t="n"/>
+      <c r="BV43" s="2" t="inlineStr"/>
       <c r="BW43" s="28" t="n"/>
       <c r="BX43" s="5" t="n"/>
-      <c r="BY43" s="2" t="n"/>
+      <c r="BY43" s="2" t="inlineStr"/>
       <c r="BZ43" s="4" t="n"/>
       <c r="CA43" s="4" t="n"/>
       <c r="CB43" s="4" t="n"/>
@@ -8277,22 +8027,12 @@
       <c r="CH43" s="4" t="n"/>
       <c r="CI43" s="4" t="n"/>
       <c r="CJ43" s="4" t="n"/>
-      <c r="CK43" s="2" t="n"/>
+      <c r="CK43" s="2" t="inlineStr"/>
       <c r="CL43" s="28" t="n"/>
-      <c r="CN43" s="2" t="n"/>
+      <c r="CN43" s="2" t="inlineStr"/>
       <c r="CP43" s="11" t="n"/>
       <c r="CQ43" s="7" t="n"/>
       <c r="CR43" s="12" t="n"/>
-      <c r="CS43" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU43" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,10 +8069,10 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="2" t="n"/>
+      <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="28" t="n"/>
       <c r="AE44" s="5" t="n"/>
-      <c r="AF44" s="2" t="n"/>
+      <c r="AF44" s="2" t="inlineStr"/>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
@@ -8344,10 +8084,10 @@
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
-      <c r="AR44" s="2" t="n"/>
+      <c r="AR44" s="2" t="inlineStr"/>
       <c r="AS44" s="28" t="n"/>
       <c r="AT44" s="5" t="n"/>
-      <c r="AU44" s="2" t="n"/>
+      <c r="AU44" s="2" t="inlineStr"/>
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
@@ -8359,10 +8099,10 @@
       <c r="BD44" s="4" t="n"/>
       <c r="BE44" s="4" t="n"/>
       <c r="BF44" s="4" t="n"/>
-      <c r="BG44" s="2" t="n"/>
+      <c r="BG44" s="2" t="inlineStr"/>
       <c r="BH44" s="28" t="n"/>
       <c r="BI44" s="5" t="n"/>
-      <c r="BJ44" s="2" t="n"/>
+      <c r="BJ44" s="2" t="inlineStr"/>
       <c r="BK44" s="4" t="n"/>
       <c r="BL44" s="4" t="n"/>
       <c r="BM44" s="4" t="n"/>
@@ -8374,10 +8114,10 @@
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
       <c r="BU44" s="4" t="n"/>
-      <c r="BV44" s="2" t="n"/>
+      <c r="BV44" s="2" t="inlineStr"/>
       <c r="BW44" s="28" t="n"/>
       <c r="BX44" s="5" t="n"/>
-      <c r="BY44" s="2" t="n"/>
+      <c r="BY44" s="2" t="inlineStr"/>
       <c r="BZ44" s="4" t="n"/>
       <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
@@ -8389,22 +8129,12 @@
       <c r="CH44" s="4" t="n"/>
       <c r="CI44" s="4" t="n"/>
       <c r="CJ44" s="4" t="n"/>
-      <c r="CK44" s="2" t="n"/>
+      <c r="CK44" s="2" t="inlineStr"/>
       <c r="CL44" s="28" t="n"/>
-      <c r="CN44" s="2" t="n"/>
+      <c r="CN44" s="2" t="inlineStr"/>
       <c r="CP44" s="11" t="n"/>
       <c r="CQ44" s="7" t="n"/>
       <c r="CR44" s="12" t="n"/>
-      <c r="CS44" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU44" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8536,7 +8266,7 @@
         <v>99.8</v>
       </c>
       <c r="AZ45" s="4" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="BA45" s="4" t="n">
         <v>0</v>
@@ -8807,7 +8537,7 @@
         <v>96.7</v>
       </c>
       <c r="AZ46" s="4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="BA46" s="4" t="n">
         <v>0</v>
@@ -9235,7 +8965,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AZ48" s="4" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="BA48" s="4" t="n">
         <v>0</v>
@@ -9416,10 +9146,10 @@
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
-      <c r="AC49" s="2" t="n"/>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="28" t="n"/>
       <c r="AE49" s="5" t="n"/>
-      <c r="AF49" s="2" t="n"/>
+      <c r="AF49" s="2" t="inlineStr"/>
       <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
@@ -9431,10 +9161,10 @@
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
-      <c r="AR49" s="2" t="n"/>
+      <c r="AR49" s="2" t="inlineStr"/>
       <c r="AS49" s="28" t="n"/>
       <c r="AT49" s="5" t="n"/>
-      <c r="AU49" s="2" t="n"/>
+      <c r="AU49" s="2" t="inlineStr"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
@@ -9446,10 +9176,10 @@
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="2" t="n"/>
+      <c r="BG49" s="2" t="inlineStr"/>
       <c r="BH49" s="28" t="n"/>
       <c r="BI49" s="5" t="n"/>
-      <c r="BJ49" s="2" t="n"/>
+      <c r="BJ49" s="2" t="inlineStr"/>
       <c r="BK49" s="4" t="n"/>
       <c r="BL49" s="4" t="n"/>
       <c r="BM49" s="4" t="n"/>
@@ -9461,10 +9191,10 @@
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
       <c r="BU49" s="4" t="n"/>
-      <c r="BV49" s="2" t="n"/>
+      <c r="BV49" s="2" t="inlineStr"/>
       <c r="BW49" s="28" t="n"/>
       <c r="BX49" s="5" t="n"/>
-      <c r="BY49" s="2" t="n"/>
+      <c r="BY49" s="2" t="inlineStr"/>
       <c r="BZ49" s="4" t="n"/>
       <c r="CA49" s="4" t="n"/>
       <c r="CB49" s="4" t="n"/>
@@ -9476,22 +9206,12 @@
       <c r="CH49" s="4" t="n"/>
       <c r="CI49" s="4" t="n"/>
       <c r="CJ49" s="4" t="n"/>
-      <c r="CK49" s="2" t="n"/>
+      <c r="CK49" s="2" t="inlineStr"/>
       <c r="CL49" s="28" t="n"/>
-      <c r="CN49" s="2" t="n"/>
+      <c r="CN49" s="2" t="inlineStr"/>
       <c r="CP49" s="11" t="n"/>
       <c r="CQ49" s="7" t="n"/>
       <c r="CR49" s="12" t="n"/>
-      <c r="CS49" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU49" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9621,7 +9341,7 @@
         <v>97.7</v>
       </c>
       <c r="AZ50" s="4" t="n">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="BA50" s="4" t="n">
         <v>0</v>
@@ -9912,7 +9632,7 @@
         <v>100</v>
       </c>
       <c r="AZ51" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA51" s="4" t="n">
         <v>0</v>
@@ -10099,10 +9819,10 @@
       <c r="Z52" s="4" t="n"/>
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
-      <c r="AC52" s="2" t="n"/>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="28" t="n"/>
       <c r="AE52" s="5" t="n"/>
-      <c r="AF52" s="2" t="n"/>
+      <c r="AF52" s="2" t="inlineStr"/>
       <c r="AG52" s="4" t="n"/>
       <c r="AH52" s="4" t="n"/>
       <c r="AI52" s="4" t="n"/>
@@ -10114,10 +9834,10 @@
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
-      <c r="AR52" s="2" t="n"/>
+      <c r="AR52" s="2" t="inlineStr"/>
       <c r="AS52" s="28" t="n"/>
       <c r="AT52" s="5" t="n"/>
-      <c r="AU52" s="2" t="n"/>
+      <c r="AU52" s="2" t="inlineStr"/>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
@@ -10129,10 +9849,10 @@
       <c r="BD52" s="4" t="n"/>
       <c r="BE52" s="4" t="n"/>
       <c r="BF52" s="4" t="n"/>
-      <c r="BG52" s="2" t="n"/>
+      <c r="BG52" s="2" t="inlineStr"/>
       <c r="BH52" s="28" t="n"/>
       <c r="BI52" s="5" t="n"/>
-      <c r="BJ52" s="2" t="n"/>
+      <c r="BJ52" s="2" t="inlineStr"/>
       <c r="BK52" s="4" t="n"/>
       <c r="BL52" s="4" t="n"/>
       <c r="BM52" s="4" t="n"/>
@@ -10144,10 +9864,10 @@
       <c r="BS52" s="4" t="n"/>
       <c r="BT52" s="4" t="n"/>
       <c r="BU52" s="4" t="n"/>
-      <c r="BV52" s="2" t="n"/>
+      <c r="BV52" s="2" t="inlineStr"/>
       <c r="BW52" s="28" t="n"/>
       <c r="BX52" s="5" t="n"/>
-      <c r="BY52" s="2" t="n"/>
+      <c r="BY52" s="2" t="inlineStr"/>
       <c r="BZ52" s="4" t="n"/>
       <c r="CA52" s="4" t="n"/>
       <c r="CB52" s="4" t="n"/>
@@ -10159,22 +9879,12 @@
       <c r="CH52" s="4" t="n"/>
       <c r="CI52" s="4" t="n"/>
       <c r="CJ52" s="4" t="n"/>
-      <c r="CK52" s="2" t="n"/>
+      <c r="CK52" s="2" t="inlineStr"/>
       <c r="CL52" s="28" t="n"/>
-      <c r="CN52" s="2" t="n"/>
+      <c r="CN52" s="2" t="inlineStr"/>
       <c r="CP52" s="11" t="n"/>
       <c r="CQ52" s="7" t="n"/>
       <c r="CR52" s="12" t="n"/>
-      <c r="CS52" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU52" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,10 +9922,10 @@
       <c r="Z53" s="4" t="n"/>
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
-      <c r="AC53" s="2" t="n"/>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="28" t="n"/>
       <c r="AE53" s="5" t="n"/>
-      <c r="AF53" s="2" t="n"/>
+      <c r="AF53" s="2" t="inlineStr"/>
       <c r="AG53" s="4" t="n"/>
       <c r="AH53" s="4" t="n"/>
       <c r="AI53" s="4" t="n"/>
@@ -10227,10 +9937,10 @@
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
-      <c r="AR53" s="2" t="n"/>
+      <c r="AR53" s="2" t="inlineStr"/>
       <c r="AS53" s="28" t="n"/>
       <c r="AT53" s="5" t="n"/>
-      <c r="AU53" s="2" t="n"/>
+      <c r="AU53" s="2" t="inlineStr"/>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
@@ -10242,10 +9952,10 @@
       <c r="BD53" s="4" t="n"/>
       <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
-      <c r="BG53" s="2" t="n"/>
+      <c r="BG53" s="2" t="inlineStr"/>
       <c r="BH53" s="28" t="n"/>
       <c r="BI53" s="5" t="n"/>
-      <c r="BJ53" s="2" t="n"/>
+      <c r="BJ53" s="2" t="inlineStr"/>
       <c r="BK53" s="4" t="n"/>
       <c r="BL53" s="4" t="n"/>
       <c r="BM53" s="4" t="n"/>
@@ -10257,10 +9967,10 @@
       <c r="BS53" s="4" t="n"/>
       <c r="BT53" s="4" t="n"/>
       <c r="BU53" s="4" t="n"/>
-      <c r="BV53" s="2" t="n"/>
+      <c r="BV53" s="2" t="inlineStr"/>
       <c r="BW53" s="28" t="n"/>
       <c r="BX53" s="5" t="n"/>
-      <c r="BY53" s="2" t="n"/>
+      <c r="BY53" s="2" t="inlineStr"/>
       <c r="BZ53" s="4" t="n"/>
       <c r="CA53" s="4" t="n"/>
       <c r="CB53" s="4" t="n"/>
@@ -10272,22 +9982,12 @@
       <c r="CH53" s="4" t="n"/>
       <c r="CI53" s="4" t="n"/>
       <c r="CJ53" s="4" t="n"/>
-      <c r="CK53" s="2" t="n"/>
+      <c r="CK53" s="2" t="inlineStr"/>
       <c r="CL53" s="28" t="n"/>
-      <c r="CN53" s="2" t="n"/>
+      <c r="CN53" s="2" t="inlineStr"/>
       <c r="CP53" s="11" t="n"/>
       <c r="CQ53" s="7" t="n"/>
       <c r="CR53" s="12" t="n"/>
-      <c r="CS53" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU53" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10325,10 +10025,10 @@
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
-      <c r="AC54" s="2" t="n"/>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="28" t="n"/>
       <c r="AE54" s="5" t="n"/>
-      <c r="AF54" s="2" t="n"/>
+      <c r="AF54" s="2" t="inlineStr"/>
       <c r="AG54" s="4" t="n"/>
       <c r="AH54" s="4" t="n"/>
       <c r="AI54" s="4" t="n"/>
@@ -10340,10 +10040,10 @@
       <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
-      <c r="AR54" s="2" t="n"/>
+      <c r="AR54" s="2" t="inlineStr"/>
       <c r="AS54" s="28" t="n"/>
       <c r="AT54" s="5" t="n"/>
-      <c r="AU54" s="2" t="n"/>
+      <c r="AU54" s="2" t="inlineStr"/>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
@@ -10355,10 +10055,10 @@
       <c r="BD54" s="4" t="n"/>
       <c r="BE54" s="4" t="n"/>
       <c r="BF54" s="4" t="n"/>
-      <c r="BG54" s="2" t="n"/>
+      <c r="BG54" s="2" t="inlineStr"/>
       <c r="BH54" s="28" t="n"/>
       <c r="BI54" s="5" t="n"/>
-      <c r="BJ54" s="2" t="n"/>
+      <c r="BJ54" s="2" t="inlineStr"/>
       <c r="BK54" s="4" t="n"/>
       <c r="BL54" s="4" t="n"/>
       <c r="BM54" s="4" t="n"/>
@@ -10370,10 +10070,10 @@
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
       <c r="BU54" s="4" t="n"/>
-      <c r="BV54" s="2" t="n"/>
+      <c r="BV54" s="2" t="inlineStr"/>
       <c r="BW54" s="28" t="n"/>
       <c r="BX54" s="5" t="n"/>
-      <c r="BY54" s="2" t="n"/>
+      <c r="BY54" s="2" t="inlineStr"/>
       <c r="BZ54" s="4" t="n"/>
       <c r="CA54" s="4" t="n"/>
       <c r="CB54" s="4" t="n"/>
@@ -10385,22 +10085,12 @@
       <c r="CH54" s="4" t="n"/>
       <c r="CI54" s="4" t="n"/>
       <c r="CJ54" s="4" t="n"/>
-      <c r="CK54" s="2" t="n"/>
+      <c r="CK54" s="2" t="inlineStr"/>
       <c r="CL54" s="28" t="n"/>
-      <c r="CN54" s="2" t="n"/>
+      <c r="CN54" s="2" t="inlineStr"/>
       <c r="CP54" s="11" t="n"/>
       <c r="CQ54" s="7" t="n"/>
       <c r="CR54" s="12" t="n"/>
-      <c r="CS54" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU54" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10438,10 +10128,10 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="2" t="n"/>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="28" t="n"/>
       <c r="AE55" s="5" t="n"/>
-      <c r="AF55" s="2" t="n"/>
+      <c r="AF55" s="2" t="inlineStr"/>
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
@@ -10453,10 +10143,10 @@
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
-      <c r="AR55" s="2" t="n"/>
+      <c r="AR55" s="2" t="inlineStr"/>
       <c r="AS55" s="28" t="n"/>
       <c r="AT55" s="5" t="n"/>
-      <c r="AU55" s="2" t="n"/>
+      <c r="AU55" s="2" t="inlineStr"/>
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
       <c r="AX55" s="4" t="n"/>
@@ -10468,10 +10158,10 @@
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
-      <c r="BG55" s="2" t="n"/>
+      <c r="BG55" s="2" t="inlineStr"/>
       <c r="BH55" s="28" t="n"/>
       <c r="BI55" s="5" t="n"/>
-      <c r="BJ55" s="2" t="n"/>
+      <c r="BJ55" s="2" t="inlineStr"/>
       <c r="BK55" s="4" t="n"/>
       <c r="BL55" s="4" t="n"/>
       <c r="BM55" s="4" t="n"/>
@@ -10483,10 +10173,10 @@
       <c r="BS55" s="4" t="n"/>
       <c r="BT55" s="4" t="n"/>
       <c r="BU55" s="4" t="n"/>
-      <c r="BV55" s="2" t="n"/>
+      <c r="BV55" s="2" t="inlineStr"/>
       <c r="BW55" s="28" t="n"/>
       <c r="BX55" s="5" t="n"/>
-      <c r="BY55" s="2" t="n"/>
+      <c r="BY55" s="2" t="inlineStr"/>
       <c r="BZ55" s="4" t="n"/>
       <c r="CA55" s="4" t="n"/>
       <c r="CB55" s="4" t="n"/>
@@ -10498,22 +10188,12 @@
       <c r="CH55" s="4" t="n"/>
       <c r="CI55" s="4" t="n"/>
       <c r="CJ55" s="4" t="n"/>
-      <c r="CK55" s="2" t="n"/>
+      <c r="CK55" s="2" t="inlineStr"/>
       <c r="CL55" s="28" t="n"/>
-      <c r="CN55" s="2" t="n"/>
+      <c r="CN55" s="2" t="inlineStr"/>
       <c r="CP55" s="11" t="n"/>
       <c r="CQ55" s="7" t="n"/>
       <c r="CR55" s="12" t="n"/>
-      <c r="CS55" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU55" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10667,7 +10347,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AZ56" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="BA56" s="4" t="n">
         <v>0</v>
@@ -10854,10 +10534,10 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="2" t="n"/>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="28" t="n"/>
       <c r="AE57" s="5" t="n"/>
-      <c r="AF57" s="2" t="n"/>
+      <c r="AF57" s="2" t="inlineStr"/>
       <c r="AG57" s="4" t="n"/>
       <c r="AH57" s="4" t="n"/>
       <c r="AI57" s="4" t="n"/>
@@ -10869,10 +10549,10 @@
       <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
-      <c r="AR57" s="2" t="n"/>
+      <c r="AR57" s="2" t="inlineStr"/>
       <c r="AS57" s="28" t="n"/>
       <c r="AT57" s="5" t="n"/>
-      <c r="AU57" s="2" t="n"/>
+      <c r="AU57" s="2" t="inlineStr"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
@@ -10884,10 +10564,10 @@
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
       <c r="BF57" s="4" t="n"/>
-      <c r="BG57" s="2" t="n"/>
+      <c r="BG57" s="2" t="inlineStr"/>
       <c r="BH57" s="28" t="n"/>
       <c r="BI57" s="5" t="n"/>
-      <c r="BJ57" s="2" t="n"/>
+      <c r="BJ57" s="2" t="inlineStr"/>
       <c r="BK57" s="4" t="n"/>
       <c r="BL57" s="4" t="n"/>
       <c r="BM57" s="4" t="n"/>
@@ -10899,10 +10579,10 @@
       <c r="BS57" s="4" t="n"/>
       <c r="BT57" s="4" t="n"/>
       <c r="BU57" s="4" t="n"/>
-      <c r="BV57" s="2" t="n"/>
+      <c r="BV57" s="2" t="inlineStr"/>
       <c r="BW57" s="28" t="n"/>
       <c r="BX57" s="5" t="n"/>
-      <c r="BY57" s="2" t="n"/>
+      <c r="BY57" s="2" t="inlineStr"/>
       <c r="BZ57" s="4" t="n"/>
       <c r="CA57" s="4" t="n"/>
       <c r="CB57" s="4" t="n"/>
@@ -10914,22 +10594,12 @@
       <c r="CH57" s="4" t="n"/>
       <c r="CI57" s="4" t="n"/>
       <c r="CJ57" s="4" t="n"/>
-      <c r="CK57" s="2" t="n"/>
+      <c r="CK57" s="2" t="inlineStr"/>
       <c r="CL57" s="28" t="n"/>
-      <c r="CN57" s="2" t="n"/>
+      <c r="CN57" s="2" t="inlineStr"/>
       <c r="CP57" s="11" t="n"/>
       <c r="CQ57" s="7" t="n"/>
       <c r="CR57" s="12" t="n"/>
-      <c r="CS57" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU57" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10966,10 +10636,10 @@
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
-      <c r="AC58" s="2" t="n"/>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="28" t="n"/>
       <c r="AE58" s="5" t="n"/>
-      <c r="AF58" s="2" t="n"/>
+      <c r="AF58" s="2" t="inlineStr"/>
       <c r="AG58" s="4" t="n"/>
       <c r="AH58" s="4" t="n"/>
       <c r="AI58" s="4" t="n"/>
@@ -10981,10 +10651,10 @@
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
-      <c r="AR58" s="2" t="n"/>
+      <c r="AR58" s="2" t="inlineStr"/>
       <c r="AS58" s="28" t="n"/>
       <c r="AT58" s="5" t="n"/>
-      <c r="AU58" s="2" t="n"/>
+      <c r="AU58" s="2" t="inlineStr"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
@@ -10996,10 +10666,10 @@
       <c r="BD58" s="4" t="n"/>
       <c r="BE58" s="4" t="n"/>
       <c r="BF58" s="4" t="n"/>
-      <c r="BG58" s="2" t="n"/>
+      <c r="BG58" s="2" t="inlineStr"/>
       <c r="BH58" s="28" t="n"/>
       <c r="BI58" s="5" t="n"/>
-      <c r="BJ58" s="2" t="n"/>
+      <c r="BJ58" s="2" t="inlineStr"/>
       <c r="BK58" s="4" t="n"/>
       <c r="BL58" s="4" t="n"/>
       <c r="BM58" s="4" t="n"/>
@@ -11011,10 +10681,10 @@
       <c r="BS58" s="4" t="n"/>
       <c r="BT58" s="4" t="n"/>
       <c r="BU58" s="4" t="n"/>
-      <c r="BV58" s="2" t="n"/>
+      <c r="BV58" s="2" t="inlineStr"/>
       <c r="BW58" s="28" t="n"/>
       <c r="BX58" s="5" t="n"/>
-      <c r="BY58" s="2" t="n"/>
+      <c r="BY58" s="2" t="inlineStr"/>
       <c r="BZ58" s="4" t="n"/>
       <c r="CA58" s="4" t="n"/>
       <c r="CB58" s="4" t="n"/>
@@ -11026,22 +10696,12 @@
       <c r="CH58" s="4" t="n"/>
       <c r="CI58" s="4" t="n"/>
       <c r="CJ58" s="4" t="n"/>
-      <c r="CK58" s="2" t="n"/>
+      <c r="CK58" s="2" t="inlineStr"/>
       <c r="CL58" s="28" t="n"/>
-      <c r="CN58" s="2" t="n"/>
+      <c r="CN58" s="2" t="inlineStr"/>
       <c r="CP58" s="11" t="n"/>
       <c r="CQ58" s="7" t="n"/>
       <c r="CR58" s="12" t="n"/>
-      <c r="CS58" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU58" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11154,7 +10814,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AZ59" s="4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="BA59" s="4" t="n">
         <v>0</v>
@@ -11342,10 +11002,10 @@
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
-      <c r="AC60" s="2" t="n"/>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="28" t="n"/>
       <c r="AE60" s="5" t="n"/>
-      <c r="AF60" s="2" t="n"/>
+      <c r="AF60" s="2" t="inlineStr"/>
       <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
       <c r="AI60" s="4" t="n"/>
@@ -11357,10 +11017,10 @@
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
-      <c r="AR60" s="2" t="n"/>
+      <c r="AR60" s="2" t="inlineStr"/>
       <c r="AS60" s="28" t="n"/>
       <c r="AT60" s="5" t="n"/>
-      <c r="AU60" s="2" t="n"/>
+      <c r="AU60" s="2" t="inlineStr"/>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
@@ -11372,10 +11032,10 @@
       <c r="BD60" s="4" t="n"/>
       <c r="BE60" s="4" t="n"/>
       <c r="BF60" s="4" t="n"/>
-      <c r="BG60" s="2" t="n"/>
+      <c r="BG60" s="2" t="inlineStr"/>
       <c r="BH60" s="28" t="n"/>
       <c r="BI60" s="5" t="n"/>
-      <c r="BJ60" s="2" t="n"/>
+      <c r="BJ60" s="2" t="inlineStr"/>
       <c r="BK60" s="4" t="n"/>
       <c r="BL60" s="4" t="n"/>
       <c r="BM60" s="4" t="n"/>
@@ -11387,10 +11047,10 @@
       <c r="BS60" s="4" t="n"/>
       <c r="BT60" s="4" t="n"/>
       <c r="BU60" s="4" t="n"/>
-      <c r="BV60" s="2" t="n"/>
+      <c r="BV60" s="2" t="inlineStr"/>
       <c r="BW60" s="28" t="n"/>
       <c r="BX60" s="5" t="n"/>
-      <c r="BY60" s="2" t="n"/>
+      <c r="BY60" s="2" t="inlineStr"/>
       <c r="BZ60" s="4" t="n"/>
       <c r="CA60" s="4" t="n"/>
       <c r="CB60" s="4" t="n"/>
@@ -11402,23 +11062,13 @@
       <c r="CH60" s="4" t="n"/>
       <c r="CI60" s="4" t="n"/>
       <c r="CJ60" s="4" t="n"/>
-      <c r="CK60" s="2" t="n"/>
+      <c r="CK60" s="2" t="inlineStr"/>
       <c r="CL60" s="28" t="n"/>
       <c r="CM60" s="5" t="n"/>
-      <c r="CN60" s="2" t="n"/>
+      <c r="CN60" s="2" t="inlineStr"/>
       <c r="CP60" s="11" t="n"/>
       <c r="CQ60" s="7" t="n"/>
       <c r="CR60" s="12" t="n"/>
-      <c r="CS60" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU60" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11769,7 +11419,7 @@
         <v>100</v>
       </c>
       <c r="AZ62" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA62" s="4" t="n">
         <v>1</v>
@@ -11960,10 +11610,10 @@
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
-      <c r="AC63" s="2" t="n"/>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="28" t="n"/>
       <c r="AE63" s="29" t="n"/>
-      <c r="AF63" s="2" t="n"/>
+      <c r="AF63" s="2" t="inlineStr"/>
       <c r="AG63" s="4" t="n"/>
       <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="n"/>
@@ -11975,10 +11625,10 @@
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
-      <c r="AR63" s="2" t="n"/>
+      <c r="AR63" s="2" t="inlineStr"/>
       <c r="AS63" s="28" t="n"/>
       <c r="AT63" s="29" t="n"/>
-      <c r="AU63" s="2" t="n"/>
+      <c r="AU63" s="2" t="inlineStr"/>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
@@ -11990,10 +11640,10 @@
       <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="n"/>
       <c r="BF63" s="4" t="n"/>
-      <c r="BG63" s="2" t="n"/>
+      <c r="BG63" s="2" t="inlineStr"/>
       <c r="BH63" s="28" t="n"/>
       <c r="BI63" s="29" t="n"/>
-      <c r="BJ63" s="2" t="n"/>
+      <c r="BJ63" s="2" t="inlineStr"/>
       <c r="BK63" s="4" t="n"/>
       <c r="BL63" s="4" t="n"/>
       <c r="BM63" s="4" t="n"/>
@@ -12005,10 +11655,10 @@
       <c r="BS63" s="4" t="n"/>
       <c r="BT63" s="4" t="n"/>
       <c r="BU63" s="4" t="n"/>
-      <c r="BV63" s="2" t="n"/>
+      <c r="BV63" s="2" t="inlineStr"/>
       <c r="BW63" s="28" t="n"/>
       <c r="BX63" s="29" t="n"/>
-      <c r="BY63" s="2" t="n"/>
+      <c r="BY63" s="2" t="inlineStr"/>
       <c r="BZ63" s="4" t="n"/>
       <c r="CA63" s="4" t="n"/>
       <c r="CB63" s="4" t="n"/>
@@ -12020,24 +11670,14 @@
       <c r="CH63" s="4" t="n"/>
       <c r="CI63" s="4" t="n"/>
       <c r="CJ63" s="4" t="n"/>
-      <c r="CK63" s="2" t="n"/>
+      <c r="CK63" s="2" t="inlineStr"/>
       <c r="CL63" s="28" t="n"/>
       <c r="CM63" s="31" t="n"/>
-      <c r="CN63" s="2" t="n"/>
+      <c r="CN63" s="2" t="inlineStr"/>
       <c r="CO63" s="13" t="n"/>
       <c r="CP63" s="14" t="n"/>
       <c r="CQ63" s="15" t="n"/>
       <c r="CR63" s="16" t="n"/>
-      <c r="CS63" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU63" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12076,10 +11716,10 @@
       <c r="Z64" s="4" t="n"/>
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
-      <c r="AC64" s="2" t="n"/>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="28" t="n"/>
       <c r="AE64" s="5" t="n"/>
-      <c r="AF64" s="2" t="n"/>
+      <c r="AF64" s="2" t="inlineStr"/>
       <c r="AG64" s="4" t="n"/>
       <c r="AH64" s="4" t="n"/>
       <c r="AI64" s="4" t="n"/>
@@ -12091,10 +11731,10 @@
       <c r="AO64" s="4" t="n"/>
       <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="2" t="n"/>
+      <c r="AR64" s="2" t="inlineStr"/>
       <c r="AS64" s="28" t="n"/>
       <c r="AT64" s="5" t="n"/>
-      <c r="AU64" s="2" t="n"/>
+      <c r="AU64" s="2" t="inlineStr"/>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
@@ -12106,10 +11746,10 @@
       <c r="BD64" s="4" t="n"/>
       <c r="BE64" s="4" t="n"/>
       <c r="BF64" s="4" t="n"/>
-      <c r="BG64" s="2" t="n"/>
+      <c r="BG64" s="2" t="inlineStr"/>
       <c r="BH64" s="28" t="n"/>
       <c r="BI64" s="5" t="n"/>
-      <c r="BJ64" s="2" t="n"/>
+      <c r="BJ64" s="2" t="inlineStr"/>
       <c r="BK64" s="4" t="n"/>
       <c r="BL64" s="4" t="n"/>
       <c r="BM64" s="4" t="n"/>
@@ -12121,10 +11761,10 @@
       <c r="BS64" s="4" t="n"/>
       <c r="BT64" s="4" t="n"/>
       <c r="BU64" s="4" t="n"/>
-      <c r="BV64" s="2" t="n"/>
+      <c r="BV64" s="2" t="inlineStr"/>
       <c r="BW64" s="28" t="n"/>
       <c r="BX64" s="5" t="n"/>
-      <c r="BY64" s="2" t="n"/>
+      <c r="BY64" s="2" t="inlineStr"/>
       <c r="BZ64" s="4" t="n"/>
       <c r="CA64" s="4" t="n"/>
       <c r="CB64" s="4" t="n"/>
@@ -12136,23 +11776,13 @@
       <c r="CH64" s="4" t="n"/>
       <c r="CI64" s="4" t="n"/>
       <c r="CJ64" s="4" t="n"/>
-      <c r="CK64" s="2" t="n"/>
+      <c r="CK64" s="2" t="inlineStr"/>
       <c r="CL64" s="28" t="n"/>
       <c r="CM64" s="5" t="n"/>
-      <c r="CN64" s="2" t="n"/>
+      <c r="CN64" s="2" t="inlineStr"/>
       <c r="CP64" s="11" t="n"/>
       <c r="CQ64" s="7" t="n"/>
       <c r="CR64" s="12" t="n"/>
-      <c r="CS64" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU64" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12190,10 +11820,10 @@
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="2" t="n"/>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="28" t="n"/>
       <c r="AE65" s="5" t="n"/>
-      <c r="AF65" s="2" t="n"/>
+      <c r="AF65" s="2" t="inlineStr"/>
       <c r="AG65" s="4" t="n"/>
       <c r="AH65" s="4" t="n"/>
       <c r="AI65" s="4" t="n"/>
@@ -12205,10 +11835,10 @@
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
-      <c r="AR65" s="2" t="n"/>
+      <c r="AR65" s="2" t="inlineStr"/>
       <c r="AS65" s="28" t="n"/>
       <c r="AT65" s="5" t="n"/>
-      <c r="AU65" s="2" t="n"/>
+      <c r="AU65" s="2" t="inlineStr"/>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
@@ -12220,10 +11850,10 @@
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
-      <c r="BG65" s="2" t="n"/>
+      <c r="BG65" s="2" t="inlineStr"/>
       <c r="BH65" s="28" t="n"/>
       <c r="BI65" s="5" t="n"/>
-      <c r="BJ65" s="2" t="n"/>
+      <c r="BJ65" s="2" t="inlineStr"/>
       <c r="BK65" s="4" t="n"/>
       <c r="BL65" s="4" t="n"/>
       <c r="BM65" s="4" t="n"/>
@@ -12235,10 +11865,10 @@
       <c r="BS65" s="4" t="n"/>
       <c r="BT65" s="4" t="n"/>
       <c r="BU65" s="4" t="n"/>
-      <c r="BV65" s="2" t="n"/>
+      <c r="BV65" s="2" t="inlineStr"/>
       <c r="BW65" s="28" t="n"/>
       <c r="BX65" s="5" t="n"/>
-      <c r="BY65" s="2" t="n"/>
+      <c r="BY65" s="2" t="inlineStr"/>
       <c r="BZ65" s="4" t="n"/>
       <c r="CA65" s="4" t="n"/>
       <c r="CB65" s="4" t="n"/>
@@ -12250,22 +11880,12 @@
       <c r="CH65" s="4" t="n"/>
       <c r="CI65" s="4" t="n"/>
       <c r="CJ65" s="4" t="n"/>
-      <c r="CK65" s="2" t="n"/>
+      <c r="CK65" s="2" t="inlineStr"/>
       <c r="CL65" s="28" t="n"/>
-      <c r="CN65" s="2" t="n"/>
+      <c r="CN65" s="2" t="inlineStr"/>
       <c r="CP65" s="11" t="n"/>
       <c r="CQ65" s="7" t="n"/>
       <c r="CR65" s="12" t="n"/>
-      <c r="CS65" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU65" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12393,7 +12013,7 @@
         <v>96.3</v>
       </c>
       <c r="AZ66" s="4" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="BA66" s="4" t="n">
         <v>0</v>
@@ -12554,10 +12174,10 @@
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
-      <c r="AC67" s="2" t="n"/>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="28" t="n"/>
       <c r="AE67" s="5" t="n"/>
-      <c r="AF67" s="2" t="n"/>
+      <c r="AF67" s="2" t="inlineStr"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="n"/>
@@ -12569,10 +12189,10 @@
       <c r="AO67" s="4" t="n"/>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
-      <c r="AR67" s="2" t="n"/>
+      <c r="AR67" s="2" t="inlineStr"/>
       <c r="AS67" s="28" t="n"/>
       <c r="AT67" s="5" t="n"/>
-      <c r="AU67" s="2" t="n"/>
+      <c r="AU67" s="2" t="inlineStr"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
@@ -12584,10 +12204,10 @@
       <c r="BD67" s="4" t="n"/>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="n"/>
-      <c r="BG67" s="2" t="n"/>
+      <c r="BG67" s="2" t="inlineStr"/>
       <c r="BH67" s="28" t="n"/>
       <c r="BI67" s="5" t="n"/>
-      <c r="BJ67" s="2" t="n"/>
+      <c r="BJ67" s="2" t="inlineStr"/>
       <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
@@ -12599,10 +12219,10 @@
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
       <c r="BU67" s="4" t="n"/>
-      <c r="BV67" s="2" t="n"/>
+      <c r="BV67" s="2" t="inlineStr"/>
       <c r="BW67" s="28" t="n"/>
       <c r="BX67" s="5" t="n"/>
-      <c r="BY67" s="2" t="n"/>
+      <c r="BY67" s="2" t="inlineStr"/>
       <c r="BZ67" s="4" t="n"/>
       <c r="CA67" s="4" t="n"/>
       <c r="CB67" s="4" t="n"/>
@@ -12614,23 +12234,13 @@
       <c r="CH67" s="4" t="n"/>
       <c r="CI67" s="4" t="n"/>
       <c r="CJ67" s="4" t="n"/>
-      <c r="CK67" s="2" t="n"/>
+      <c r="CK67" s="2" t="inlineStr"/>
       <c r="CL67" s="28" t="n"/>
       <c r="CM67" s="5" t="n"/>
-      <c r="CN67" s="2" t="n"/>
+      <c r="CN67" s="2" t="inlineStr"/>
       <c r="CP67" s="11" t="n"/>
       <c r="CQ67" s="7" t="n"/>
       <c r="CR67" s="12" t="n"/>
-      <c r="CS67" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU67" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12782,7 +12392,7 @@
         <v>92.8</v>
       </c>
       <c r="AZ68" s="4" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="BA68" s="4" t="n">
         <v>0</v>
@@ -12969,10 +12579,10 @@
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
-      <c r="AC69" s="2" t="n"/>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="28" t="n"/>
       <c r="AE69" s="5" t="n"/>
-      <c r="AF69" s="2" t="n"/>
+      <c r="AF69" s="2" t="inlineStr"/>
       <c r="AG69" s="4" t="n"/>
       <c r="AH69" s="4" t="n"/>
       <c r="AI69" s="4" t="n"/>
@@ -12984,10 +12594,10 @@
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="2" t="n"/>
+      <c r="AR69" s="2" t="inlineStr"/>
       <c r="AS69" s="28" t="n"/>
       <c r="AT69" s="5" t="n"/>
-      <c r="AU69" s="2" t="n"/>
+      <c r="AU69" s="2" t="inlineStr"/>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
@@ -12999,10 +12609,10 @@
       <c r="BD69" s="4" t="n"/>
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
-      <c r="BG69" s="2" t="n"/>
+      <c r="BG69" s="2" t="inlineStr"/>
       <c r="BH69" s="28" t="n"/>
       <c r="BI69" s="5" t="n"/>
-      <c r="BJ69" s="2" t="n"/>
+      <c r="BJ69" s="2" t="inlineStr"/>
       <c r="BK69" s="4" t="n"/>
       <c r="BL69" s="4" t="n"/>
       <c r="BM69" s="4" t="n"/>
@@ -13014,10 +12624,10 @@
       <c r="BS69" s="4" t="n"/>
       <c r="BT69" s="4" t="n"/>
       <c r="BU69" s="4" t="n"/>
-      <c r="BV69" s="2" t="n"/>
+      <c r="BV69" s="2" t="inlineStr"/>
       <c r="BW69" s="28" t="n"/>
       <c r="BX69" s="5" t="n"/>
-      <c r="BY69" s="2" t="n"/>
+      <c r="BY69" s="2" t="inlineStr"/>
       <c r="BZ69" s="4" t="n"/>
       <c r="CA69" s="4" t="n"/>
       <c r="CB69" s="4" t="n"/>
@@ -13029,22 +12639,12 @@
       <c r="CH69" s="4" t="n"/>
       <c r="CI69" s="4" t="n"/>
       <c r="CJ69" s="4" t="n"/>
-      <c r="CK69" s="2" t="n"/>
+      <c r="CK69" s="2" t="inlineStr"/>
       <c r="CL69" s="28" t="n"/>
-      <c r="CN69" s="2" t="n"/>
+      <c r="CN69" s="2" t="inlineStr"/>
       <c r="CP69" s="11" t="n"/>
       <c r="CQ69" s="7" t="n"/>
       <c r="CR69" s="12" t="n"/>
-      <c r="CS69" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU69" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13158,7 +12758,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AZ70" s="4" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="BA70" s="4" t="n">
         <v>0</v>
@@ -13462,7 +13062,7 @@
         <v>99.8</v>
       </c>
       <c r="AZ71" s="4" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="BA71" s="4" t="n">
         <v>0</v>
@@ -13740,7 +13340,7 @@
         <v>90.7</v>
       </c>
       <c r="AZ72" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="BA72" s="4" t="n">
         <v>0</v>
@@ -14032,7 +13632,7 @@
         <v>99.8</v>
       </c>
       <c r="AZ73" s="4" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="BA73" s="4" t="n">
         <v>0</v>
@@ -14221,10 +13821,10 @@
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="2" t="n"/>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="28" t="n"/>
       <c r="AE74" s="5" t="n"/>
-      <c r="AF74" s="2" t="n"/>
+      <c r="AF74" s="2" t="inlineStr"/>
       <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n"/>
       <c r="AI74" s="4" t="n"/>
@@ -14236,10 +13836,10 @@
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
-      <c r="AR74" s="2" t="n"/>
+      <c r="AR74" s="2" t="inlineStr"/>
       <c r="AS74" s="28" t="n"/>
       <c r="AT74" s="5" t="n"/>
-      <c r="AU74" s="2" t="n"/>
+      <c r="AU74" s="2" t="inlineStr"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
@@ -14251,10 +13851,10 @@
       <c r="BD74" s="4" t="n"/>
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
-      <c r="BG74" s="2" t="n"/>
+      <c r="BG74" s="2" t="inlineStr"/>
       <c r="BH74" s="28" t="n"/>
       <c r="BI74" s="5" t="n"/>
-      <c r="BJ74" s="2" t="n"/>
+      <c r="BJ74" s="2" t="inlineStr"/>
       <c r="BK74" s="4" t="n"/>
       <c r="BL74" s="4" t="n"/>
       <c r="BM74" s="4" t="n"/>
@@ -14266,10 +13866,10 @@
       <c r="BS74" s="4" t="n"/>
       <c r="BT74" s="4" t="n"/>
       <c r="BU74" s="4" t="n"/>
-      <c r="BV74" s="2" t="n"/>
+      <c r="BV74" s="2" t="inlineStr"/>
       <c r="BW74" s="28" t="n"/>
       <c r="BX74" s="5" t="n"/>
-      <c r="BY74" s="2" t="n"/>
+      <c r="BY74" s="2" t="inlineStr"/>
       <c r="BZ74" s="4" t="n"/>
       <c r="CA74" s="4" t="n"/>
       <c r="CB74" s="4" t="n"/>
@@ -14281,22 +13881,12 @@
       <c r="CH74" s="4" t="n"/>
       <c r="CI74" s="4" t="n"/>
       <c r="CJ74" s="4" t="n"/>
-      <c r="CK74" s="2" t="n"/>
+      <c r="CK74" s="2" t="inlineStr"/>
       <c r="CL74" s="28" t="n"/>
-      <c r="CN74" s="2" t="n"/>
+      <c r="CN74" s="2" t="inlineStr"/>
       <c r="CP74" s="11" t="n"/>
       <c r="CQ74" s="7" t="n"/>
       <c r="CR74" s="12" t="n"/>
-      <c r="CS74" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU74" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14448,7 +14038,7 @@
         <v>86</v>
       </c>
       <c r="AZ75" s="4" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="BA75" s="4" t="n">
         <v>0</v>
@@ -14607,10 +14197,10 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="2" t="n"/>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="28" t="n"/>
       <c r="AE76" s="5" t="n"/>
-      <c r="AF76" s="2" t="n"/>
+      <c r="AF76" s="2" t="inlineStr"/>
       <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
@@ -14622,10 +14212,10 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="2" t="n"/>
+      <c r="AR76" s="2" t="inlineStr"/>
       <c r="AS76" s="28" t="n"/>
       <c r="AT76" s="5" t="n"/>
-      <c r="AU76" s="2" t="n"/>
+      <c r="AU76" s="2" t="inlineStr"/>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
@@ -14637,10 +14227,10 @@
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
-      <c r="BG76" s="2" t="n"/>
+      <c r="BG76" s="2" t="inlineStr"/>
       <c r="BH76" s="28" t="n"/>
       <c r="BI76" s="5" t="n"/>
-      <c r="BJ76" s="2" t="n"/>
+      <c r="BJ76" s="2" t="inlineStr"/>
       <c r="BK76" s="4" t="n"/>
       <c r="BL76" s="4" t="n"/>
       <c r="BM76" s="4" t="n"/>
@@ -14652,10 +14242,10 @@
       <c r="BS76" s="4" t="n"/>
       <c r="BT76" s="4" t="n"/>
       <c r="BU76" s="4" t="n"/>
-      <c r="BV76" s="2" t="n"/>
+      <c r="BV76" s="2" t="inlineStr"/>
       <c r="BW76" s="28" t="n"/>
       <c r="BX76" s="5" t="n"/>
-      <c r="BY76" s="2" t="n"/>
+      <c r="BY76" s="2" t="inlineStr"/>
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="n"/>
@@ -14667,22 +14257,12 @@
       <c r="CH76" s="4" t="n"/>
       <c r="CI76" s="4" t="n"/>
       <c r="CJ76" s="4" t="n"/>
-      <c r="CK76" s="2" t="n"/>
+      <c r="CK76" s="2" t="inlineStr"/>
       <c r="CL76" s="28" t="n"/>
-      <c r="CN76" s="2" t="n"/>
+      <c r="CN76" s="2" t="inlineStr"/>
       <c r="CP76" s="11" t="n"/>
       <c r="CQ76" s="7" t="n"/>
       <c r="CR76" s="12" t="n"/>
-      <c r="CS76" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU76" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14720,10 +14300,10 @@
       <c r="Z77" s="4" t="n"/>
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="2" t="n"/>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="28" t="n"/>
       <c r="AE77" s="5" t="n"/>
-      <c r="AF77" s="2" t="n"/>
+      <c r="AF77" s="2" t="inlineStr"/>
       <c r="AG77" s="4" t="n"/>
       <c r="AH77" s="4" t="n"/>
       <c r="AI77" s="4" t="n"/>
@@ -14735,10 +14315,10 @@
       <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
-      <c r="AR77" s="2" t="n"/>
+      <c r="AR77" s="2" t="inlineStr"/>
       <c r="AS77" s="28" t="n"/>
       <c r="AT77" s="5" t="n"/>
-      <c r="AU77" s="2" t="n"/>
+      <c r="AU77" s="2" t="inlineStr"/>
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
@@ -14750,10 +14330,10 @@
       <c r="BD77" s="4" t="n"/>
       <c r="BE77" s="4" t="n"/>
       <c r="BF77" s="4" t="n"/>
-      <c r="BG77" s="2" t="n"/>
+      <c r="BG77" s="2" t="inlineStr"/>
       <c r="BH77" s="28" t="n"/>
       <c r="BI77" s="5" t="n"/>
-      <c r="BJ77" s="2" t="n"/>
+      <c r="BJ77" s="2" t="inlineStr"/>
       <c r="BK77" s="4" t="n"/>
       <c r="BL77" s="4" t="n"/>
       <c r="BM77" s="4" t="n"/>
@@ -14765,10 +14345,10 @@
       <c r="BS77" s="4" t="n"/>
       <c r="BT77" s="4" t="n"/>
       <c r="BU77" s="4" t="n"/>
-      <c r="BV77" s="2" t="n"/>
+      <c r="BV77" s="2" t="inlineStr"/>
       <c r="BW77" s="28" t="n"/>
       <c r="BX77" s="5" t="n"/>
-      <c r="BY77" s="2" t="n"/>
+      <c r="BY77" s="2" t="inlineStr"/>
       <c r="BZ77" s="4" t="n"/>
       <c r="CA77" s="4" t="n"/>
       <c r="CB77" s="4" t="n"/>
@@ -14780,23 +14360,13 @@
       <c r="CH77" s="4" t="n"/>
       <c r="CI77" s="4" t="n"/>
       <c r="CJ77" s="4" t="n"/>
-      <c r="CK77" s="2" t="n"/>
+      <c r="CK77" s="2" t="inlineStr"/>
       <c r="CL77" s="28" t="n"/>
       <c r="CM77" s="5" t="n"/>
-      <c r="CN77" s="2" t="n"/>
+      <c r="CN77" s="2" t="inlineStr"/>
       <c r="CP77" s="11" t="n"/>
       <c r="CQ77" s="7" t="n"/>
       <c r="CR77" s="12" t="n"/>
-      <c r="CS77" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU77" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14948,7 +14518,7 @@
         <v>99.5</v>
       </c>
       <c r="AZ78" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA78" s="4" t="n">
         <v>0</v>
@@ -15252,7 +14822,7 @@
         <v>99.3</v>
       </c>
       <c r="AZ79" s="4" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="BA79" s="4" t="n">
         <v>0</v>
@@ -15439,10 +15009,10 @@
       <c r="Z80" s="4" t="n"/>
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
-      <c r="AC80" s="2" t="n"/>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="28" t="n"/>
       <c r="AE80" s="5" t="n"/>
-      <c r="AF80" s="2" t="n"/>
+      <c r="AF80" s="2" t="inlineStr"/>
       <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n"/>
       <c r="AI80" s="4" t="n"/>
@@ -15454,10 +15024,10 @@
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
-      <c r="AR80" s="2" t="n"/>
+      <c r="AR80" s="2" t="inlineStr"/>
       <c r="AS80" s="28" t="n"/>
       <c r="AT80" s="5" t="n"/>
-      <c r="AU80" s="2" t="n"/>
+      <c r="AU80" s="2" t="inlineStr"/>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
@@ -15469,10 +15039,10 @@
       <c r="BD80" s="4" t="n"/>
       <c r="BE80" s="4" t="n"/>
       <c r="BF80" s="4" t="n"/>
-      <c r="BG80" s="2" t="n"/>
+      <c r="BG80" s="2" t="inlineStr"/>
       <c r="BH80" s="28" t="n"/>
       <c r="BI80" s="5" t="n"/>
-      <c r="BJ80" s="2" t="n"/>
+      <c r="BJ80" s="2" t="inlineStr"/>
       <c r="BK80" s="4" t="n"/>
       <c r="BL80" s="4" t="n"/>
       <c r="BM80" s="4" t="n"/>
@@ -15484,10 +15054,10 @@
       <c r="BS80" s="4" t="n"/>
       <c r="BT80" s="4" t="n"/>
       <c r="BU80" s="4" t="n"/>
-      <c r="BV80" s="2" t="n"/>
+      <c r="BV80" s="2" t="inlineStr"/>
       <c r="BW80" s="28" t="n"/>
       <c r="BX80" s="5" t="n"/>
-      <c r="BY80" s="2" t="n"/>
+      <c r="BY80" s="2" t="inlineStr"/>
       <c r="BZ80" s="4" t="n"/>
       <c r="CA80" s="4" t="n"/>
       <c r="CB80" s="4" t="n"/>
@@ -15499,22 +15069,12 @@
       <c r="CH80" s="4" t="n"/>
       <c r="CI80" s="4" t="n"/>
       <c r="CJ80" s="4" t="n"/>
-      <c r="CK80" s="2" t="n"/>
+      <c r="CK80" s="2" t="inlineStr"/>
       <c r="CL80" s="28" t="n"/>
-      <c r="CN80" s="2" t="n"/>
+      <c r="CN80" s="2" t="inlineStr"/>
       <c r="CP80" s="11" t="n"/>
       <c r="CQ80" s="7" t="n"/>
       <c r="CR80" s="12" t="n"/>
-      <c r="CS80" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU80" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15668,7 +15228,7 @@
         <v>99.3</v>
       </c>
       <c r="AZ81" s="4" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="BA81" s="4" t="n">
         <v>1</v>
@@ -15972,7 +15532,7 @@
         <v>100</v>
       </c>
       <c r="AZ82" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="BA82" s="4" t="n">
         <v>0</v>
@@ -16274,7 +15834,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AZ83" s="4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="BA83" s="4" t="n">
         <v>0</v>
@@ -16458,10 +16018,10 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="2" t="n"/>
+      <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="28" t="n"/>
       <c r="AE84" s="5" t="n"/>
-      <c r="AF84" s="2" t="n"/>
+      <c r="AF84" s="2" t="inlineStr"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
       <c r="AI84" s="4" t="n"/>
@@ -16473,10 +16033,10 @@
       <c r="AO84" s="4" t="n"/>
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>
-      <c r="AR84" s="2" t="n"/>
+      <c r="AR84" s="2" t="inlineStr"/>
       <c r="AS84" s="28" t="n"/>
       <c r="AT84" s="5" t="n"/>
-      <c r="AU84" s="2" t="n"/>
+      <c r="AU84" s="2" t="inlineStr"/>
       <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
@@ -16488,10 +16048,10 @@
       <c r="BD84" s="4" t="n"/>
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
-      <c r="BG84" s="2" t="n"/>
+      <c r="BG84" s="2" t="inlineStr"/>
       <c r="BH84" s="28" t="n"/>
       <c r="BI84" s="5" t="n"/>
-      <c r="BJ84" s="2" t="n"/>
+      <c r="BJ84" s="2" t="inlineStr"/>
       <c r="BK84" s="4" t="n"/>
       <c r="BL84" s="4" t="n"/>
       <c r="BM84" s="4" t="n"/>
@@ -16503,10 +16063,10 @@
       <c r="BS84" s="4" t="n"/>
       <c r="BT84" s="4" t="n"/>
       <c r="BU84" s="4" t="n"/>
-      <c r="BV84" s="2" t="n"/>
+      <c r="BV84" s="2" t="inlineStr"/>
       <c r="BW84" s="2" t="n"/>
       <c r="BX84" s="2" t="n"/>
-      <c r="BY84" s="2" t="n"/>
+      <c r="BY84" s="2" t="inlineStr"/>
       <c r="BZ84" s="4" t="n"/>
       <c r="CA84" s="4" t="n"/>
       <c r="CB84" s="4" t="n"/>
@@ -16518,22 +16078,12 @@
       <c r="CH84" s="4" t="n"/>
       <c r="CI84" s="4" t="n"/>
       <c r="CJ84" s="4" t="n"/>
-      <c r="CK84" s="2" t="n"/>
+      <c r="CK84" s="2" t="inlineStr"/>
       <c r="CL84" s="28" t="n"/>
-      <c r="CN84" s="2" t="n"/>
+      <c r="CN84" s="2" t="inlineStr"/>
       <c r="CP84" s="11" t="n"/>
       <c r="CQ84" s="7" t="n"/>
       <c r="CR84" s="12" t="n"/>
-      <c r="CS84" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU84" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -16574,10 +16124,10 @@
       <c r="Z85" s="4" t="n"/>
       <c r="AA85" s="4" t="n"/>
       <c r="AB85" s="4" t="n"/>
-      <c r="AC85" s="2" t="n"/>
+      <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="28" t="n"/>
       <c r="AE85" s="5" t="n"/>
-      <c r="AF85" s="2" t="n"/>
+      <c r="AF85" s="2" t="inlineStr"/>
       <c r="AG85" s="4" t="n"/>
       <c r="AH85" s="4" t="n"/>
       <c r="AI85" s="4" t="n"/>
@@ -16589,10 +16139,10 @@
       <c r="AO85" s="4" t="n"/>
       <c r="AP85" s="4" t="n"/>
       <c r="AQ85" s="4" t="n"/>
-      <c r="AR85" s="2" t="n"/>
+      <c r="AR85" s="2" t="inlineStr"/>
       <c r="AS85" s="28" t="n"/>
       <c r="AT85" s="30" t="n"/>
-      <c r="AU85" s="2" t="n"/>
+      <c r="AU85" s="2" t="inlineStr"/>
       <c r="AV85" s="4" t="n"/>
       <c r="AW85" s="4" t="n"/>
       <c r="AX85" s="4" t="n"/>
@@ -16604,10 +16154,10 @@
       <c r="BD85" s="4" t="n"/>
       <c r="BE85" s="4" t="n"/>
       <c r="BF85" s="4" t="n"/>
-      <c r="BG85" s="2" t="n"/>
+      <c r="BG85" s="2" t="inlineStr"/>
       <c r="BH85" s="28" t="n"/>
       <c r="BI85" s="5" t="n"/>
-      <c r="BJ85" s="2" t="n"/>
+      <c r="BJ85" s="2" t="inlineStr"/>
       <c r="BK85" s="4" t="n"/>
       <c r="BL85" s="4" t="n"/>
       <c r="BM85" s="4" t="n"/>
@@ -16619,10 +16169,10 @@
       <c r="BS85" s="4" t="n"/>
       <c r="BT85" s="4" t="n"/>
       <c r="BU85" s="4" t="n"/>
-      <c r="BV85" s="2" t="n"/>
+      <c r="BV85" s="2" t="inlineStr"/>
       <c r="BW85" s="2" t="n"/>
       <c r="BX85" s="2" t="n"/>
-      <c r="BY85" s="2" t="n"/>
+      <c r="BY85" s="2" t="inlineStr"/>
       <c r="BZ85" s="4" t="n"/>
       <c r="CA85" s="4" t="n"/>
       <c r="CB85" s="4" t="n"/>
@@ -16634,23 +16184,13 @@
       <c r="CH85" s="4" t="n"/>
       <c r="CI85" s="4" t="n"/>
       <c r="CJ85" s="4" t="n"/>
-      <c r="CK85" s="2" t="n"/>
+      <c r="CK85" s="2" t="inlineStr"/>
       <c r="CL85" s="28" t="n"/>
-      <c r="CN85" s="2" t="n"/>
+      <c r="CN85" s="2" t="inlineStr"/>
       <c r="CO85" s="17" t="n"/>
       <c r="CP85" s="18" t="n"/>
       <c r="CQ85" s="19" t="n"/>
       <c r="CR85" s="19" t="n"/>
-      <c r="CS85" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="CU85" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -18048,12 +17588,20 @@
           <t>1000015</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AR100" t="inlineStr"/>
       <c r="AU100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
       <c r="BJ100" t="inlineStr">
         <is>
           <t>11111</t>
         </is>
       </c>
+      <c r="BV100" t="inlineStr"/>
+      <c r="BY100" t="inlineStr"/>
+      <c r="CK100" t="inlineStr"/>
+      <c r="CN100" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K84">

--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grades" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,13 +90,6 @@
       <color theme="0" tint="-0.249977111117893"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <strike val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -158,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -238,178 +231,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF4D50"/>
-          <bgColor rgb="FFFF4D50"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF99CC00"/>
-          <bgColor rgb="FF99CC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF33CC33"/>
-          <bgColor rgb="FF33CC33"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF4D50"/>
-          <bgColor rgb="FFFF4D50"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF33CC33"/>
-          <bgColor rgb="FF33CC33"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF99CC00"/>
-          <bgColor rgb="FF99CC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF99CC00"/>
-          <bgColor rgb="FF99CC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF33CC33"/>
-          <bgColor rgb="FF33CC33"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF4D50"/>
-          <bgColor rgb="FFFF4D50"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF33CC33"/>
-          <bgColor rgb="FF33CC33"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF99CC00"/>
-          <bgColor rgb="FF99CC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF4D50"/>
-          <bgColor rgb="FFFF4D50"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -813,69 +639,69 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CU100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4.6328125" customWidth="1" min="1" max="1"/>
-    <col width="17.90625" customWidth="1" min="2" max="2"/>
+    <col width="4.6640625" customWidth="1" min="1" max="1"/>
+    <col width="17.88671875" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8.08984375" customWidth="1" style="10" min="11" max="11"/>
-    <col width="6.08984375" customWidth="1" style="7" min="12" max="12"/>
-    <col width="6.90625" customWidth="1" min="13" max="13"/>
-    <col width="6.453125" customWidth="1" style="22" min="14" max="14"/>
-    <col width="13.54296875" customWidth="1" style="21" min="15" max="15"/>
-    <col width="7.453125" customWidth="1" style="10" min="16" max="16"/>
-    <col width="5.36328125" customWidth="1" style="10" min="17" max="17"/>
-    <col width="10.1796875" customWidth="1" min="18" max="18"/>
-    <col width="7.6328125" customWidth="1" min="19" max="19"/>
-    <col width="7.453125" customWidth="1" min="20" max="22"/>
+    <col width="8.109375" customWidth="1" style="10" min="11" max="11"/>
+    <col width="6.109375" customWidth="1" style="7" min="12" max="12"/>
+    <col width="6.88671875" customWidth="1" min="13" max="13"/>
+    <col width="6.44140625" customWidth="1" style="22" min="14" max="14"/>
+    <col width="13.5546875" customWidth="1" style="21" min="15" max="15"/>
+    <col width="7.44140625" customWidth="1" style="10" min="16" max="16"/>
+    <col width="5.33203125" customWidth="1" style="10" min="17" max="17"/>
+    <col width="10.21875" customWidth="1" min="18" max="18"/>
+    <col width="7.6640625" customWidth="1" min="19" max="19"/>
+    <col width="7.44140625" customWidth="1" min="20" max="22"/>
     <col width="5" customWidth="1" min="23" max="25"/>
-    <col width="5.453125" customWidth="1" min="26" max="27"/>
+    <col width="5.44140625" customWidth="1" min="26" max="27"/>
     <col width="6" customWidth="1" min="28" max="28"/>
-    <col width="6.81640625" customWidth="1" min="29" max="29"/>
-    <col width="10.36328125" customWidth="1" min="30" max="30"/>
-    <col width="7.08984375" customWidth="1" min="31" max="31"/>
-    <col width="6.81640625" customWidth="1" min="32" max="32"/>
-    <col width="10.1796875" customWidth="1" min="33" max="33"/>
-    <col width="7.6328125" customWidth="1" min="34" max="34"/>
-    <col width="7.453125" customWidth="1" min="35" max="37"/>
+    <col width="6.77734375" customWidth="1" min="29" max="29"/>
+    <col width="10.33203125" customWidth="1" min="30" max="30"/>
+    <col width="7.109375" customWidth="1" min="31" max="31"/>
+    <col width="6.77734375" customWidth="1" min="32" max="32"/>
+    <col width="10.21875" customWidth="1" min="33" max="33"/>
+    <col width="7.6640625" customWidth="1" min="34" max="34"/>
+    <col width="7.44140625" customWidth="1" min="35" max="37"/>
     <col width="5" customWidth="1" min="38" max="40"/>
-    <col width="5.453125" customWidth="1" min="41" max="42"/>
+    <col width="5.44140625" customWidth="1" min="41" max="42"/>
     <col width="6" customWidth="1" min="43" max="43"/>
-    <col width="6.81640625" customWidth="1" min="44" max="44"/>
-    <col width="10.36328125" customWidth="1" min="45" max="45"/>
-    <col width="7.08984375" customWidth="1" min="46" max="46"/>
-    <col width="6.81640625" customWidth="1" min="47" max="47"/>
-    <col width="10.1796875" customWidth="1" min="48" max="48"/>
-    <col width="7.6328125" customWidth="1" min="49" max="49"/>
-    <col width="7.453125" customWidth="1" min="50" max="52"/>
+    <col width="6.77734375" customWidth="1" min="44" max="44"/>
+    <col width="10.33203125" customWidth="1" min="45" max="45"/>
+    <col width="7.109375" customWidth="1" min="46" max="46"/>
+    <col width="6.77734375" customWidth="1" min="47" max="47"/>
+    <col width="10.21875" customWidth="1" min="48" max="48"/>
+    <col width="7.6640625" customWidth="1" min="49" max="49"/>
+    <col width="7.44140625" customWidth="1" min="50" max="52"/>
     <col width="5" customWidth="1" min="53" max="55"/>
-    <col width="5.453125" customWidth="1" min="56" max="57"/>
+    <col width="5.44140625" customWidth="1" min="56" max="57"/>
     <col width="6" customWidth="1" min="58" max="58"/>
-    <col width="6.81640625" customWidth="1" min="59" max="59"/>
-    <col width="10.36328125" customWidth="1" min="60" max="60"/>
-    <col width="7.08984375" customWidth="1" min="61" max="61"/>
-    <col width="6.81640625" customWidth="1" min="62" max="62"/>
-    <col width="10.1796875" customWidth="1" min="63" max="63"/>
-    <col width="7.6328125" customWidth="1" min="64" max="64"/>
-    <col width="7.453125" customWidth="1" min="65" max="67"/>
+    <col width="6.77734375" customWidth="1" min="59" max="59"/>
+    <col width="10.33203125" customWidth="1" min="60" max="60"/>
+    <col width="7.109375" customWidth="1" min="61" max="61"/>
+    <col width="6.77734375" customWidth="1" min="62" max="62"/>
+    <col width="10.21875" customWidth="1" min="63" max="63"/>
+    <col width="7.6640625" customWidth="1" min="64" max="64"/>
+    <col width="7.44140625" customWidth="1" min="65" max="67"/>
     <col width="5" customWidth="1" min="68" max="70"/>
-    <col width="5.453125" customWidth="1" min="71" max="72"/>
+    <col width="5.44140625" customWidth="1" min="71" max="72"/>
     <col width="6" customWidth="1" min="73" max="73"/>
-    <col width="6.81640625" customWidth="1" min="74" max="74"/>
-    <col width="10.36328125" customWidth="1" min="75" max="75"/>
-    <col width="7.08984375" customWidth="1" min="76" max="76"/>
-    <col width="6.81640625" customWidth="1" min="77" max="77"/>
-    <col width="10.1796875" customWidth="1" min="78" max="78"/>
-    <col width="7.6328125" customWidth="1" min="79" max="79"/>
-    <col width="7.453125" customWidth="1" min="80" max="82"/>
+    <col width="6.77734375" customWidth="1" min="74" max="74"/>
+    <col width="10.33203125" customWidth="1" min="75" max="75"/>
+    <col width="7.109375" customWidth="1" min="76" max="76"/>
+    <col width="6.77734375" customWidth="1" min="77" max="77"/>
+    <col width="10.21875" customWidth="1" min="78" max="78"/>
+    <col width="7.6640625" customWidth="1" min="79" max="79"/>
+    <col width="7.44140625" customWidth="1" min="80" max="82"/>
     <col width="5" customWidth="1" min="83" max="85"/>
-    <col width="5.453125" customWidth="1" min="86" max="87"/>
+    <col width="5.44140625" customWidth="1" min="86" max="87"/>
     <col width="6" customWidth="1" min="88" max="88"/>
-    <col width="6.81640625" customWidth="1" min="89" max="89"/>
-    <col width="10.36328125" customWidth="1" min="90" max="90"/>
-    <col width="7.08984375" customWidth="1" min="91" max="91"/>
-    <col width="6.81640625" customWidth="1" min="92" max="92"/>
-    <col width="8.90625" customWidth="1" style="10" min="93" max="93"/>
+    <col width="6.77734375" customWidth="1" min="89" max="89"/>
+    <col width="10.33203125" customWidth="1" min="90" max="90"/>
+    <col width="7.109375" customWidth="1" min="91" max="91"/>
+    <col width="6.77734375" customWidth="1" min="92" max="92"/>
+    <col width="8.88671875" customWidth="1" style="10" min="93" max="93"/>
     <col width="10" bestFit="1" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
@@ -1381,10 +1207,8 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="28" t="n"/>
-      <c r="AE2" s="5" t="n"/>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
@@ -1396,10 +1220,8 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="28" t="n"/>
-      <c r="AT2" s="5" t="n"/>
-      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AU2" s="2" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
@@ -1411,10 +1233,8 @@
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="28" t="n"/>
-      <c r="BI2" s="5" t="n"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="n"/>
+      <c r="BJ2" s="2" t="n"/>
       <c r="BK2" s="4" t="n"/>
       <c r="BL2" s="4" t="n"/>
       <c r="BM2" s="4" t="n"/>
@@ -1426,10 +1246,10 @@
       <c r="BS2" s="4" t="n"/>
       <c r="BT2" s="4" t="n"/>
       <c r="BU2" s="4" t="n"/>
-      <c r="BV2" s="2" t="inlineStr"/>
-      <c r="BW2" s="28" t="n"/>
-      <c r="BX2" s="5" t="n"/>
-      <c r="BY2" s="2" t="inlineStr"/>
+      <c r="BV2" s="2" t="n"/>
+      <c r="BW2" s="2" t="n"/>
+      <c r="BX2" s="2" t="n"/>
+      <c r="BY2" s="2" t="n"/>
       <c r="BZ2" s="4" t="n"/>
       <c r="CA2" s="4" t="n"/>
       <c r="CB2" s="4" t="n"/>
@@ -1441,12 +1261,22 @@
       <c r="CH2" s="4" t="n"/>
       <c r="CI2" s="4" t="n"/>
       <c r="CJ2" s="4" t="n"/>
-      <c r="CK2" s="2" t="inlineStr"/>
+      <c r="CK2" s="2" t="n"/>
       <c r="CL2" s="28" t="n"/>
-      <c r="CN2" s="2" t="inlineStr"/>
+      <c r="CN2" s="2" t="n"/>
       <c r="CP2" s="11" t="n"/>
       <c r="CQ2" s="7" t="n"/>
       <c r="CR2" s="12" t="n"/>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1483,10 +1313,8 @@
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="2" t="inlineStr"/>
-      <c r="AD3" s="28" t="n"/>
-      <c r="AE3" s="5" t="n"/>
-      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="n"/>
+      <c r="AF3" s="2" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
@@ -1498,10 +1326,8 @@
       <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="28" t="n"/>
-      <c r="AT3" s="5" t="n"/>
-      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="n"/>
+      <c r="AU3" s="2" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
@@ -1513,10 +1339,8 @@
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="28" t="n"/>
-      <c r="BI3" s="5" t="n"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="n"/>
+      <c r="BJ3" s="2" t="n"/>
       <c r="BK3" s="4" t="n"/>
       <c r="BL3" s="4" t="n"/>
       <c r="BM3" s="4" t="n"/>
@@ -1528,10 +1352,8 @@
       <c r="BS3" s="4" t="n"/>
       <c r="BT3" s="4" t="n"/>
       <c r="BU3" s="4" t="n"/>
-      <c r="BV3" s="2" t="inlineStr"/>
-      <c r="BW3" s="28" t="n"/>
-      <c r="BX3" s="5" t="n"/>
-      <c r="BY3" s="2" t="inlineStr"/>
+      <c r="BV3" s="2" t="n"/>
+      <c r="BY3" s="2" t="n"/>
       <c r="BZ3" s="4" t="n"/>
       <c r="CA3" s="4" t="n"/>
       <c r="CB3" s="4" t="n"/>
@@ -1543,12 +1365,21 @@
       <c r="CH3" s="4" t="n"/>
       <c r="CI3" s="4" t="n"/>
       <c r="CJ3" s="4" t="n"/>
-      <c r="CK3" s="2" t="inlineStr"/>
-      <c r="CL3" s="28" t="n"/>
-      <c r="CN3" s="2" t="inlineStr"/>
+      <c r="CK3" s="2" t="n"/>
+      <c r="CN3" s="2" t="n"/>
       <c r="CP3" s="11" t="n"/>
       <c r="CQ3" s="7" t="n"/>
       <c r="CR3" s="12" t="n"/>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1623,14 +1454,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD4" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
           <t>01011</t>
@@ -1674,14 +1497,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS4" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU4" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -1723,14 +1538,6 @@
       <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH4" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI4" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
         </is>
       </c>
       <c r="BJ4" s="2" t="inlineStr">
@@ -1774,14 +1581,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW4" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY4" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -1823,14 +1622,6 @@
       <c r="CK4" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL4" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN4" s="2" t="inlineStr">
@@ -1927,14 +1718,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -1978,14 +1761,6 @@
           <t>C2&gt;</t>
         </is>
       </c>
-      <c r="AS5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU5" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -2027,14 +1802,6 @@
       <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ5" s="2" t="inlineStr">
@@ -2076,14 +1843,6 @@
       <c r="BV5" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BW5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BY5" s="2" t="inlineStr">
@@ -2103,14 +1862,6 @@
       <c r="CI5" s="4" t="n"/>
       <c r="CJ5" s="4" t="n"/>
       <c r="CK5" s="2" t="inlineStr"/>
-      <c r="CL5" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN5" s="2" t="inlineStr">
         <is>
           <t>010</t>
@@ -2179,10 +1930,6 @@
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="2" t="inlineStr"/>
-      <c r="AD6" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE6" s="5" t="n"/>
       <c r="AF6" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -2200,10 +1947,6 @@
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" s="5" t="n"/>
       <c r="AU6" s="2" t="inlineStr">
         <is>
           <t>011101</t>
@@ -2221,10 +1964,6 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="2" t="inlineStr"/>
-      <c r="BH6" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI6" s="5" t="n"/>
       <c r="BJ6" s="2" t="inlineStr">
         <is>
           <t>01110</t>
@@ -2242,8 +1981,6 @@
       <c r="BT6" s="4" t="n"/>
       <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="2" t="inlineStr"/>
-      <c r="BW6" s="28" t="n"/>
-      <c r="BX6" s="5" t="n"/>
       <c r="BY6" s="2" t="inlineStr"/>
       <c r="BZ6" s="4" t="n"/>
       <c r="CA6" s="4" t="n"/>
@@ -2257,7 +1994,6 @@
       <c r="CI6" s="4" t="n"/>
       <c r="CJ6" s="4" t="n"/>
       <c r="CK6" s="2" t="inlineStr"/>
-      <c r="CL6" s="28" t="n"/>
       <c r="CN6" s="2" t="inlineStr"/>
       <c r="CP6" s="11" t="n"/>
       <c r="CQ6" s="7" t="n"/>
@@ -2298,10 +2034,8 @@
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="2" t="inlineStr"/>
-      <c r="AD7" s="28" t="n"/>
-      <c r="AE7" s="5" t="n"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="n"/>
+      <c r="AF7" s="2" t="n"/>
       <c r="AG7" s="4" t="n"/>
       <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="n"/>
@@ -2313,10 +2047,8 @@
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="28" t="n"/>
-      <c r="AT7" s="5" t="n"/>
-      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
@@ -2328,10 +2060,8 @@
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="2" t="inlineStr"/>
-      <c r="BH7" s="28" t="n"/>
-      <c r="BI7" s="5" t="n"/>
-      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BG7" s="2" t="n"/>
+      <c r="BJ7" s="2" t="n"/>
       <c r="BK7" s="4" t="n"/>
       <c r="BL7" s="4" t="n"/>
       <c r="BM7" s="4" t="n"/>
@@ -2343,10 +2073,8 @@
       <c r="BS7" s="4" t="n"/>
       <c r="BT7" s="4" t="n"/>
       <c r="BU7" s="4" t="n"/>
-      <c r="BV7" s="2" t="inlineStr"/>
-      <c r="BW7" s="28" t="n"/>
-      <c r="BX7" s="5" t="n"/>
-      <c r="BY7" s="2" t="inlineStr"/>
+      <c r="BV7" s="2" t="n"/>
+      <c r="BY7" s="2" t="n"/>
       <c r="BZ7" s="4" t="n"/>
       <c r="CA7" s="4" t="n"/>
       <c r="CB7" s="4" t="n"/>
@@ -2358,12 +2086,21 @@
       <c r="CH7" s="4" t="n"/>
       <c r="CI7" s="4" t="n"/>
       <c r="CJ7" s="4" t="n"/>
-      <c r="CK7" s="2" t="inlineStr"/>
-      <c r="CL7" s="28" t="n"/>
-      <c r="CN7" s="2" t="inlineStr"/>
+      <c r="CK7" s="2" t="n"/>
+      <c r="CN7" s="2" t="n"/>
       <c r="CP7" s="11" t="n"/>
       <c r="CQ7" s="7" t="n"/>
       <c r="CR7" s="12" t="n"/>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,10 +2138,8 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="28" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="n"/>
+      <c r="AF8" s="2" t="n"/>
       <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="n"/>
@@ -2416,10 +2151,8 @@
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="28" t="n"/>
-      <c r="AT8" s="5" t="n"/>
-      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -2431,10 +2164,8 @@
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="2" t="inlineStr"/>
-      <c r="BH8" s="28" t="n"/>
-      <c r="BI8" s="5" t="n"/>
-      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BG8" s="2" t="n"/>
+      <c r="BJ8" s="2" t="n"/>
       <c r="BK8" s="4" t="n"/>
       <c r="BL8" s="4" t="n"/>
       <c r="BM8" s="4" t="n"/>
@@ -2446,10 +2177,8 @@
       <c r="BS8" s="4" t="n"/>
       <c r="BT8" s="4" t="n"/>
       <c r="BU8" s="4" t="n"/>
-      <c r="BV8" s="2" t="inlineStr"/>
-      <c r="BW8" s="28" t="n"/>
-      <c r="BX8" s="5" t="n"/>
-      <c r="BY8" s="2" t="inlineStr"/>
+      <c r="BV8" s="2" t="n"/>
+      <c r="BY8" s="2" t="n"/>
       <c r="BZ8" s="4" t="n"/>
       <c r="CA8" s="4" t="n"/>
       <c r="CB8" s="4" t="n"/>
@@ -2461,12 +2190,21 @@
       <c r="CH8" s="4" t="n"/>
       <c r="CI8" s="4" t="n"/>
       <c r="CJ8" s="4" t="n"/>
-      <c r="CK8" s="2" t="inlineStr"/>
-      <c r="CL8" s="28" t="n"/>
-      <c r="CN8" s="2" t="inlineStr"/>
+      <c r="CK8" s="2" t="n"/>
+      <c r="CN8" s="2" t="n"/>
       <c r="CP8" s="11" t="n"/>
       <c r="CQ8" s="7" t="n"/>
       <c r="CR8" s="12" t="n"/>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2514,14 +2252,6 @@
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="2" t="inlineStr"/>
-      <c r="AD9" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
           <t>00011</t>
@@ -2565,14 +2295,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS9" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT9" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU9" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -2614,14 +2336,6 @@
       <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH9" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI9" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ9" s="2" t="inlineStr">
@@ -2641,14 +2355,6 @@
       <c r="BT9" s="4" t="n"/>
       <c r="BU9" s="4" t="n"/>
       <c r="BV9" s="2" t="inlineStr"/>
-      <c r="BW9" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX9" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY9" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -2666,14 +2372,6 @@
       <c r="CI9" s="4" t="n"/>
       <c r="CJ9" s="4" t="n"/>
       <c r="CK9" s="2" t="inlineStr"/>
-      <c r="CL9" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM9" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN9" s="2" t="inlineStr">
         <is>
           <t>010</t>
@@ -2718,10 +2416,8 @@
       <c r="Z10" s="4" t="n"/>
       <c r="AA10" s="4" t="n"/>
       <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="2" t="inlineStr"/>
-      <c r="AD10" s="28" t="n"/>
-      <c r="AE10" s="5" t="n"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="n"/>
+      <c r="AF10" s="2" t="n"/>
       <c r="AG10" s="4" t="n"/>
       <c r="AH10" s="4" t="n"/>
       <c r="AI10" s="4" t="n"/>
@@ -2733,10 +2429,8 @@
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="28" t="n"/>
-      <c r="AT10" s="5" t="n"/>
-      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AU10" s="2" t="n"/>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
@@ -2748,10 +2442,8 @@
       <c r="BD10" s="4" t="n"/>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="2" t="inlineStr"/>
-      <c r="BH10" s="28" t="n"/>
-      <c r="BI10" s="5" t="n"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="n"/>
+      <c r="BJ10" s="2" t="n"/>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
       <c r="BM10" s="4" t="n"/>
@@ -2763,10 +2455,8 @@
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
       <c r="BU10" s="4" t="n"/>
-      <c r="BV10" s="2" t="inlineStr"/>
-      <c r="BW10" s="28" t="n"/>
-      <c r="BX10" s="5" t="n"/>
-      <c r="BY10" s="2" t="inlineStr"/>
+      <c r="BV10" s="2" t="n"/>
+      <c r="BY10" s="2" t="n"/>
       <c r="BZ10" s="4" t="n"/>
       <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
@@ -2778,12 +2468,21 @@
       <c r="CH10" s="4" t="n"/>
       <c r="CI10" s="4" t="n"/>
       <c r="CJ10" s="4" t="n"/>
-      <c r="CK10" s="2" t="inlineStr"/>
-      <c r="CL10" s="28" t="n"/>
-      <c r="CN10" s="2" t="inlineStr"/>
+      <c r="CK10" s="2" t="n"/>
+      <c r="CN10" s="2" t="n"/>
       <c r="CP10" s="11" t="n"/>
       <c r="CQ10" s="7" t="n"/>
       <c r="CR10" s="12" t="n"/>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2821,10 +2520,8 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="2" t="inlineStr"/>
-      <c r="AD11" s="28" t="n"/>
-      <c r="AE11" s="5" t="n"/>
-      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AF11" s="2" t="n"/>
       <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="n"/>
@@ -2836,10 +2533,8 @@
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="28" t="n"/>
-      <c r="AT11" s="5" t="n"/>
-      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AU11" s="2" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -2851,10 +2546,8 @@
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="2" t="inlineStr"/>
-      <c r="BH11" s="28" t="n"/>
-      <c r="BI11" s="5" t="n"/>
-      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BG11" s="2" t="n"/>
+      <c r="BJ11" s="2" t="n"/>
       <c r="BK11" s="4" t="n"/>
       <c r="BL11" s="4" t="n"/>
       <c r="BM11" s="4" t="n"/>
@@ -2866,10 +2559,8 @@
       <c r="BS11" s="4" t="n"/>
       <c r="BT11" s="4" t="n"/>
       <c r="BU11" s="4" t="n"/>
-      <c r="BV11" s="2" t="inlineStr"/>
-      <c r="BW11" s="28" t="n"/>
-      <c r="BX11" s="5" t="n"/>
-      <c r="BY11" s="2" t="inlineStr"/>
+      <c r="BV11" s="2" t="n"/>
+      <c r="BY11" s="2" t="n"/>
       <c r="BZ11" s="4" t="n"/>
       <c r="CA11" s="4" t="n"/>
       <c r="CB11" s="4" t="n"/>
@@ -2881,12 +2572,21 @@
       <c r="CH11" s="4" t="n"/>
       <c r="CI11" s="4" t="n"/>
       <c r="CJ11" s="4" t="n"/>
-      <c r="CK11" s="2" t="inlineStr"/>
-      <c r="CL11" s="28" t="n"/>
-      <c r="CN11" s="2" t="inlineStr"/>
+      <c r="CK11" s="2" t="n"/>
+      <c r="CN11" s="2" t="n"/>
       <c r="CP11" s="11" t="n"/>
       <c r="CQ11" s="7" t="n"/>
       <c r="CR11" s="12" t="n"/>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2937,14 +2637,6 @@
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="2" t="inlineStr"/>
-      <c r="AD12" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE12" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
           <t>01011</t>
@@ -2988,14 +2680,6 @@
           <t>C1&gt;</t>
         </is>
       </c>
-      <c r="AS12" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT12" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU12" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -3037,14 +2721,6 @@
       <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH12" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI12" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ12" s="2" t="inlineStr">
@@ -3088,14 +2764,6 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="BW12" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX12" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY12" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -3137,14 +2805,6 @@
       <c r="CK12" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL12" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM12" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN12" s="2" t="inlineStr">
@@ -3202,10 +2862,8 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="2" t="inlineStr"/>
-      <c r="AD13" s="28" t="n"/>
-      <c r="AE13" s="5" t="n"/>
-      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="n"/>
+      <c r="AF13" s="2" t="n"/>
       <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
       <c r="AI13" s="4" t="n"/>
@@ -3217,10 +2875,8 @@
       <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="28" t="n"/>
-      <c r="AT13" s="5" t="n"/>
-      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AU13" s="2" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -3232,10 +2888,8 @@
       <c r="BD13" s="4" t="n"/>
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="2" t="inlineStr"/>
-      <c r="BH13" s="28" t="n"/>
-      <c r="BI13" s="5" t="n"/>
-      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="n"/>
+      <c r="BJ13" s="2" t="n"/>
       <c r="BK13" s="4" t="n"/>
       <c r="BL13" s="4" t="n"/>
       <c r="BM13" s="4" t="n"/>
@@ -3247,10 +2901,8 @@
       <c r="BS13" s="4" t="n"/>
       <c r="BT13" s="4" t="n"/>
       <c r="BU13" s="4" t="n"/>
-      <c r="BV13" s="2" t="inlineStr"/>
-      <c r="BW13" s="28" t="n"/>
-      <c r="BX13" s="5" t="n"/>
-      <c r="BY13" s="2" t="inlineStr"/>
+      <c r="BV13" s="2" t="n"/>
+      <c r="BY13" s="2" t="n"/>
       <c r="BZ13" s="4" t="n"/>
       <c r="CA13" s="4" t="n"/>
       <c r="CB13" s="4" t="n"/>
@@ -3262,12 +2914,21 @@
       <c r="CH13" s="4" t="n"/>
       <c r="CI13" s="4" t="n"/>
       <c r="CJ13" s="4" t="n"/>
-      <c r="CK13" s="2" t="inlineStr"/>
-      <c r="CL13" s="28" t="n"/>
-      <c r="CN13" s="2" t="inlineStr"/>
+      <c r="CK13" s="2" t="n"/>
+      <c r="CN13" s="2" t="n"/>
       <c r="CP13" s="11" t="n"/>
       <c r="CQ13" s="7" t="n"/>
       <c r="CR13" s="12" t="n"/>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU13" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3301,14 +2962,6 @@
       <c r="AA14" s="4" t="n"/>
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="2" t="inlineStr"/>
-      <c r="AD14" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF14" s="2" t="inlineStr">
         <is>
           <t>01011</t>
@@ -3326,14 +2979,6 @@
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="2" t="inlineStr"/>
-      <c r="AS14" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT14" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="AU14" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -3351,14 +2996,6 @@
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
       <c r="BG14" s="2" t="inlineStr"/>
-      <c r="BH14" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI14" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BJ14" s="2" t="inlineStr">
         <is>
           <t>00010</t>
@@ -3376,14 +3013,6 @@
       <c r="BT14" s="4" t="n"/>
       <c r="BU14" s="4" t="n"/>
       <c r="BV14" s="2" t="inlineStr"/>
-      <c r="BW14" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX14" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY14" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -3424,15 +3053,7 @@
       </c>
       <c r="CK14" s="2" t="inlineStr">
         <is>
-          <t>C1&lt;</t>
-        </is>
-      </c>
-      <c r="CL14" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM14" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>_</t>
         </is>
       </c>
       <c r="CN14" s="2" t="inlineStr">
@@ -3479,10 +3100,8 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="2" t="inlineStr"/>
-      <c r="AD15" s="28" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="n"/>
+      <c r="AF15" s="2" t="n"/>
       <c r="AG15" s="4" t="n"/>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
@@ -3494,10 +3113,8 @@
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="2" t="inlineStr"/>
-      <c r="AS15" s="28" t="n"/>
-      <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="n"/>
+      <c r="AU15" s="2" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
@@ -3509,10 +3126,8 @@
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
       <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="2" t="inlineStr"/>
-      <c r="BH15" s="28" t="n"/>
-      <c r="BI15" s="5" t="n"/>
-      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="n"/>
+      <c r="BJ15" s="2" t="n"/>
       <c r="BK15" s="4" t="n"/>
       <c r="BL15" s="4" t="n"/>
       <c r="BM15" s="4" t="n"/>
@@ -3524,10 +3139,8 @@
       <c r="BS15" s="4" t="n"/>
       <c r="BT15" s="4" t="n"/>
       <c r="BU15" s="4" t="n"/>
-      <c r="BV15" s="2" t="inlineStr"/>
-      <c r="BW15" s="28" t="n"/>
-      <c r="BX15" s="5" t="n"/>
-      <c r="BY15" s="2" t="inlineStr"/>
+      <c r="BV15" s="2" t="n"/>
+      <c r="BY15" s="2" t="n"/>
       <c r="BZ15" s="4" t="n"/>
       <c r="CA15" s="4" t="n"/>
       <c r="CB15" s="4" t="n"/>
@@ -3539,12 +3152,21 @@
       <c r="CH15" s="4" t="n"/>
       <c r="CI15" s="4" t="n"/>
       <c r="CJ15" s="4" t="n"/>
-      <c r="CK15" s="2" t="inlineStr"/>
-      <c r="CL15" s="28" t="n"/>
-      <c r="CN15" s="2" t="inlineStr"/>
+      <c r="CK15" s="2" t="n"/>
+      <c r="CN15" s="2" t="n"/>
       <c r="CP15" s="11" t="n"/>
       <c r="CQ15" s="7" t="n"/>
       <c r="CR15" s="12" t="n"/>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU15" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3581,10 +3203,8 @@
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="2" t="inlineStr"/>
-      <c r="AD16" s="28" t="n"/>
-      <c r="AE16" s="5" t="n"/>
-      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="n"/>
+      <c r="AF16" s="2" t="n"/>
       <c r="AG16" s="4" t="n"/>
       <c r="AH16" s="4" t="n"/>
       <c r="AI16" s="4" t="n"/>
@@ -3596,10 +3216,8 @@
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="28" t="n"/>
-      <c r="AT16" s="5" t="n"/>
-      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="n"/>
+      <c r="AU16" s="2" t="n"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -3611,10 +3229,8 @@
       <c r="BD16" s="4" t="n"/>
       <c r="BE16" s="4" t="n"/>
       <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="2" t="inlineStr"/>
-      <c r="BH16" s="28" t="n"/>
-      <c r="BI16" s="5" t="n"/>
-      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BG16" s="2" t="n"/>
+      <c r="BJ16" s="2" t="n"/>
       <c r="BK16" s="4" t="n"/>
       <c r="BL16" s="4" t="n"/>
       <c r="BM16" s="4" t="n"/>
@@ -3626,10 +3242,8 @@
       <c r="BS16" s="4" t="n"/>
       <c r="BT16" s="4" t="n"/>
       <c r="BU16" s="4" t="n"/>
-      <c r="BV16" s="2" t="inlineStr"/>
-      <c r="BW16" s="28" t="n"/>
-      <c r="BX16" s="5" t="n"/>
-      <c r="BY16" s="2" t="inlineStr"/>
+      <c r="BV16" s="2" t="n"/>
+      <c r="BY16" s="2" t="n"/>
       <c r="BZ16" s="4" t="n"/>
       <c r="CA16" s="4" t="n"/>
       <c r="CB16" s="4" t="n"/>
@@ -3641,12 +3255,21 @@
       <c r="CH16" s="4" t="n"/>
       <c r="CI16" s="4" t="n"/>
       <c r="CJ16" s="4" t="n"/>
-      <c r="CK16" s="2" t="inlineStr"/>
-      <c r="CL16" s="28" t="n"/>
-      <c r="CN16" s="2" t="inlineStr"/>
+      <c r="CK16" s="2" t="n"/>
+      <c r="CN16" s="2" t="n"/>
       <c r="CP16" s="11" t="n"/>
       <c r="CQ16" s="7" t="n"/>
       <c r="CR16" s="12" t="n"/>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU16" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3683,10 +3306,8 @@
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="2" t="inlineStr"/>
-      <c r="AD17" s="28" t="n"/>
-      <c r="AE17" s="5" t="n"/>
-      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="n"/>
+      <c r="AF17" s="2" t="n"/>
       <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
@@ -3698,10 +3319,8 @@
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="28" t="n"/>
-      <c r="AT17" s="5" t="n"/>
-      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="n"/>
+      <c r="AU17" s="2" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
@@ -3713,10 +3332,8 @@
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="2" t="inlineStr"/>
-      <c r="BH17" s="28" t="n"/>
-      <c r="BI17" s="5" t="n"/>
-      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BG17" s="2" t="n"/>
+      <c r="BJ17" s="2" t="n"/>
       <c r="BK17" s="4" t="n"/>
       <c r="BL17" s="4" t="n"/>
       <c r="BM17" s="4" t="n"/>
@@ -3728,10 +3345,8 @@
       <c r="BS17" s="4" t="n"/>
       <c r="BT17" s="4" t="n"/>
       <c r="BU17" s="4" t="n"/>
-      <c r="BV17" s="2" t="inlineStr"/>
-      <c r="BW17" s="28" t="n"/>
-      <c r="BX17" s="5" t="n"/>
-      <c r="BY17" s="2" t="inlineStr"/>
+      <c r="BV17" s="2" t="n"/>
+      <c r="BY17" s="2" t="n"/>
       <c r="BZ17" s="4" t="n"/>
       <c r="CA17" s="4" t="n"/>
       <c r="CB17" s="4" t="n"/>
@@ -3743,12 +3358,21 @@
       <c r="CH17" s="4" t="n"/>
       <c r="CI17" s="4" t="n"/>
       <c r="CJ17" s="4" t="n"/>
-      <c r="CK17" s="2" t="inlineStr"/>
-      <c r="CL17" s="28" t="n"/>
-      <c r="CN17" s="2" t="inlineStr"/>
+      <c r="CK17" s="2" t="n"/>
+      <c r="CN17" s="2" t="n"/>
       <c r="CP17" s="11" t="n"/>
       <c r="CQ17" s="7" t="n"/>
       <c r="CR17" s="12" t="n"/>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU17" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3786,10 +3410,8 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="2" t="inlineStr"/>
-      <c r="AD18" s="28" t="n"/>
-      <c r="AE18" s="5" t="n"/>
-      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="n"/>
+      <c r="AF18" s="2" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
@@ -3801,10 +3423,8 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="2" t="inlineStr"/>
-      <c r="AS18" s="28" t="n"/>
-      <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="n"/>
+      <c r="AU18" s="2" t="n"/>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
@@ -3816,10 +3436,8 @@
       <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="2" t="inlineStr"/>
-      <c r="BH18" s="28" t="n"/>
-      <c r="BI18" s="5" t="n"/>
-      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BG18" s="2" t="n"/>
+      <c r="BJ18" s="2" t="n"/>
       <c r="BK18" s="4" t="n"/>
       <c r="BL18" s="4" t="n"/>
       <c r="BM18" s="4" t="n"/>
@@ -3831,10 +3449,8 @@
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
       <c r="BU18" s="4" t="n"/>
-      <c r="BV18" s="2" t="inlineStr"/>
-      <c r="BW18" s="28" t="n"/>
-      <c r="BX18" s="5" t="n"/>
-      <c r="BY18" s="2" t="inlineStr"/>
+      <c r="BV18" s="2" t="n"/>
+      <c r="BY18" s="2" t="n"/>
       <c r="BZ18" s="4" t="n"/>
       <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
@@ -3846,12 +3462,21 @@
       <c r="CH18" s="4" t="n"/>
       <c r="CI18" s="4" t="n"/>
       <c r="CJ18" s="4" t="n"/>
-      <c r="CK18" s="2" t="inlineStr"/>
-      <c r="CL18" s="28" t="n"/>
-      <c r="CN18" s="2" t="inlineStr"/>
+      <c r="CK18" s="2" t="n"/>
+      <c r="CN18" s="2" t="n"/>
       <c r="CP18" s="11" t="n"/>
       <c r="CQ18" s="7" t="n"/>
       <c r="CR18" s="12" t="n"/>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU18" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3926,14 +3551,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD19" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -3977,14 +3594,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS19" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU19" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -4026,14 +3635,6 @@
       <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH19" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ19" s="2" t="inlineStr">
@@ -4077,14 +3678,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW19" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY19" s="2" t="inlineStr">
         <is>
           <t>011</t>
@@ -4126,14 +3719,6 @@
       <c r="CK19" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL19" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN19" s="2" t="inlineStr">
@@ -4190,10 +3775,8 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="2" t="inlineStr"/>
-      <c r="AD20" s="28" t="n"/>
-      <c r="AE20" s="5" t="n"/>
-      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="n"/>
+      <c r="AF20" s="2" t="n"/>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -4205,10 +3788,8 @@
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="2" t="inlineStr"/>
-      <c r="AS20" s="28" t="n"/>
-      <c r="AT20" s="5" t="n"/>
-      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="n"/>
+      <c r="AU20" s="2" t="n"/>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
@@ -4220,10 +3801,8 @@
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="2" t="inlineStr"/>
-      <c r="BH20" s="28" t="n"/>
-      <c r="BI20" s="5" t="n"/>
-      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BG20" s="2" t="n"/>
+      <c r="BJ20" s="2" t="n"/>
       <c r="BK20" s="4" t="n"/>
       <c r="BL20" s="4" t="n"/>
       <c r="BM20" s="4" t="n"/>
@@ -4235,10 +3814,8 @@
       <c r="BS20" s="4" t="n"/>
       <c r="BT20" s="4" t="n"/>
       <c r="BU20" s="4" t="n"/>
-      <c r="BV20" s="2" t="inlineStr"/>
-      <c r="BW20" s="28" t="n"/>
-      <c r="BX20" s="5" t="n"/>
-      <c r="BY20" s="2" t="inlineStr"/>
+      <c r="BV20" s="2" t="n"/>
+      <c r="BY20" s="2" t="n"/>
       <c r="BZ20" s="4" t="n"/>
       <c r="CA20" s="4" t="n"/>
       <c r="CB20" s="4" t="n"/>
@@ -4250,12 +3827,21 @@
       <c r="CH20" s="4" t="n"/>
       <c r="CI20" s="4" t="n"/>
       <c r="CJ20" s="4" t="n"/>
-      <c r="CK20" s="2" t="inlineStr"/>
-      <c r="CL20" s="28" t="n"/>
-      <c r="CN20" s="2" t="inlineStr"/>
+      <c r="CK20" s="2" t="n"/>
+      <c r="CN20" s="2" t="n"/>
       <c r="CP20" s="11" t="n"/>
       <c r="CQ20" s="7" t="n"/>
       <c r="CR20" s="12" t="n"/>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU20" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4330,14 +3916,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
           <t>00010</t>
@@ -4381,14 +3959,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT21" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU21" s="2" t="inlineStr">
         <is>
           <t>000010</t>
@@ -4430,14 +4000,6 @@
       <c r="BG21" s="2" t="inlineStr">
         <is>
           <t>AI</t>
-        </is>
-      </c>
-      <c r="BH21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI21" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ21" s="2" t="inlineStr">
@@ -4481,14 +4043,6 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="BW21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX21" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY21" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -4530,14 +4084,6 @@
       <c r="CK21" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM21" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN21" s="2" t="inlineStr">
@@ -4584,10 +4130,8 @@
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
       <c r="AB22" s="4" t="n"/>
-      <c r="AC22" s="2" t="inlineStr"/>
-      <c r="AD22" s="28" t="n"/>
-      <c r="AE22" s="5" t="n"/>
-      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="n"/>
+      <c r="AF22" s="2" t="n"/>
       <c r="AG22" s="4" t="n"/>
       <c r="AH22" s="4" t="n"/>
       <c r="AI22" s="4" t="n"/>
@@ -4599,10 +4143,8 @@
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
-      <c r="AR22" s="2" t="inlineStr"/>
-      <c r="AS22" s="28" t="n"/>
-      <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="n"/>
+      <c r="AU22" s="2" t="n"/>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
@@ -4614,10 +4156,8 @@
       <c r="BD22" s="4" t="n"/>
       <c r="BE22" s="4" t="n"/>
       <c r="BF22" s="4" t="n"/>
-      <c r="BG22" s="2" t="inlineStr"/>
-      <c r="BH22" s="28" t="n"/>
-      <c r="BI22" s="5" t="n"/>
-      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BG22" s="2" t="n"/>
+      <c r="BJ22" s="2" t="n"/>
       <c r="BK22" s="4" t="n"/>
       <c r="BL22" s="4" t="n"/>
       <c r="BM22" s="4" t="n"/>
@@ -4629,10 +4169,8 @@
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
       <c r="BU22" s="4" t="n"/>
-      <c r="BV22" s="2" t="inlineStr"/>
-      <c r="BW22" s="28" t="n"/>
-      <c r="BX22" s="5" t="n"/>
-      <c r="BY22" s="2" t="inlineStr"/>
+      <c r="BV22" s="2" t="n"/>
+      <c r="BY22" s="2" t="n"/>
       <c r="BZ22" s="4" t="n"/>
       <c r="CA22" s="4" t="n"/>
       <c r="CB22" s="4" t="n"/>
@@ -4644,12 +4182,21 @@
       <c r="CH22" s="4" t="n"/>
       <c r="CI22" s="4" t="n"/>
       <c r="CJ22" s="4" t="n"/>
-      <c r="CK22" s="2" t="inlineStr"/>
-      <c r="CL22" s="28" t="n"/>
-      <c r="CN22" s="2" t="inlineStr"/>
+      <c r="CK22" s="2" t="n"/>
+      <c r="CN22" s="2" t="n"/>
       <c r="CP22" s="11" t="n"/>
       <c r="CQ22" s="7" t="n"/>
       <c r="CR22" s="12" t="n"/>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU22" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4687,10 +4234,8 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="2" t="inlineStr"/>
-      <c r="AD23" s="28" t="n"/>
-      <c r="AE23" s="5" t="n"/>
-      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="n"/>
+      <c r="AF23" s="2" t="n"/>
       <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
       <c r="AI23" s="4" t="n"/>
@@ -4702,10 +4247,8 @@
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
-      <c r="AR23" s="2" t="inlineStr"/>
-      <c r="AS23" s="28" t="n"/>
-      <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="2" t="inlineStr"/>
+      <c r="AR23" s="2" t="n"/>
+      <c r="AU23" s="2" t="n"/>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
@@ -4717,10 +4260,8 @@
       <c r="BD23" s="4" t="n"/>
       <c r="BE23" s="4" t="n"/>
       <c r="BF23" s="4" t="n"/>
-      <c r="BG23" s="2" t="inlineStr"/>
-      <c r="BH23" s="28" t="n"/>
-      <c r="BI23" s="5" t="n"/>
-      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BG23" s="2" t="n"/>
+      <c r="BJ23" s="2" t="n"/>
       <c r="BK23" s="4" t="n"/>
       <c r="BL23" s="4" t="n"/>
       <c r="BM23" s="4" t="n"/>
@@ -4732,10 +4273,8 @@
       <c r="BS23" s="4" t="n"/>
       <c r="BT23" s="4" t="n"/>
       <c r="BU23" s="4" t="n"/>
-      <c r="BV23" s="2" t="inlineStr"/>
-      <c r="BW23" s="28" t="n"/>
-      <c r="BX23" s="5" t="n"/>
-      <c r="BY23" s="2" t="inlineStr"/>
+      <c r="BV23" s="2" t="n"/>
+      <c r="BY23" s="2" t="n"/>
       <c r="BZ23" s="4" t="n"/>
       <c r="CA23" s="4" t="n"/>
       <c r="CB23" s="4" t="n"/>
@@ -4747,13 +4286,21 @@
       <c r="CH23" s="4" t="n"/>
       <c r="CI23" s="4" t="n"/>
       <c r="CJ23" s="4" t="n"/>
-      <c r="CK23" s="2" t="inlineStr"/>
-      <c r="CL23" s="28" t="n"/>
-      <c r="CM23" s="5" t="n"/>
-      <c r="CN23" s="2" t="inlineStr"/>
+      <c r="CK23" s="2" t="n"/>
+      <c r="CN23" s="2" t="n"/>
       <c r="CP23" s="11" t="n"/>
       <c r="CQ23" s="7" t="n"/>
       <c r="CR23" s="12" t="n"/>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU23" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4830,14 +4377,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -4881,14 +4420,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT24" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU24" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -4930,14 +4461,6 @@
       <c r="BG24" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI24" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ24" s="2" t="inlineStr">
@@ -4981,14 +4504,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX24" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY24" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -5030,14 +4545,6 @@
       <c r="CK24" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL24" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM24" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN24" s="2" t="inlineStr">
@@ -5134,14 +4641,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD25" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE25" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF25" s="2" t="inlineStr">
         <is>
           <t>01111</t>
@@ -5185,14 +4684,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS25" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT25" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU25" s="2" t="inlineStr">
         <is>
           <t>001111</t>
@@ -5234,14 +4725,6 @@
       <c r="BG25" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH25" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI25" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ25" s="2" t="inlineStr">
@@ -5285,14 +4768,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW25" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX25" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY25" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -5334,14 +4809,6 @@
       <c r="CK25" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL25" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM25" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN25" s="2" t="inlineStr">
@@ -5392,10 +4859,8 @@
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
       <c r="AB26" s="4" t="n"/>
-      <c r="AC26" s="2" t="inlineStr"/>
-      <c r="AD26" s="28" t="n"/>
-      <c r="AE26" s="5" t="n"/>
-      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
@@ -5407,10 +4872,8 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="2" t="inlineStr"/>
-      <c r="AS26" s="28" t="n"/>
-      <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AR26" s="2" t="n"/>
+      <c r="AU26" s="2" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
       <c r="AX26" s="4" t="n"/>
@@ -5422,10 +4885,8 @@
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
-      <c r="BG26" s="2" t="inlineStr"/>
-      <c r="BH26" s="28" t="n"/>
-      <c r="BI26" s="5" t="n"/>
-      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BG26" s="2" t="n"/>
+      <c r="BJ26" s="2" t="n"/>
       <c r="BK26" s="4" t="n"/>
       <c r="BL26" s="4" t="n"/>
       <c r="BM26" s="4" t="n"/>
@@ -5437,10 +4898,8 @@
       <c r="BS26" s="4" t="n"/>
       <c r="BT26" s="4" t="n"/>
       <c r="BU26" s="4" t="n"/>
-      <c r="BV26" s="2" t="inlineStr"/>
-      <c r="BW26" s="28" t="n"/>
-      <c r="BX26" s="5" t="n"/>
-      <c r="BY26" s="2" t="inlineStr"/>
+      <c r="BV26" s="2" t="n"/>
+      <c r="BY26" s="2" t="n"/>
       <c r="BZ26" s="4" t="n"/>
       <c r="CA26" s="4" t="n"/>
       <c r="CB26" s="4" t="n"/>
@@ -5452,13 +4911,21 @@
       <c r="CH26" s="4" t="n"/>
       <c r="CI26" s="4" t="n"/>
       <c r="CJ26" s="4" t="n"/>
-      <c r="CK26" s="2" t="inlineStr"/>
-      <c r="CL26" s="28" t="n"/>
-      <c r="CM26" s="5" t="n"/>
-      <c r="CN26" s="2" t="inlineStr"/>
+      <c r="CK26" s="2" t="n"/>
+      <c r="CN26" s="2" t="n"/>
       <c r="CP26" s="11" t="n"/>
       <c r="CQ26" s="7" t="n"/>
       <c r="CR26" s="12" t="n"/>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU26" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5496,10 +4963,8 @@
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="2" t="inlineStr"/>
-      <c r="AD27" s="28" t="n"/>
-      <c r="AE27" s="5" t="n"/>
-      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="n"/>
+      <c r="AF27" s="2" t="n"/>
       <c r="AG27" s="4" t="n"/>
       <c r="AH27" s="4" t="n"/>
       <c r="AI27" s="4" t="n"/>
@@ -5511,10 +4976,8 @@
       <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
-      <c r="AR27" s="2" t="inlineStr"/>
-      <c r="AS27" s="28" t="n"/>
-      <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AR27" s="2" t="n"/>
+      <c r="AU27" s="2" t="n"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
@@ -5526,10 +4989,8 @@
       <c r="BD27" s="4" t="n"/>
       <c r="BE27" s="4" t="n"/>
       <c r="BF27" s="4" t="n"/>
-      <c r="BG27" s="2" t="inlineStr"/>
-      <c r="BH27" s="28" t="n"/>
-      <c r="BI27" s="5" t="n"/>
-      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BG27" s="2" t="n"/>
+      <c r="BJ27" s="2" t="n"/>
       <c r="BK27" s="4" t="n"/>
       <c r="BL27" s="4" t="n"/>
       <c r="BM27" s="4" t="n"/>
@@ -5541,10 +5002,8 @@
       <c r="BS27" s="4" t="n"/>
       <c r="BT27" s="4" t="n"/>
       <c r="BU27" s="4" t="n"/>
-      <c r="BV27" s="2" t="inlineStr"/>
-      <c r="BW27" s="28" t="n"/>
-      <c r="BX27" s="5" t="n"/>
-      <c r="BY27" s="2" t="inlineStr"/>
+      <c r="BV27" s="2" t="n"/>
+      <c r="BY27" s="2" t="n"/>
       <c r="BZ27" s="4" t="n"/>
       <c r="CA27" s="4" t="n"/>
       <c r="CB27" s="4" t="n"/>
@@ -5556,12 +5015,21 @@
       <c r="CH27" s="4" t="n"/>
       <c r="CI27" s="4" t="n"/>
       <c r="CJ27" s="4" t="n"/>
-      <c r="CK27" s="2" t="inlineStr"/>
-      <c r="CL27" s="28" t="n"/>
-      <c r="CN27" s="2" t="inlineStr"/>
+      <c r="CK27" s="2" t="n"/>
+      <c r="CN27" s="2" t="n"/>
       <c r="CP27" s="11" t="n"/>
       <c r="CQ27" s="7" t="n"/>
       <c r="CR27" s="12" t="n"/>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU27" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5595,10 +5063,6 @@
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="2" t="inlineStr"/>
-      <c r="AD28" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" s="5" t="n"/>
       <c r="AF28" s="2" t="inlineStr">
         <is>
           <t>10111</t>
@@ -5616,10 +5080,6 @@
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
       <c r="AR28" s="2" t="inlineStr"/>
-      <c r="AS28" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT28" s="5" t="n"/>
       <c r="AU28" s="2" t="inlineStr">
         <is>
           <t>111011</t>
@@ -5637,10 +5097,6 @@
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="2" t="inlineStr"/>
-      <c r="BH28" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI28" s="5" t="n"/>
       <c r="BJ28" s="2" t="inlineStr">
         <is>
           <t>11111</t>
@@ -5658,8 +5114,6 @@
       <c r="BT28" s="4" t="n"/>
       <c r="BU28" s="4" t="n"/>
       <c r="BV28" s="2" t="inlineStr"/>
-      <c r="BW28" s="28" t="n"/>
-      <c r="BX28" s="5" t="n"/>
       <c r="BY28" s="2" t="inlineStr"/>
       <c r="BZ28" s="4" t="n"/>
       <c r="CA28" s="4" t="n"/>
@@ -5673,9 +5127,6 @@
       <c r="CI28" s="4" t="n"/>
       <c r="CJ28" s="4" t="n"/>
       <c r="CK28" s="2" t="inlineStr"/>
-      <c r="CL28" s="28" t="n">
-        <v>1</v>
-      </c>
       <c r="CN28" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -5721,10 +5172,8 @@
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
-      <c r="AC29" s="2" t="inlineStr"/>
-      <c r="AD29" s="28" t="n"/>
-      <c r="AE29" s="5" t="n"/>
-      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="n"/>
+      <c r="AF29" s="2" t="n"/>
       <c r="AG29" s="4" t="n"/>
       <c r="AH29" s="4" t="n"/>
       <c r="AI29" s="4" t="n"/>
@@ -5736,10 +5185,8 @@
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
-      <c r="AR29" s="2" t="inlineStr"/>
-      <c r="AS29" s="28" t="n"/>
-      <c r="AT29" s="5" t="n"/>
-      <c r="AU29" s="2" t="inlineStr"/>
+      <c r="AR29" s="2" t="n"/>
+      <c r="AU29" s="2" t="n"/>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
@@ -5751,10 +5198,8 @@
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
-      <c r="BG29" s="2" t="inlineStr"/>
-      <c r="BH29" s="28" t="n"/>
-      <c r="BI29" s="5" t="n"/>
-      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BG29" s="2" t="n"/>
+      <c r="BJ29" s="2" t="n"/>
       <c r="BK29" s="4" t="n"/>
       <c r="BL29" s="4" t="n"/>
       <c r="BM29" s="4" t="n"/>
@@ -5766,10 +5211,8 @@
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
       <c r="BU29" s="4" t="n"/>
-      <c r="BV29" s="2" t="inlineStr"/>
-      <c r="BW29" s="28" t="n"/>
-      <c r="BX29" s="5" t="n"/>
-      <c r="BY29" s="2" t="inlineStr"/>
+      <c r="BV29" s="2" t="n"/>
+      <c r="BY29" s="2" t="n"/>
       <c r="BZ29" s="4" t="n"/>
       <c r="CA29" s="4" t="n"/>
       <c r="CB29" s="4" t="n"/>
@@ -5781,13 +5224,21 @@
       <c r="CH29" s="4" t="n"/>
       <c r="CI29" s="4" t="n"/>
       <c r="CJ29" s="4" t="n"/>
-      <c r="CK29" s="2" t="inlineStr"/>
-      <c r="CL29" s="28" t="n"/>
-      <c r="CM29" s="5" t="n"/>
-      <c r="CN29" s="2" t="inlineStr"/>
+      <c r="CK29" s="2" t="n"/>
+      <c r="CN29" s="2" t="n"/>
       <c r="CP29" s="11" t="n"/>
       <c r="CQ29" s="7" t="n"/>
       <c r="CR29" s="12" t="n"/>
+      <c r="CS29" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU29" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5838,14 +5289,6 @@
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="2" t="inlineStr"/>
-      <c r="AD30" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE30" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF30" s="2" t="inlineStr">
         <is>
           <t>00101</t>
@@ -5889,14 +5332,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS30" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT30" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU30" s="2" t="inlineStr">
         <is>
           <t>000100</t>
@@ -5938,14 +5373,6 @@
       <c r="BG30" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH30" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI30" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ30" s="2" t="inlineStr">
@@ -5989,14 +5416,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW30" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX30" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY30" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -6038,14 +5457,6 @@
       <c r="CK30" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL30" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM30" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN30" s="2" t="inlineStr">
@@ -6140,14 +5551,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE31" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF31" s="2" t="inlineStr">
         <is>
           <t>00100</t>
@@ -6191,14 +5594,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU31" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -6240,14 +5635,6 @@
       <c r="BG31" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI31" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ31" s="2" t="inlineStr">
@@ -6291,14 +5678,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX31" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY31" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -6340,14 +5719,6 @@
       <c r="CK31" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM31" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN31" s="2" t="inlineStr">
@@ -6405,10 +5776,8 @@
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="2" t="inlineStr"/>
-      <c r="AD32" s="28" t="n"/>
-      <c r="AE32" s="5" t="n"/>
-      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="n"/>
+      <c r="AF32" s="2" t="n"/>
       <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="n"/>
@@ -6420,10 +5789,8 @@
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="2" t="inlineStr"/>
-      <c r="AS32" s="28" t="n"/>
-      <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="2" t="inlineStr"/>
+      <c r="AR32" s="2" t="n"/>
+      <c r="AU32" s="2" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
@@ -6435,10 +5802,8 @@
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="2" t="inlineStr"/>
-      <c r="BH32" s="28" t="n"/>
-      <c r="BI32" s="5" t="n"/>
-      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BG32" s="2" t="n"/>
+      <c r="BJ32" s="2" t="n"/>
       <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
       <c r="BM32" s="4" t="n"/>
@@ -6450,10 +5815,8 @@
       <c r="BS32" s="4" t="n"/>
       <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
-      <c r="BV32" s="2" t="inlineStr"/>
-      <c r="BW32" s="28" t="n"/>
-      <c r="BX32" s="5" t="n"/>
-      <c r="BY32" s="2" t="inlineStr"/>
+      <c r="BV32" s="2" t="n"/>
+      <c r="BY32" s="2" t="n"/>
       <c r="BZ32" s="4" t="n"/>
       <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
@@ -6465,13 +5828,21 @@
       <c r="CH32" s="4" t="n"/>
       <c r="CI32" s="4" t="n"/>
       <c r="CJ32" s="4" t="n"/>
-      <c r="CK32" s="2" t="inlineStr"/>
-      <c r="CL32" s="28" t="n"/>
-      <c r="CM32" s="5" t="n"/>
-      <c r="CN32" s="2" t="inlineStr"/>
+      <c r="CK32" s="2" t="n"/>
+      <c r="CN32" s="2" t="n"/>
       <c r="CP32" s="11" t="n"/>
       <c r="CQ32" s="7" t="n"/>
       <c r="CR32" s="12" t="n"/>
+      <c r="CS32" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU32" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6508,10 +5879,8 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="2" t="inlineStr"/>
-      <c r="AD33" s="28" t="n"/>
-      <c r="AE33" s="5" t="n"/>
-      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="n"/>
+      <c r="AF33" s="2" t="n"/>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
@@ -6523,10 +5892,8 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="2" t="inlineStr"/>
-      <c r="AS33" s="28" t="n"/>
-      <c r="AT33" s="5" t="n"/>
-      <c r="AU33" s="2" t="inlineStr"/>
+      <c r="AR33" s="2" t="n"/>
+      <c r="AU33" s="2" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
@@ -6538,10 +5905,8 @@
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
-      <c r="BG33" s="2" t="inlineStr"/>
-      <c r="BH33" s="28" t="n"/>
-      <c r="BI33" s="5" t="n"/>
-      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BG33" s="2" t="n"/>
+      <c r="BJ33" s="2" t="n"/>
       <c r="BK33" s="4" t="n"/>
       <c r="BL33" s="4" t="n"/>
       <c r="BM33" s="4" t="n"/>
@@ -6553,10 +5918,8 @@
       <c r="BS33" s="4" t="n"/>
       <c r="BT33" s="4" t="n"/>
       <c r="BU33" s="4" t="n"/>
-      <c r="BV33" s="2" t="inlineStr"/>
-      <c r="BW33" s="28" t="n"/>
-      <c r="BX33" s="5" t="n"/>
-      <c r="BY33" s="2" t="inlineStr"/>
+      <c r="BV33" s="2" t="n"/>
+      <c r="BY33" s="2" t="n"/>
       <c r="BZ33" s="4" t="n"/>
       <c r="CA33" s="4" t="n"/>
       <c r="CB33" s="4" t="n"/>
@@ -6568,12 +5931,21 @@
       <c r="CH33" s="4" t="n"/>
       <c r="CI33" s="4" t="n"/>
       <c r="CJ33" s="4" t="n"/>
-      <c r="CK33" s="2" t="inlineStr"/>
-      <c r="CL33" s="28" t="n"/>
-      <c r="CN33" s="2" t="inlineStr"/>
+      <c r="CK33" s="2" t="n"/>
+      <c r="CN33" s="2" t="n"/>
       <c r="CP33" s="11" t="n"/>
       <c r="CQ33" s="7" t="n"/>
       <c r="CR33" s="12" t="n"/>
+      <c r="CS33" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU33" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6611,10 +5983,8 @@
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
-      <c r="AC34" s="2" t="inlineStr"/>
-      <c r="AD34" s="28" t="n"/>
-      <c r="AE34" s="5" t="n"/>
-      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="n"/>
+      <c r="AF34" s="2" t="n"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
       <c r="AI34" s="4" t="n"/>
@@ -6626,10 +5996,8 @@
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
-      <c r="AR34" s="2" t="inlineStr"/>
-      <c r="AS34" s="28" t="n"/>
-      <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="2" t="inlineStr"/>
+      <c r="AR34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -6641,10 +6009,8 @@
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
-      <c r="BG34" s="2" t="inlineStr"/>
-      <c r="BH34" s="28" t="n"/>
-      <c r="BI34" s="5" t="n"/>
-      <c r="BJ34" s="2" t="inlineStr"/>
+      <c r="BG34" s="2" t="n"/>
+      <c r="BJ34" s="2" t="n"/>
       <c r="BK34" s="4" t="n"/>
       <c r="BL34" s="4" t="n"/>
       <c r="BM34" s="4" t="n"/>
@@ -6656,10 +6022,8 @@
       <c r="BS34" s="4" t="n"/>
       <c r="BT34" s="4" t="n"/>
       <c r="BU34" s="4" t="n"/>
-      <c r="BV34" s="2" t="inlineStr"/>
-      <c r="BW34" s="28" t="n"/>
-      <c r="BX34" s="5" t="n"/>
-      <c r="BY34" s="2" t="inlineStr"/>
+      <c r="BV34" s="2" t="n"/>
+      <c r="BY34" s="2" t="n"/>
       <c r="BZ34" s="4" t="n"/>
       <c r="CA34" s="4" t="n"/>
       <c r="CB34" s="4" t="n"/>
@@ -6671,12 +6035,21 @@
       <c r="CH34" s="4" t="n"/>
       <c r="CI34" s="4" t="n"/>
       <c r="CJ34" s="4" t="n"/>
-      <c r="CK34" s="2" t="inlineStr"/>
-      <c r="CL34" s="28" t="n"/>
-      <c r="CN34" s="2" t="inlineStr"/>
+      <c r="CK34" s="2" t="n"/>
+      <c r="CN34" s="2" t="n"/>
       <c r="CP34" s="11" t="n"/>
       <c r="CQ34" s="7" t="n"/>
       <c r="CR34" s="12" t="n"/>
+      <c r="CS34" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU34" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6715,10 +6088,8 @@
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="2" t="inlineStr"/>
-      <c r="AD35" s="28" t="n"/>
-      <c r="AE35" s="5" t="n"/>
-      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="n"/>
+      <c r="AF35" s="2" t="n"/>
       <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="n"/>
@@ -6730,10 +6101,8 @@
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
-      <c r="AR35" s="2" t="inlineStr"/>
-      <c r="AS35" s="28" t="n"/>
-      <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="2" t="inlineStr"/>
+      <c r="AR35" s="2" t="n"/>
+      <c r="AU35" s="2" t="n"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
@@ -6745,10 +6114,8 @@
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
-      <c r="BG35" s="2" t="inlineStr"/>
-      <c r="BH35" s="28" t="n"/>
-      <c r="BI35" s="5" t="n"/>
-      <c r="BJ35" s="2" t="inlineStr"/>
+      <c r="BG35" s="2" t="n"/>
+      <c r="BJ35" s="2" t="n"/>
       <c r="BK35" s="4" t="n"/>
       <c r="BL35" s="4" t="n"/>
       <c r="BM35" s="4" t="n"/>
@@ -6760,10 +6127,8 @@
       <c r="BS35" s="4" t="n"/>
       <c r="BT35" s="4" t="n"/>
       <c r="BU35" s="4" t="n"/>
-      <c r="BV35" s="2" t="inlineStr"/>
-      <c r="BW35" s="28" t="n"/>
-      <c r="BX35" s="5" t="n"/>
-      <c r="BY35" s="2" t="inlineStr"/>
+      <c r="BV35" s="2" t="n"/>
+      <c r="BY35" s="2" t="n"/>
       <c r="BZ35" s="4" t="n"/>
       <c r="CA35" s="4" t="n"/>
       <c r="CB35" s="4" t="n"/>
@@ -6775,13 +6140,22 @@
       <c r="CH35" s="4" t="n"/>
       <c r="CI35" s="4" t="n"/>
       <c r="CJ35" s="4" t="n"/>
-      <c r="CK35" s="2" t="inlineStr"/>
-      <c r="CL35" s="28" t="n"/>
-      <c r="CN35" s="2" t="inlineStr"/>
+      <c r="CK35" s="2" t="n"/>
+      <c r="CN35" s="2" t="n"/>
       <c r="CO35" s="6" t="n"/>
       <c r="CP35" s="11" t="n"/>
       <c r="CQ35" s="7" t="n"/>
       <c r="CR35" s="12" t="n"/>
+      <c r="CS35" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU35" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6821,14 +6195,6 @@
           <t>Scr</t>
         </is>
       </c>
-      <c r="AD36" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF36" s="2" t="inlineStr">
         <is>
           <t>11011</t>
@@ -6872,14 +6238,6 @@
           <t>C3&lt;</t>
         </is>
       </c>
-      <c r="AS36" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU36" s="2" t="inlineStr">
         <is>
           <t>010101</t>
@@ -6921,14 +6279,6 @@
       <c r="BG36" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH36" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ36" s="2" t="inlineStr">
@@ -6972,14 +6322,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW36" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY36" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -7021,14 +6363,6 @@
       <c r="CK36" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL36" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN36" s="2" t="inlineStr">
@@ -7085,10 +6419,8 @@
       <c r="Z37" s="4" t="n"/>
       <c r="AA37" s="4" t="n"/>
       <c r="AB37" s="4" t="n"/>
-      <c r="AC37" s="2" t="inlineStr"/>
-      <c r="AD37" s="28" t="n"/>
-      <c r="AE37" s="5" t="n"/>
-      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="n"/>
+      <c r="AF37" s="2" t="n"/>
       <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
@@ -7100,10 +6432,8 @@
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="2" t="inlineStr"/>
-      <c r="AS37" s="28" t="n"/>
-      <c r="AT37" s="5" t="n"/>
-      <c r="AU37" s="2" t="inlineStr"/>
+      <c r="AR37" s="2" t="n"/>
+      <c r="AU37" s="2" t="n"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
@@ -7115,10 +6445,8 @@
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="n"/>
-      <c r="BG37" s="2" t="inlineStr"/>
-      <c r="BH37" s="28" t="n"/>
-      <c r="BI37" s="5" t="n"/>
-      <c r="BJ37" s="2" t="inlineStr"/>
+      <c r="BG37" s="2" t="n"/>
+      <c r="BJ37" s="2" t="n"/>
       <c r="BK37" s="4" t="n"/>
       <c r="BL37" s="4" t="n"/>
       <c r="BM37" s="4" t="n"/>
@@ -7130,10 +6458,8 @@
       <c r="BS37" s="4" t="n"/>
       <c r="BT37" s="4" t="n"/>
       <c r="BU37" s="4" t="n"/>
-      <c r="BV37" s="2" t="inlineStr"/>
-      <c r="BW37" s="28" t="n"/>
-      <c r="BX37" s="5" t="n"/>
-      <c r="BY37" s="2" t="inlineStr"/>
+      <c r="BV37" s="2" t="n"/>
+      <c r="BY37" s="2" t="n"/>
       <c r="BZ37" s="4" t="n"/>
       <c r="CA37" s="4" t="n"/>
       <c r="CB37" s="4" t="n"/>
@@ -7145,13 +6471,21 @@
       <c r="CH37" s="4" t="n"/>
       <c r="CI37" s="4" t="n"/>
       <c r="CJ37" s="4" t="n"/>
-      <c r="CK37" s="2" t="inlineStr"/>
-      <c r="CL37" s="28" t="n"/>
-      <c r="CM37" s="5" t="n"/>
-      <c r="CN37" s="2" t="inlineStr"/>
+      <c r="CK37" s="2" t="n"/>
+      <c r="CN37" s="2" t="n"/>
       <c r="CP37" s="11" t="n"/>
       <c r="CQ37" s="7" t="n"/>
       <c r="CR37" s="12" t="n"/>
+      <c r="CS37" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU37" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7189,10 +6523,8 @@
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
-      <c r="AC38" s="2" t="inlineStr"/>
-      <c r="AD38" s="28" t="n"/>
-      <c r="AE38" s="5" t="n"/>
-      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="n"/>
+      <c r="AF38" s="2" t="n"/>
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
@@ -7204,10 +6536,8 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="2" t="inlineStr"/>
-      <c r="AS38" s="28" t="n"/>
-      <c r="AT38" s="5" t="n"/>
-      <c r="AU38" s="2" t="inlineStr"/>
+      <c r="AR38" s="2" t="n"/>
+      <c r="AU38" s="2" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
@@ -7219,10 +6549,8 @@
       <c r="BD38" s="4" t="n"/>
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
-      <c r="BG38" s="2" t="inlineStr"/>
-      <c r="BH38" s="28" t="n"/>
-      <c r="BI38" s="5" t="n"/>
-      <c r="BJ38" s="2" t="inlineStr"/>
+      <c r="BG38" s="2" t="n"/>
+      <c r="BJ38" s="2" t="n"/>
       <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
@@ -7234,10 +6562,8 @@
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
       <c r="BU38" s="4" t="n"/>
-      <c r="BV38" s="2" t="inlineStr"/>
-      <c r="BW38" s="28" t="n"/>
-      <c r="BX38" s="5" t="n"/>
-      <c r="BY38" s="2" t="inlineStr"/>
+      <c r="BV38" s="2" t="n"/>
+      <c r="BY38" s="2" t="n"/>
       <c r="BZ38" s="4" t="n"/>
       <c r="CA38" s="4" t="n"/>
       <c r="CB38" s="4" t="n"/>
@@ -7249,12 +6575,21 @@
       <c r="CH38" s="4" t="n"/>
       <c r="CI38" s="4" t="n"/>
       <c r="CJ38" s="4" t="n"/>
-      <c r="CK38" s="2" t="inlineStr"/>
-      <c r="CL38" s="28" t="n"/>
-      <c r="CN38" s="2" t="inlineStr"/>
+      <c r="CK38" s="2" t="n"/>
+      <c r="CN38" s="2" t="n"/>
       <c r="CP38" s="11" t="n"/>
       <c r="CQ38" s="7" t="n"/>
       <c r="CR38" s="12" t="n"/>
+      <c r="CS38" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU38" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7292,10 +6627,8 @@
       <c r="Z39" s="4" t="n"/>
       <c r="AA39" s="4" t="n"/>
       <c r="AB39" s="4" t="n"/>
-      <c r="AC39" s="2" t="inlineStr"/>
-      <c r="AD39" s="28" t="n"/>
-      <c r="AE39" s="5" t="n"/>
-      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="n"/>
+      <c r="AF39" s="2" t="n"/>
       <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n"/>
       <c r="AI39" s="4" t="n"/>
@@ -7307,10 +6640,8 @@
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
-      <c r="AR39" s="2" t="inlineStr"/>
-      <c r="AS39" s="28" t="n"/>
-      <c r="AT39" s="5" t="n"/>
-      <c r="AU39" s="2" t="inlineStr"/>
+      <c r="AR39" s="2" t="n"/>
+      <c r="AU39" s="2" t="n"/>
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
@@ -7322,10 +6653,8 @@
       <c r="BD39" s="4" t="n"/>
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
-      <c r="BG39" s="2" t="inlineStr"/>
-      <c r="BH39" s="28" t="n"/>
-      <c r="BI39" s="5" t="n"/>
-      <c r="BJ39" s="2" t="inlineStr"/>
+      <c r="BG39" s="2" t="n"/>
+      <c r="BJ39" s="2" t="n"/>
       <c r="BK39" s="4" t="n"/>
       <c r="BL39" s="4" t="n"/>
       <c r="BM39" s="4" t="n"/>
@@ -7337,10 +6666,8 @@
       <c r="BS39" s="4" t="n"/>
       <c r="BT39" s="4" t="n"/>
       <c r="BU39" s="4" t="n"/>
-      <c r="BV39" s="2" t="inlineStr"/>
-      <c r="BW39" s="28" t="n"/>
-      <c r="BX39" s="5" t="n"/>
-      <c r="BY39" s="2" t="inlineStr"/>
+      <c r="BV39" s="2" t="n"/>
+      <c r="BY39" s="2" t="n"/>
       <c r="BZ39" s="4" t="n"/>
       <c r="CA39" s="4" t="n"/>
       <c r="CB39" s="4" t="n"/>
@@ -7352,13 +6679,21 @@
       <c r="CH39" s="4" t="n"/>
       <c r="CI39" s="4" t="n"/>
       <c r="CJ39" s="4" t="n"/>
-      <c r="CK39" s="2" t="inlineStr"/>
-      <c r="CL39" s="28" t="n"/>
-      <c r="CM39" s="5" t="n"/>
-      <c r="CN39" s="2" t="inlineStr"/>
+      <c r="CK39" s="2" t="n"/>
+      <c r="CN39" s="2" t="n"/>
       <c r="CP39" s="11" t="n"/>
       <c r="CQ39" s="7" t="n"/>
       <c r="CR39" s="12" t="n"/>
+      <c r="CS39" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU39" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7396,10 +6731,8 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="2" t="inlineStr"/>
-      <c r="AD40" s="28" t="n"/>
-      <c r="AE40" s="5" t="n"/>
-      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="n"/>
+      <c r="AF40" s="2" t="n"/>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -7411,10 +6744,8 @@
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="2" t="inlineStr"/>
-      <c r="AS40" s="28" t="n"/>
-      <c r="AT40" s="5" t="n"/>
-      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AR40" s="2" t="n"/>
+      <c r="AU40" s="2" t="n"/>
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
@@ -7426,10 +6757,8 @@
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
       <c r="BF40" s="4" t="n"/>
-      <c r="BG40" s="2" t="inlineStr"/>
-      <c r="BH40" s="28" t="n"/>
-      <c r="BI40" s="5" t="n"/>
-      <c r="BJ40" s="2" t="inlineStr"/>
+      <c r="BG40" s="2" t="n"/>
+      <c r="BJ40" s="2" t="n"/>
       <c r="BK40" s="4" t="n"/>
       <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="4" t="n"/>
@@ -7441,10 +6770,8 @@
       <c r="BS40" s="4" t="n"/>
       <c r="BT40" s="4" t="n"/>
       <c r="BU40" s="4" t="n"/>
-      <c r="BV40" s="2" t="inlineStr"/>
-      <c r="BW40" s="28" t="n"/>
-      <c r="BX40" s="5" t="n"/>
-      <c r="BY40" s="2" t="inlineStr"/>
+      <c r="BV40" s="2" t="n"/>
+      <c r="BY40" s="2" t="n"/>
       <c r="BZ40" s="4" t="n"/>
       <c r="CA40" s="4" t="n"/>
       <c r="CB40" s="4" t="n"/>
@@ -7456,12 +6783,21 @@
       <c r="CH40" s="4" t="n"/>
       <c r="CI40" s="4" t="n"/>
       <c r="CJ40" s="4" t="n"/>
-      <c r="CK40" s="2" t="inlineStr"/>
-      <c r="CL40" s="28" t="n"/>
-      <c r="CN40" s="2" t="inlineStr"/>
+      <c r="CK40" s="2" t="n"/>
+      <c r="CN40" s="2" t="n"/>
       <c r="CP40" s="11" t="n"/>
       <c r="CQ40" s="7" t="n"/>
       <c r="CR40" s="12" t="n"/>
+      <c r="CS40" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU40" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7519,14 +6855,6 @@
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="AD41" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="AF41" s="2" t="inlineStr">
@@ -7546,14 +6874,6 @@
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
       <c r="AR41" s="2" t="inlineStr"/>
-      <c r="AS41" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT41" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU41" s="2" t="inlineStr">
         <is>
           <t>001011</t>
@@ -7571,14 +6891,6 @@
       <c r="BE41" s="4" t="n"/>
       <c r="BF41" s="4" t="n"/>
       <c r="BG41" s="2" t="inlineStr"/>
-      <c r="BH41" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI41" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BJ41" s="2" t="inlineStr">
         <is>
           <t>01101</t>
@@ -7620,14 +6932,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW41" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX41" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="BY41" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -7667,14 +6971,6 @@
         <v>-15</v>
       </c>
       <c r="CK41" s="2" t="inlineStr"/>
-      <c r="CL41" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM41" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN41" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -7728,14 +7024,6 @@
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="2" t="inlineStr"/>
-      <c r="AD42" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF42" s="2" t="inlineStr">
         <is>
           <t>10011</t>
@@ -7753,14 +7041,6 @@
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
       <c r="AR42" s="2" t="inlineStr"/>
-      <c r="AS42" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT42" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="AU42" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -7802,14 +7082,6 @@
       <c r="BG42" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH42" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI42" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ42" s="2" t="inlineStr">
@@ -7853,14 +7125,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW42" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX42" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY42" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -7902,14 +7166,6 @@
       <c r="CK42" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL42" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM42" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN42" s="2" t="inlineStr">
@@ -7967,10 +7223,8 @@
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="4" t="n"/>
       <c r="AB43" s="4" t="n"/>
-      <c r="AC43" s="2" t="inlineStr"/>
-      <c r="AD43" s="28" t="n"/>
-      <c r="AE43" s="5" t="n"/>
-      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="n"/>
+      <c r="AF43" s="2" t="n"/>
       <c r="AG43" s="4" t="n"/>
       <c r="AH43" s="4" t="n"/>
       <c r="AI43" s="4" t="n"/>
@@ -7982,10 +7236,8 @@
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
-      <c r="AR43" s="2" t="inlineStr"/>
-      <c r="AS43" s="28" t="n"/>
-      <c r="AT43" s="5" t="n"/>
-      <c r="AU43" s="2" t="inlineStr"/>
+      <c r="AR43" s="2" t="n"/>
+      <c r="AU43" s="2" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
@@ -7997,10 +7249,8 @@
       <c r="BD43" s="4" t="n"/>
       <c r="BE43" s="4" t="n"/>
       <c r="BF43" s="4" t="n"/>
-      <c r="BG43" s="2" t="inlineStr"/>
-      <c r="BH43" s="28" t="n"/>
-      <c r="BI43" s="5" t="n"/>
-      <c r="BJ43" s="2" t="inlineStr"/>
+      <c r="BG43" s="2" t="n"/>
+      <c r="BJ43" s="2" t="n"/>
       <c r="BK43" s="4" t="n"/>
       <c r="BL43" s="4" t="n"/>
       <c r="BM43" s="4" t="n"/>
@@ -8012,10 +7262,8 @@
       <c r="BS43" s="4" t="n"/>
       <c r="BT43" s="4" t="n"/>
       <c r="BU43" s="4" t="n"/>
-      <c r="BV43" s="2" t="inlineStr"/>
-      <c r="BW43" s="28" t="n"/>
-      <c r="BX43" s="5" t="n"/>
-      <c r="BY43" s="2" t="inlineStr"/>
+      <c r="BV43" s="2" t="n"/>
+      <c r="BY43" s="2" t="n"/>
       <c r="BZ43" s="4" t="n"/>
       <c r="CA43" s="4" t="n"/>
       <c r="CB43" s="4" t="n"/>
@@ -8027,12 +7275,21 @@
       <c r="CH43" s="4" t="n"/>
       <c r="CI43" s="4" t="n"/>
       <c r="CJ43" s="4" t="n"/>
-      <c r="CK43" s="2" t="inlineStr"/>
-      <c r="CL43" s="28" t="n"/>
-      <c r="CN43" s="2" t="inlineStr"/>
+      <c r="CK43" s="2" t="n"/>
+      <c r="CN43" s="2" t="n"/>
       <c r="CP43" s="11" t="n"/>
       <c r="CQ43" s="7" t="n"/>
       <c r="CR43" s="12" t="n"/>
+      <c r="CS43" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU43" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8069,10 +7326,8 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="2" t="inlineStr"/>
-      <c r="AD44" s="28" t="n"/>
-      <c r="AE44" s="5" t="n"/>
-      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="n"/>
+      <c r="AF44" s="2" t="n"/>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
@@ -8084,10 +7339,8 @@
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
-      <c r="AR44" s="2" t="inlineStr"/>
-      <c r="AS44" s="28" t="n"/>
-      <c r="AT44" s="5" t="n"/>
-      <c r="AU44" s="2" t="inlineStr"/>
+      <c r="AR44" s="2" t="n"/>
+      <c r="AU44" s="2" t="n"/>
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
@@ -8099,10 +7352,8 @@
       <c r="BD44" s="4" t="n"/>
       <c r="BE44" s="4" t="n"/>
       <c r="BF44" s="4" t="n"/>
-      <c r="BG44" s="2" t="inlineStr"/>
-      <c r="BH44" s="28" t="n"/>
-      <c r="BI44" s="5" t="n"/>
-      <c r="BJ44" s="2" t="inlineStr"/>
+      <c r="BG44" s="2" t="n"/>
+      <c r="BJ44" s="2" t="n"/>
       <c r="BK44" s="4" t="n"/>
       <c r="BL44" s="4" t="n"/>
       <c r="BM44" s="4" t="n"/>
@@ -8114,10 +7365,8 @@
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
       <c r="BU44" s="4" t="n"/>
-      <c r="BV44" s="2" t="inlineStr"/>
-      <c r="BW44" s="28" t="n"/>
-      <c r="BX44" s="5" t="n"/>
-      <c r="BY44" s="2" t="inlineStr"/>
+      <c r="BV44" s="2" t="n"/>
+      <c r="BY44" s="2" t="n"/>
       <c r="BZ44" s="4" t="n"/>
       <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
@@ -8129,12 +7378,21 @@
       <c r="CH44" s="4" t="n"/>
       <c r="CI44" s="4" t="n"/>
       <c r="CJ44" s="4" t="n"/>
-      <c r="CK44" s="2" t="inlineStr"/>
-      <c r="CL44" s="28" t="n"/>
-      <c r="CN44" s="2" t="inlineStr"/>
+      <c r="CK44" s="2" t="n"/>
+      <c r="CN44" s="2" t="n"/>
       <c r="CP44" s="11" t="n"/>
       <c r="CQ44" s="7" t="n"/>
       <c r="CR44" s="12" t="n"/>
+      <c r="CS44" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU44" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8189,14 +7447,6 @@
           <t>Scr</t>
         </is>
       </c>
-      <c r="AD45" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF45" s="2" t="inlineStr">
         <is>
           <t>00001</t>
@@ -8240,14 +7490,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS45" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT45" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU45" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -8289,14 +7531,6 @@
       <c r="BG45" s="2" t="inlineStr">
         <is>
           <t>ID</t>
-        </is>
-      </c>
-      <c r="BH45" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI45" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ45" s="2" t="inlineStr">
@@ -8340,14 +7574,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW45" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX45" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY45" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -8389,14 +7615,6 @@
       <c r="CK45" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL45" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM45" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN45" s="2" t="inlineStr">
@@ -8460,14 +7678,6 @@
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="2" t="inlineStr"/>
-      <c r="AD46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF46" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -8511,14 +7721,6 @@
           <t>C2&lt;</t>
         </is>
       </c>
-      <c r="AS46" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT46" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU46" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -8560,14 +7762,6 @@
       <c r="BG46" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH46" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI46" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ46" s="2" t="inlineStr">
@@ -8611,14 +7805,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW46" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX46" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY46" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -8660,14 +7846,6 @@
       <c r="CK46" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL46" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM46" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN46" s="2" t="inlineStr">
@@ -8720,14 +7898,6 @@
       <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="2" t="inlineStr"/>
-      <c r="AD47" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE47" s="5" t="inlineStr">
-        <is>
-          <t>Pass'</t>
-        </is>
-      </c>
       <c r="AF47" s="2" t="inlineStr">
         <is>
           <t>11011</t>
@@ -8745,14 +7915,6 @@
       <c r="AP47" s="4" t="n"/>
       <c r="AQ47" s="4" t="n"/>
       <c r="AR47" s="2" t="inlineStr"/>
-      <c r="AS47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT47" s="5" t="inlineStr">
-        <is>
-          <t>Pass'</t>
-        </is>
-      </c>
       <c r="AU47" s="2" t="inlineStr">
         <is>
           <t>001011</t>
@@ -8770,14 +7932,6 @@
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
       <c r="BG47" s="2" t="inlineStr"/>
-      <c r="BH47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI47" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BJ47" s="2" t="inlineStr">
         <is>
           <t>01110</t>
@@ -8795,14 +7949,6 @@
       <c r="BT47" s="4" t="n"/>
       <c r="BU47" s="4" t="n"/>
       <c r="BV47" s="2" t="inlineStr"/>
-      <c r="BW47" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX47" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="BY47" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -8820,14 +7966,6 @@
       <c r="CI47" s="4" t="n"/>
       <c r="CJ47" s="4" t="n"/>
       <c r="CK47" s="2" t="inlineStr"/>
-      <c r="CL47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM47" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN47" s="2" t="inlineStr">
         <is>
           <t>010</t>
@@ -8888,14 +8026,6 @@
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
       <c r="AC48" s="2" t="inlineStr"/>
-      <c r="AD48" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE48" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF48" s="2" t="inlineStr">
         <is>
           <t>01001</t>
@@ -8939,14 +8069,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS48" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT48" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU48" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -8987,15 +8109,7 @@
       </c>
       <c r="BG48" s="2" t="inlineStr">
         <is>
-          <t>C2&gt;</t>
-        </is>
-      </c>
-      <c r="BH48" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI48" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>C1&gt;</t>
         </is>
       </c>
       <c r="BJ48" s="2" t="inlineStr">
@@ -9039,14 +8153,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW48" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX48" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY48" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -9088,14 +8194,6 @@
       <c r="CK48" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL48" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM48" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN48" s="2" t="inlineStr">
@@ -9146,10 +8244,8 @@
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
-      <c r="AC49" s="2" t="inlineStr"/>
-      <c r="AD49" s="28" t="n"/>
-      <c r="AE49" s="5" t="n"/>
-      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="n"/>
+      <c r="AF49" s="2" t="n"/>
       <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
@@ -9161,10 +8257,8 @@
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
-      <c r="AR49" s="2" t="inlineStr"/>
-      <c r="AS49" s="28" t="n"/>
-      <c r="AT49" s="5" t="n"/>
-      <c r="AU49" s="2" t="inlineStr"/>
+      <c r="AR49" s="2" t="n"/>
+      <c r="AU49" s="2" t="n"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
@@ -9176,10 +8270,8 @@
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="2" t="inlineStr"/>
-      <c r="BH49" s="28" t="n"/>
-      <c r="BI49" s="5" t="n"/>
-      <c r="BJ49" s="2" t="inlineStr"/>
+      <c r="BG49" s="2" t="n"/>
+      <c r="BJ49" s="2" t="n"/>
       <c r="BK49" s="4" t="n"/>
       <c r="BL49" s="4" t="n"/>
       <c r="BM49" s="4" t="n"/>
@@ -9191,10 +8283,8 @@
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
       <c r="BU49" s="4" t="n"/>
-      <c r="BV49" s="2" t="inlineStr"/>
-      <c r="BW49" s="28" t="n"/>
-      <c r="BX49" s="5" t="n"/>
-      <c r="BY49" s="2" t="inlineStr"/>
+      <c r="BV49" s="2" t="n"/>
+      <c r="BY49" s="2" t="n"/>
       <c r="BZ49" s="4" t="n"/>
       <c r="CA49" s="4" t="n"/>
       <c r="CB49" s="4" t="n"/>
@@ -9206,12 +8296,21 @@
       <c r="CH49" s="4" t="n"/>
       <c r="CI49" s="4" t="n"/>
       <c r="CJ49" s="4" t="n"/>
-      <c r="CK49" s="2" t="inlineStr"/>
-      <c r="CL49" s="28" t="n"/>
-      <c r="CN49" s="2" t="inlineStr"/>
+      <c r="CK49" s="2" t="n"/>
+      <c r="CN49" s="2" t="n"/>
       <c r="CP49" s="11" t="n"/>
       <c r="CQ49" s="7" t="n"/>
       <c r="CR49" s="12" t="n"/>
+      <c r="CS49" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU49" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9264,14 +8363,6 @@
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="2" t="inlineStr"/>
-      <c r="AD50" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE50" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF50" s="2" t="inlineStr">
         <is>
           <t>00011</t>
@@ -9315,14 +8406,6 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="AS50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT50" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU50" s="2" t="inlineStr">
         <is>
           <t>001110</t>
@@ -9363,15 +8446,7 @@
       </c>
       <c r="BG50" s="2" t="inlineStr">
         <is>
-          <t>C1&gt;</t>
-        </is>
-      </c>
-      <c r="BH50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI50" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
+          <t>_</t>
         </is>
       </c>
       <c r="BJ50" s="2" t="inlineStr">
@@ -9415,10 +8490,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX50" s="5" t="n"/>
       <c r="BY50" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -9460,14 +8531,6 @@
       <c r="CK50" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL50" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM50" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN50" s="2" t="inlineStr">
@@ -9555,14 +8618,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD51" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE51" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF51" s="2" t="inlineStr">
         <is>
           <t>00010</t>
@@ -9606,14 +8661,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS51" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT51" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU51" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -9655,14 +8702,6 @@
       <c r="BG51" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH51" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI51" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ51" s="2" t="inlineStr">
@@ -9706,14 +8745,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW51" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX51" s="5" t="inlineStr">
-        <is>
-          <t>Pass'</t>
-        </is>
-      </c>
       <c r="BY51" s="2" t="inlineStr">
         <is>
           <t>100</t>
@@ -9755,14 +8786,6 @@
       <c r="CK51" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL51" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM51" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN51" s="2" t="inlineStr">
@@ -9819,10 +8842,8 @@
       <c r="Z52" s="4" t="n"/>
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
-      <c r="AC52" s="2" t="inlineStr"/>
-      <c r="AD52" s="28" t="n"/>
-      <c r="AE52" s="5" t="n"/>
-      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="n"/>
+      <c r="AF52" s="2" t="n"/>
       <c r="AG52" s="4" t="n"/>
       <c r="AH52" s="4" t="n"/>
       <c r="AI52" s="4" t="n"/>
@@ -9834,10 +8855,8 @@
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
-      <c r="AR52" s="2" t="inlineStr"/>
-      <c r="AS52" s="28" t="n"/>
-      <c r="AT52" s="5" t="n"/>
-      <c r="AU52" s="2" t="inlineStr"/>
+      <c r="AR52" s="2" t="n"/>
+      <c r="AU52" s="2" t="n"/>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
@@ -9849,10 +8868,8 @@
       <c r="BD52" s="4" t="n"/>
       <c r="BE52" s="4" t="n"/>
       <c r="BF52" s="4" t="n"/>
-      <c r="BG52" s="2" t="inlineStr"/>
-      <c r="BH52" s="28" t="n"/>
-      <c r="BI52" s="5" t="n"/>
-      <c r="BJ52" s="2" t="inlineStr"/>
+      <c r="BG52" s="2" t="n"/>
+      <c r="BJ52" s="2" t="n"/>
       <c r="BK52" s="4" t="n"/>
       <c r="BL52" s="4" t="n"/>
       <c r="BM52" s="4" t="n"/>
@@ -9864,10 +8881,8 @@
       <c r="BS52" s="4" t="n"/>
       <c r="BT52" s="4" t="n"/>
       <c r="BU52" s="4" t="n"/>
-      <c r="BV52" s="2" t="inlineStr"/>
-      <c r="BW52" s="28" t="n"/>
-      <c r="BX52" s="5" t="n"/>
-      <c r="BY52" s="2" t="inlineStr"/>
+      <c r="BV52" s="2" t="n"/>
+      <c r="BY52" s="2" t="n"/>
       <c r="BZ52" s="4" t="n"/>
       <c r="CA52" s="4" t="n"/>
       <c r="CB52" s="4" t="n"/>
@@ -9879,12 +8894,21 @@
       <c r="CH52" s="4" t="n"/>
       <c r="CI52" s="4" t="n"/>
       <c r="CJ52" s="4" t="n"/>
-      <c r="CK52" s="2" t="inlineStr"/>
-      <c r="CL52" s="28" t="n"/>
-      <c r="CN52" s="2" t="inlineStr"/>
+      <c r="CK52" s="2" t="n"/>
+      <c r="CN52" s="2" t="n"/>
       <c r="CP52" s="11" t="n"/>
       <c r="CQ52" s="7" t="n"/>
       <c r="CR52" s="12" t="n"/>
+      <c r="CS52" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU52" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9922,10 +8946,8 @@
       <c r="Z53" s="4" t="n"/>
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
-      <c r="AC53" s="2" t="inlineStr"/>
-      <c r="AD53" s="28" t="n"/>
-      <c r="AE53" s="5" t="n"/>
-      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="n"/>
+      <c r="AF53" s="2" t="n"/>
       <c r="AG53" s="4" t="n"/>
       <c r="AH53" s="4" t="n"/>
       <c r="AI53" s="4" t="n"/>
@@ -9937,10 +8959,8 @@
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
-      <c r="AR53" s="2" t="inlineStr"/>
-      <c r="AS53" s="28" t="n"/>
-      <c r="AT53" s="5" t="n"/>
-      <c r="AU53" s="2" t="inlineStr"/>
+      <c r="AR53" s="2" t="n"/>
+      <c r="AU53" s="2" t="n"/>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
@@ -9952,10 +8972,8 @@
       <c r="BD53" s="4" t="n"/>
       <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
-      <c r="BG53" s="2" t="inlineStr"/>
-      <c r="BH53" s="28" t="n"/>
-      <c r="BI53" s="5" t="n"/>
-      <c r="BJ53" s="2" t="inlineStr"/>
+      <c r="BG53" s="2" t="n"/>
+      <c r="BJ53" s="2" t="n"/>
       <c r="BK53" s="4" t="n"/>
       <c r="BL53" s="4" t="n"/>
       <c r="BM53" s="4" t="n"/>
@@ -9967,10 +8985,8 @@
       <c r="BS53" s="4" t="n"/>
       <c r="BT53" s="4" t="n"/>
       <c r="BU53" s="4" t="n"/>
-      <c r="BV53" s="2" t="inlineStr"/>
-      <c r="BW53" s="28" t="n"/>
-      <c r="BX53" s="5" t="n"/>
-      <c r="BY53" s="2" t="inlineStr"/>
+      <c r="BV53" s="2" t="n"/>
+      <c r="BY53" s="2" t="n"/>
       <c r="BZ53" s="4" t="n"/>
       <c r="CA53" s="4" t="n"/>
       <c r="CB53" s="4" t="n"/>
@@ -9982,12 +8998,21 @@
       <c r="CH53" s="4" t="n"/>
       <c r="CI53" s="4" t="n"/>
       <c r="CJ53" s="4" t="n"/>
-      <c r="CK53" s="2" t="inlineStr"/>
-      <c r="CL53" s="28" t="n"/>
-      <c r="CN53" s="2" t="inlineStr"/>
+      <c r="CK53" s="2" t="n"/>
+      <c r="CN53" s="2" t="n"/>
       <c r="CP53" s="11" t="n"/>
       <c r="CQ53" s="7" t="n"/>
       <c r="CR53" s="12" t="n"/>
+      <c r="CS53" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU53" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,10 +9050,8 @@
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="28" t="n"/>
-      <c r="AE54" s="5" t="n"/>
-      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="n"/>
+      <c r="AF54" s="2" t="n"/>
       <c r="AG54" s="4" t="n"/>
       <c r="AH54" s="4" t="n"/>
       <c r="AI54" s="4" t="n"/>
@@ -10040,10 +9063,8 @@
       <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
-      <c r="AR54" s="2" t="inlineStr"/>
-      <c r="AS54" s="28" t="n"/>
-      <c r="AT54" s="5" t="n"/>
-      <c r="AU54" s="2" t="inlineStr"/>
+      <c r="AR54" s="2" t="n"/>
+      <c r="AU54" s="2" t="n"/>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
@@ -10055,10 +9076,8 @@
       <c r="BD54" s="4" t="n"/>
       <c r="BE54" s="4" t="n"/>
       <c r="BF54" s="4" t="n"/>
-      <c r="BG54" s="2" t="inlineStr"/>
-      <c r="BH54" s="28" t="n"/>
-      <c r="BI54" s="5" t="n"/>
-      <c r="BJ54" s="2" t="inlineStr"/>
+      <c r="BG54" s="2" t="n"/>
+      <c r="BJ54" s="2" t="n"/>
       <c r="BK54" s="4" t="n"/>
       <c r="BL54" s="4" t="n"/>
       <c r="BM54" s="4" t="n"/>
@@ -10070,10 +9089,8 @@
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
       <c r="BU54" s="4" t="n"/>
-      <c r="BV54" s="2" t="inlineStr"/>
-      <c r="BW54" s="28" t="n"/>
-      <c r="BX54" s="5" t="n"/>
-      <c r="BY54" s="2" t="inlineStr"/>
+      <c r="BV54" s="2" t="n"/>
+      <c r="BY54" s="2" t="n"/>
       <c r="BZ54" s="4" t="n"/>
       <c r="CA54" s="4" t="n"/>
       <c r="CB54" s="4" t="n"/>
@@ -10085,12 +9102,21 @@
       <c r="CH54" s="4" t="n"/>
       <c r="CI54" s="4" t="n"/>
       <c r="CJ54" s="4" t="n"/>
-      <c r="CK54" s="2" t="inlineStr"/>
-      <c r="CL54" s="28" t="n"/>
-      <c r="CN54" s="2" t="inlineStr"/>
+      <c r="CK54" s="2" t="n"/>
+      <c r="CN54" s="2" t="n"/>
       <c r="CP54" s="11" t="n"/>
       <c r="CQ54" s="7" t="n"/>
       <c r="CR54" s="12" t="n"/>
+      <c r="CS54" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU54" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10128,10 +9154,8 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="2" t="inlineStr"/>
-      <c r="AD55" s="28" t="n"/>
-      <c r="AE55" s="5" t="n"/>
-      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="n"/>
+      <c r="AF55" s="2" t="n"/>
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
@@ -10143,10 +9167,8 @@
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
-      <c r="AR55" s="2" t="inlineStr"/>
-      <c r="AS55" s="28" t="n"/>
-      <c r="AT55" s="5" t="n"/>
-      <c r="AU55" s="2" t="inlineStr"/>
+      <c r="AR55" s="2" t="n"/>
+      <c r="AU55" s="2" t="n"/>
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
       <c r="AX55" s="4" t="n"/>
@@ -10158,10 +9180,8 @@
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
-      <c r="BG55" s="2" t="inlineStr"/>
-      <c r="BH55" s="28" t="n"/>
-      <c r="BI55" s="5" t="n"/>
-      <c r="BJ55" s="2" t="inlineStr"/>
+      <c r="BG55" s="2" t="n"/>
+      <c r="BJ55" s="2" t="n"/>
       <c r="BK55" s="4" t="n"/>
       <c r="BL55" s="4" t="n"/>
       <c r="BM55" s="4" t="n"/>
@@ -10173,10 +9193,8 @@
       <c r="BS55" s="4" t="n"/>
       <c r="BT55" s="4" t="n"/>
       <c r="BU55" s="4" t="n"/>
-      <c r="BV55" s="2" t="inlineStr"/>
-      <c r="BW55" s="28" t="n"/>
-      <c r="BX55" s="5" t="n"/>
-      <c r="BY55" s="2" t="inlineStr"/>
+      <c r="BV55" s="2" t="n"/>
+      <c r="BY55" s="2" t="n"/>
       <c r="BZ55" s="4" t="n"/>
       <c r="CA55" s="4" t="n"/>
       <c r="CB55" s="4" t="n"/>
@@ -10188,12 +9206,21 @@
       <c r="CH55" s="4" t="n"/>
       <c r="CI55" s="4" t="n"/>
       <c r="CJ55" s="4" t="n"/>
-      <c r="CK55" s="2" t="inlineStr"/>
-      <c r="CL55" s="28" t="n"/>
-      <c r="CN55" s="2" t="inlineStr"/>
+      <c r="CK55" s="2" t="n"/>
+      <c r="CN55" s="2" t="n"/>
       <c r="CP55" s="11" t="n"/>
       <c r="CQ55" s="7" t="n"/>
       <c r="CR55" s="12" t="n"/>
+      <c r="CS55" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU55" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10270,14 +9297,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD56" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE56" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF56" s="2" t="inlineStr">
         <is>
           <t>00010</t>
@@ -10321,14 +9340,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS56" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT56" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU56" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -10370,14 +9381,6 @@
       <c r="BG56" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH56" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI56" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ56" s="2" t="inlineStr">
@@ -10421,14 +9424,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW56" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX56" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="BY56" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -10470,14 +9465,6 @@
       <c r="CK56" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL56" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM56" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN56" s="2" t="inlineStr">
@@ -10534,10 +9521,8 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="2" t="inlineStr"/>
-      <c r="AD57" s="28" t="n"/>
-      <c r="AE57" s="5" t="n"/>
-      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="n"/>
+      <c r="AF57" s="2" t="n"/>
       <c r="AG57" s="4" t="n"/>
       <c r="AH57" s="4" t="n"/>
       <c r="AI57" s="4" t="n"/>
@@ -10549,10 +9534,8 @@
       <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
-      <c r="AR57" s="2" t="inlineStr"/>
-      <c r="AS57" s="28" t="n"/>
-      <c r="AT57" s="5" t="n"/>
-      <c r="AU57" s="2" t="inlineStr"/>
+      <c r="AR57" s="2" t="n"/>
+      <c r="AU57" s="2" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
@@ -10564,10 +9547,8 @@
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
       <c r="BF57" s="4" t="n"/>
-      <c r="BG57" s="2" t="inlineStr"/>
-      <c r="BH57" s="28" t="n"/>
-      <c r="BI57" s="5" t="n"/>
-      <c r="BJ57" s="2" t="inlineStr"/>
+      <c r="BG57" s="2" t="n"/>
+      <c r="BJ57" s="2" t="n"/>
       <c r="BK57" s="4" t="n"/>
       <c r="BL57" s="4" t="n"/>
       <c r="BM57" s="4" t="n"/>
@@ -10579,10 +9560,8 @@
       <c r="BS57" s="4" t="n"/>
       <c r="BT57" s="4" t="n"/>
       <c r="BU57" s="4" t="n"/>
-      <c r="BV57" s="2" t="inlineStr"/>
-      <c r="BW57" s="28" t="n"/>
-      <c r="BX57" s="5" t="n"/>
-      <c r="BY57" s="2" t="inlineStr"/>
+      <c r="BV57" s="2" t="n"/>
+      <c r="BY57" s="2" t="n"/>
       <c r="BZ57" s="4" t="n"/>
       <c r="CA57" s="4" t="n"/>
       <c r="CB57" s="4" t="n"/>
@@ -10594,12 +9573,21 @@
       <c r="CH57" s="4" t="n"/>
       <c r="CI57" s="4" t="n"/>
       <c r="CJ57" s="4" t="n"/>
-      <c r="CK57" s="2" t="inlineStr"/>
-      <c r="CL57" s="28" t="n"/>
-      <c r="CN57" s="2" t="inlineStr"/>
+      <c r="CK57" s="2" t="n"/>
+      <c r="CN57" s="2" t="n"/>
       <c r="CP57" s="11" t="n"/>
       <c r="CQ57" s="7" t="n"/>
       <c r="CR57" s="12" t="n"/>
+      <c r="CS57" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU57" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10636,10 +9624,8 @@
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
-      <c r="AC58" s="2" t="inlineStr"/>
-      <c r="AD58" s="28" t="n"/>
-      <c r="AE58" s="5" t="n"/>
-      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="n"/>
+      <c r="AF58" s="2" t="n"/>
       <c r="AG58" s="4" t="n"/>
       <c r="AH58" s="4" t="n"/>
       <c r="AI58" s="4" t="n"/>
@@ -10651,10 +9637,8 @@
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
-      <c r="AR58" s="2" t="inlineStr"/>
-      <c r="AS58" s="28" t="n"/>
-      <c r="AT58" s="5" t="n"/>
-      <c r="AU58" s="2" t="inlineStr"/>
+      <c r="AR58" s="2" t="n"/>
+      <c r="AU58" s="2" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
@@ -10666,10 +9650,8 @@
       <c r="BD58" s="4" t="n"/>
       <c r="BE58" s="4" t="n"/>
       <c r="BF58" s="4" t="n"/>
-      <c r="BG58" s="2" t="inlineStr"/>
-      <c r="BH58" s="28" t="n"/>
-      <c r="BI58" s="5" t="n"/>
-      <c r="BJ58" s="2" t="inlineStr"/>
+      <c r="BG58" s="2" t="n"/>
+      <c r="BJ58" s="2" t="n"/>
       <c r="BK58" s="4" t="n"/>
       <c r="BL58" s="4" t="n"/>
       <c r="BM58" s="4" t="n"/>
@@ -10681,10 +9663,8 @@
       <c r="BS58" s="4" t="n"/>
       <c r="BT58" s="4" t="n"/>
       <c r="BU58" s="4" t="n"/>
-      <c r="BV58" s="2" t="inlineStr"/>
-      <c r="BW58" s="28" t="n"/>
-      <c r="BX58" s="5" t="n"/>
-      <c r="BY58" s="2" t="inlineStr"/>
+      <c r="BV58" s="2" t="n"/>
+      <c r="BY58" s="2" t="n"/>
       <c r="BZ58" s="4" t="n"/>
       <c r="CA58" s="4" t="n"/>
       <c r="CB58" s="4" t="n"/>
@@ -10696,12 +9676,21 @@
       <c r="CH58" s="4" t="n"/>
       <c r="CI58" s="4" t="n"/>
       <c r="CJ58" s="4" t="n"/>
-      <c r="CK58" s="2" t="inlineStr"/>
-      <c r="CL58" s="28" t="n"/>
-      <c r="CN58" s="2" t="inlineStr"/>
+      <c r="CK58" s="2" t="n"/>
+      <c r="CN58" s="2" t="n"/>
       <c r="CP58" s="11" t="n"/>
       <c r="CQ58" s="7" t="n"/>
       <c r="CR58" s="12" t="n"/>
+      <c r="CS58" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU58" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10737,14 +9726,6 @@
       <c r="AA59" s="4" t="n"/>
       <c r="AB59" s="4" t="n"/>
       <c r="AC59" s="2" t="inlineStr"/>
-      <c r="AD59" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE59" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
-        </is>
-      </c>
       <c r="AF59" s="2" t="inlineStr">
         <is>
           <t>11111</t>
@@ -10788,14 +9769,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS59" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT59" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU59" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -10837,14 +9810,6 @@
       <c r="BG59" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH59" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI59" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ59" s="2" t="inlineStr">
@@ -10888,14 +9853,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW59" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX59" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY59" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -10937,14 +9894,6 @@
       <c r="CK59" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL59" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM59" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN59" s="2" t="inlineStr">
@@ -11002,10 +9951,8 @@
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
-      <c r="AC60" s="2" t="inlineStr"/>
-      <c r="AD60" s="28" t="n"/>
-      <c r="AE60" s="5" t="n"/>
-      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="n"/>
+      <c r="AF60" s="2" t="n"/>
       <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
       <c r="AI60" s="4" t="n"/>
@@ -11017,10 +9964,8 @@
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
-      <c r="AR60" s="2" t="inlineStr"/>
-      <c r="AS60" s="28" t="n"/>
-      <c r="AT60" s="5" t="n"/>
-      <c r="AU60" s="2" t="inlineStr"/>
+      <c r="AR60" s="2" t="n"/>
+      <c r="AU60" s="2" t="n"/>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
@@ -11032,10 +9977,8 @@
       <c r="BD60" s="4" t="n"/>
       <c r="BE60" s="4" t="n"/>
       <c r="BF60" s="4" t="n"/>
-      <c r="BG60" s="2" t="inlineStr"/>
-      <c r="BH60" s="28" t="n"/>
-      <c r="BI60" s="5" t="n"/>
-      <c r="BJ60" s="2" t="inlineStr"/>
+      <c r="BG60" s="2" t="n"/>
+      <c r="BJ60" s="2" t="n"/>
       <c r="BK60" s="4" t="n"/>
       <c r="BL60" s="4" t="n"/>
       <c r="BM60" s="4" t="n"/>
@@ -11047,10 +9990,8 @@
       <c r="BS60" s="4" t="n"/>
       <c r="BT60" s="4" t="n"/>
       <c r="BU60" s="4" t="n"/>
-      <c r="BV60" s="2" t="inlineStr"/>
-      <c r="BW60" s="28" t="n"/>
-      <c r="BX60" s="5" t="n"/>
-      <c r="BY60" s="2" t="inlineStr"/>
+      <c r="BV60" s="2" t="n"/>
+      <c r="BY60" s="2" t="n"/>
       <c r="BZ60" s="4" t="n"/>
       <c r="CA60" s="4" t="n"/>
       <c r="CB60" s="4" t="n"/>
@@ -11062,13 +10003,21 @@
       <c r="CH60" s="4" t="n"/>
       <c r="CI60" s="4" t="n"/>
       <c r="CJ60" s="4" t="n"/>
-      <c r="CK60" s="2" t="inlineStr"/>
-      <c r="CL60" s="28" t="n"/>
-      <c r="CM60" s="5" t="n"/>
-      <c r="CN60" s="2" t="inlineStr"/>
+      <c r="CK60" s="2" t="n"/>
+      <c r="CN60" s="2" t="n"/>
       <c r="CP60" s="11" t="n"/>
       <c r="CQ60" s="7" t="n"/>
       <c r="CR60" s="12" t="n"/>
+      <c r="CS60" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU60" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11119,14 +10068,6 @@
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="2" t="inlineStr"/>
-      <c r="AD61" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE61" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF61" s="2" t="inlineStr">
         <is>
           <t>00001</t>
@@ -11144,14 +10085,6 @@
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
       <c r="AR61" s="2" t="inlineStr"/>
-      <c r="AS61" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT61" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU61" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -11169,14 +10102,6 @@
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="2" t="inlineStr"/>
-      <c r="BH61" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI61" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BJ61" s="2" t="inlineStr">
         <is>
           <t>00110</t>
@@ -11218,14 +10143,6 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="BW61" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX61" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY61" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -11267,14 +10184,6 @@
       <c r="CK61" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL61" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM61" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN61" s="2" t="inlineStr">
@@ -11342,14 +10251,6 @@
       <c r="AA62" s="4" t="n"/>
       <c r="AB62" s="4" t="n"/>
       <c r="AC62" s="2" t="inlineStr"/>
-      <c r="AD62" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF62" s="2" t="inlineStr">
         <is>
           <t>00001</t>
@@ -11393,14 +10294,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS62" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT62" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU62" s="2" t="inlineStr">
         <is>
           <t>000101</t>
@@ -11442,14 +10335,6 @@
       <c r="BG62" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH62" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI62" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ62" s="2" t="inlineStr">
@@ -11493,14 +10378,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW62" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX62" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY62" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -11542,14 +10419,6 @@
       <c r="CK62" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL62" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM62" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN62" s="2" t="inlineStr">
@@ -11610,10 +10479,8 @@
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
-      <c r="AC63" s="2" t="inlineStr"/>
-      <c r="AD63" s="28" t="n"/>
-      <c r="AE63" s="29" t="n"/>
-      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="n"/>
+      <c r="AF63" s="2" t="n"/>
       <c r="AG63" s="4" t="n"/>
       <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="n"/>
@@ -11625,10 +10492,8 @@
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
-      <c r="AR63" s="2" t="inlineStr"/>
-      <c r="AS63" s="28" t="n"/>
-      <c r="AT63" s="29" t="n"/>
-      <c r="AU63" s="2" t="inlineStr"/>
+      <c r="AR63" s="2" t="n"/>
+      <c r="AU63" s="2" t="n"/>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
@@ -11640,10 +10505,8 @@
       <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="n"/>
       <c r="BF63" s="4" t="n"/>
-      <c r="BG63" s="2" t="inlineStr"/>
-      <c r="BH63" s="28" t="n"/>
-      <c r="BI63" s="29" t="n"/>
-      <c r="BJ63" s="2" t="inlineStr"/>
+      <c r="BG63" s="2" t="n"/>
+      <c r="BJ63" s="2" t="n"/>
       <c r="BK63" s="4" t="n"/>
       <c r="BL63" s="4" t="n"/>
       <c r="BM63" s="4" t="n"/>
@@ -11655,10 +10518,8 @@
       <c r="BS63" s="4" t="n"/>
       <c r="BT63" s="4" t="n"/>
       <c r="BU63" s="4" t="n"/>
-      <c r="BV63" s="2" t="inlineStr"/>
-      <c r="BW63" s="28" t="n"/>
-      <c r="BX63" s="29" t="n"/>
-      <c r="BY63" s="2" t="inlineStr"/>
+      <c r="BV63" s="2" t="n"/>
+      <c r="BY63" s="2" t="n"/>
       <c r="BZ63" s="4" t="n"/>
       <c r="CA63" s="4" t="n"/>
       <c r="CB63" s="4" t="n"/>
@@ -11670,14 +10531,22 @@
       <c r="CH63" s="4" t="n"/>
       <c r="CI63" s="4" t="n"/>
       <c r="CJ63" s="4" t="n"/>
-      <c r="CK63" s="2" t="inlineStr"/>
-      <c r="CL63" s="28" t="n"/>
-      <c r="CM63" s="31" t="n"/>
-      <c r="CN63" s="2" t="inlineStr"/>
+      <c r="CK63" s="2" t="n"/>
+      <c r="CN63" s="2" t="n"/>
       <c r="CO63" s="13" t="n"/>
       <c r="CP63" s="14" t="n"/>
       <c r="CQ63" s="15" t="n"/>
       <c r="CR63" s="16" t="n"/>
+      <c r="CS63" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU63" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11716,10 +10585,8 @@
       <c r="Z64" s="4" t="n"/>
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
-      <c r="AC64" s="2" t="inlineStr"/>
-      <c r="AD64" s="28" t="n"/>
-      <c r="AE64" s="5" t="n"/>
-      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="n"/>
+      <c r="AF64" s="2" t="n"/>
       <c r="AG64" s="4" t="n"/>
       <c r="AH64" s="4" t="n"/>
       <c r="AI64" s="4" t="n"/>
@@ -11731,10 +10598,8 @@
       <c r="AO64" s="4" t="n"/>
       <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="2" t="inlineStr"/>
-      <c r="AS64" s="28" t="n"/>
-      <c r="AT64" s="5" t="n"/>
-      <c r="AU64" s="2" t="inlineStr"/>
+      <c r="AR64" s="2" t="n"/>
+      <c r="AU64" s="2" t="n"/>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
@@ -11746,10 +10611,8 @@
       <c r="BD64" s="4" t="n"/>
       <c r="BE64" s="4" t="n"/>
       <c r="BF64" s="4" t="n"/>
-      <c r="BG64" s="2" t="inlineStr"/>
-      <c r="BH64" s="28" t="n"/>
-      <c r="BI64" s="5" t="n"/>
-      <c r="BJ64" s="2" t="inlineStr"/>
+      <c r="BG64" s="2" t="n"/>
+      <c r="BJ64" s="2" t="n"/>
       <c r="BK64" s="4" t="n"/>
       <c r="BL64" s="4" t="n"/>
       <c r="BM64" s="4" t="n"/>
@@ -11761,10 +10624,8 @@
       <c r="BS64" s="4" t="n"/>
       <c r="BT64" s="4" t="n"/>
       <c r="BU64" s="4" t="n"/>
-      <c r="BV64" s="2" t="inlineStr"/>
-      <c r="BW64" s="28" t="n"/>
-      <c r="BX64" s="5" t="n"/>
-      <c r="BY64" s="2" t="inlineStr"/>
+      <c r="BV64" s="2" t="n"/>
+      <c r="BY64" s="2" t="n"/>
       <c r="BZ64" s="4" t="n"/>
       <c r="CA64" s="4" t="n"/>
       <c r="CB64" s="4" t="n"/>
@@ -11776,13 +10637,21 @@
       <c r="CH64" s="4" t="n"/>
       <c r="CI64" s="4" t="n"/>
       <c r="CJ64" s="4" t="n"/>
-      <c r="CK64" s="2" t="inlineStr"/>
-      <c r="CL64" s="28" t="n"/>
-      <c r="CM64" s="5" t="n"/>
-      <c r="CN64" s="2" t="inlineStr"/>
+      <c r="CK64" s="2" t="n"/>
+      <c r="CN64" s="2" t="n"/>
       <c r="CP64" s="11" t="n"/>
       <c r="CQ64" s="7" t="n"/>
       <c r="CR64" s="12" t="n"/>
+      <c r="CS64" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU64" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11820,10 +10689,8 @@
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="2" t="inlineStr"/>
-      <c r="AD65" s="28" t="n"/>
-      <c r="AE65" s="5" t="n"/>
-      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="n"/>
+      <c r="AF65" s="2" t="n"/>
       <c r="AG65" s="4" t="n"/>
       <c r="AH65" s="4" t="n"/>
       <c r="AI65" s="4" t="n"/>
@@ -11835,10 +10702,8 @@
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
-      <c r="AR65" s="2" t="inlineStr"/>
-      <c r="AS65" s="28" t="n"/>
-      <c r="AT65" s="5" t="n"/>
-      <c r="AU65" s="2" t="inlineStr"/>
+      <c r="AR65" s="2" t="n"/>
+      <c r="AU65" s="2" t="n"/>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
@@ -11850,10 +10715,8 @@
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
-      <c r="BG65" s="2" t="inlineStr"/>
-      <c r="BH65" s="28" t="n"/>
-      <c r="BI65" s="5" t="n"/>
-      <c r="BJ65" s="2" t="inlineStr"/>
+      <c r="BG65" s="2" t="n"/>
+      <c r="BJ65" s="2" t="n"/>
       <c r="BK65" s="4" t="n"/>
       <c r="BL65" s="4" t="n"/>
       <c r="BM65" s="4" t="n"/>
@@ -11865,10 +10728,8 @@
       <c r="BS65" s="4" t="n"/>
       <c r="BT65" s="4" t="n"/>
       <c r="BU65" s="4" t="n"/>
-      <c r="BV65" s="2" t="inlineStr"/>
-      <c r="BW65" s="28" t="n"/>
-      <c r="BX65" s="5" t="n"/>
-      <c r="BY65" s="2" t="inlineStr"/>
+      <c r="BV65" s="2" t="n"/>
+      <c r="BY65" s="2" t="n"/>
       <c r="BZ65" s="4" t="n"/>
       <c r="CA65" s="4" t="n"/>
       <c r="CB65" s="4" t="n"/>
@@ -11880,12 +10741,21 @@
       <c r="CH65" s="4" t="n"/>
       <c r="CI65" s="4" t="n"/>
       <c r="CJ65" s="4" t="n"/>
-      <c r="CK65" s="2" t="inlineStr"/>
-      <c r="CL65" s="28" t="n"/>
-      <c r="CN65" s="2" t="inlineStr"/>
+      <c r="CK65" s="2" t="n"/>
+      <c r="CN65" s="2" t="n"/>
       <c r="CP65" s="11" t="n"/>
       <c r="CQ65" s="7" t="n"/>
       <c r="CR65" s="12" t="n"/>
+      <c r="CS65" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU65" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11936,14 +10806,6 @@
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="2" t="inlineStr"/>
-      <c r="AD66" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE66" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF66" s="2" t="inlineStr">
         <is>
           <t>00011</t>
@@ -11987,14 +10849,6 @@
           <t>C2&lt;</t>
         </is>
       </c>
-      <c r="AS66" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT66" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU66" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -12036,14 +10890,6 @@
       <c r="BG66" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH66" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI66" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ66" s="2" t="inlineStr">
@@ -12085,14 +10931,6 @@
       <c r="BV66" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BW66" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX66" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BY66" s="2" t="inlineStr">
@@ -12112,14 +10950,6 @@
       <c r="CI66" s="4" t="n"/>
       <c r="CJ66" s="4" t="n"/>
       <c r="CK66" s="2" t="inlineStr"/>
-      <c r="CL66" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM66" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN66" s="2" t="inlineStr">
         <is>
           <t>011</t>
@@ -12174,10 +11004,8 @@
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
-      <c r="AC67" s="2" t="inlineStr"/>
-      <c r="AD67" s="28" t="n"/>
-      <c r="AE67" s="5" t="n"/>
-      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="n"/>
+      <c r="AF67" s="2" t="n"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="n"/>
@@ -12189,10 +11017,8 @@
       <c r="AO67" s="4" t="n"/>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
-      <c r="AR67" s="2" t="inlineStr"/>
-      <c r="AS67" s="28" t="n"/>
-      <c r="AT67" s="5" t="n"/>
-      <c r="AU67" s="2" t="inlineStr"/>
+      <c r="AR67" s="2" t="n"/>
+      <c r="AU67" s="2" t="n"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
@@ -12204,10 +11030,8 @@
       <c r="BD67" s="4" t="n"/>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="n"/>
-      <c r="BG67" s="2" t="inlineStr"/>
-      <c r="BH67" s="28" t="n"/>
-      <c r="BI67" s="5" t="n"/>
-      <c r="BJ67" s="2" t="inlineStr"/>
+      <c r="BG67" s="2" t="n"/>
+      <c r="BJ67" s="2" t="n"/>
       <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
@@ -12219,10 +11043,8 @@
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
       <c r="BU67" s="4" t="n"/>
-      <c r="BV67" s="2" t="inlineStr"/>
-      <c r="BW67" s="28" t="n"/>
-      <c r="BX67" s="5" t="n"/>
-      <c r="BY67" s="2" t="inlineStr"/>
+      <c r="BV67" s="2" t="n"/>
+      <c r="BY67" s="2" t="n"/>
       <c r="BZ67" s="4" t="n"/>
       <c r="CA67" s="4" t="n"/>
       <c r="CB67" s="4" t="n"/>
@@ -12234,13 +11056,21 @@
       <c r="CH67" s="4" t="n"/>
       <c r="CI67" s="4" t="n"/>
       <c r="CJ67" s="4" t="n"/>
-      <c r="CK67" s="2" t="inlineStr"/>
-      <c r="CL67" s="28" t="n"/>
-      <c r="CM67" s="5" t="n"/>
-      <c r="CN67" s="2" t="inlineStr"/>
+      <c r="CK67" s="2" t="n"/>
+      <c r="CN67" s="2" t="n"/>
       <c r="CP67" s="11" t="n"/>
       <c r="CQ67" s="7" t="n"/>
       <c r="CR67" s="12" t="n"/>
+      <c r="CS67" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU67" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12315,14 +11145,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD68" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE68" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF68" s="2" t="inlineStr">
         <is>
           <t>00111</t>
@@ -12366,14 +11188,6 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="AS68" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT68" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU68" s="2" t="inlineStr">
         <is>
           <t>001010</t>
@@ -12415,14 +11229,6 @@
       <c r="BG68" s="2" t="inlineStr">
         <is>
           <t>AI</t>
-        </is>
-      </c>
-      <c r="BH68" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI68" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ68" s="2" t="inlineStr">
@@ -12466,14 +11272,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW68" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX68" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY68" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -12515,14 +11313,6 @@
       <c r="CK68" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL68" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM68" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN68" s="2" t="inlineStr">
@@ -12579,10 +11369,8 @@
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
-      <c r="AC69" s="2" t="inlineStr"/>
-      <c r="AD69" s="28" t="n"/>
-      <c r="AE69" s="5" t="n"/>
-      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="n"/>
+      <c r="AF69" s="2" t="n"/>
       <c r="AG69" s="4" t="n"/>
       <c r="AH69" s="4" t="n"/>
       <c r="AI69" s="4" t="n"/>
@@ -12594,10 +11382,8 @@
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="2" t="inlineStr"/>
-      <c r="AS69" s="28" t="n"/>
-      <c r="AT69" s="5" t="n"/>
-      <c r="AU69" s="2" t="inlineStr"/>
+      <c r="AR69" s="2" t="n"/>
+      <c r="AU69" s="2" t="n"/>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
@@ -12609,10 +11395,8 @@
       <c r="BD69" s="4" t="n"/>
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
-      <c r="BG69" s="2" t="inlineStr"/>
-      <c r="BH69" s="28" t="n"/>
-      <c r="BI69" s="5" t="n"/>
-      <c r="BJ69" s="2" t="inlineStr"/>
+      <c r="BG69" s="2" t="n"/>
+      <c r="BJ69" s="2" t="n"/>
       <c r="BK69" s="4" t="n"/>
       <c r="BL69" s="4" t="n"/>
       <c r="BM69" s="4" t="n"/>
@@ -12624,10 +11408,8 @@
       <c r="BS69" s="4" t="n"/>
       <c r="BT69" s="4" t="n"/>
       <c r="BU69" s="4" t="n"/>
-      <c r="BV69" s="2" t="inlineStr"/>
-      <c r="BW69" s="28" t="n"/>
-      <c r="BX69" s="5" t="n"/>
-      <c r="BY69" s="2" t="inlineStr"/>
+      <c r="BV69" s="2" t="n"/>
+      <c r="BY69" s="2" t="n"/>
       <c r="BZ69" s="4" t="n"/>
       <c r="CA69" s="4" t="n"/>
       <c r="CB69" s="4" t="n"/>
@@ -12639,12 +11421,21 @@
       <c r="CH69" s="4" t="n"/>
       <c r="CI69" s="4" t="n"/>
       <c r="CJ69" s="4" t="n"/>
-      <c r="CK69" s="2" t="inlineStr"/>
-      <c r="CL69" s="28" t="n"/>
-      <c r="CN69" s="2" t="inlineStr"/>
+      <c r="CK69" s="2" t="n"/>
+      <c r="CN69" s="2" t="n"/>
       <c r="CP69" s="11" t="n"/>
       <c r="CQ69" s="7" t="n"/>
       <c r="CR69" s="12" t="n"/>
+      <c r="CS69" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU69" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,14 +11472,6 @@
       <c r="AA70" s="4" t="n"/>
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="2" t="inlineStr"/>
-      <c r="AD70" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE70" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF70" s="2" t="inlineStr">
         <is>
           <t>00011</t>
@@ -12732,14 +11515,6 @@
           <t>C3&gt;</t>
         </is>
       </c>
-      <c r="AS70" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT70" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU70" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -12781,14 +11556,6 @@
       <c r="BG70" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH70" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI70" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ70" s="2" t="inlineStr">
@@ -12832,14 +11599,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW70" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX70" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY70" s="2" t="inlineStr">
         <is>
           <t>100</t>
@@ -12881,14 +11640,6 @@
       <c r="CK70" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL70" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM70" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN70" s="2" t="inlineStr">
@@ -12985,14 +11736,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE71" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF71" s="2" t="inlineStr">
         <is>
           <t>00001</t>
@@ -13036,14 +11779,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT71" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU71" s="2" t="inlineStr">
         <is>
           <t>000001</t>
@@ -13085,14 +11820,6 @@
       <c r="BG71" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI71" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ71" s="2" t="inlineStr">
@@ -13136,14 +11863,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX71" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY71" s="2" t="inlineStr">
         <is>
           <t>001</t>
@@ -13185,14 +11904,6 @@
       <c r="CK71" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL71" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM71" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN71" s="2" t="inlineStr">
@@ -13263,14 +11974,6 @@
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="2" t="inlineStr"/>
-      <c r="AD72" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE72" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF72" s="2" t="inlineStr">
         <is>
           <t>00001</t>
@@ -13314,14 +12017,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS72" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT72" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU72" s="2" t="inlineStr">
         <is>
           <t>011111</t>
@@ -13362,15 +12057,7 @@
       </c>
       <c r="BG72" s="2" t="inlineStr">
         <is>
-          <t>C2&lt;</t>
-        </is>
-      </c>
-      <c r="BH72" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI72" s="5" t="inlineStr">
-        <is>
-          <t>Pass*</t>
+          <t>C1&lt;</t>
         </is>
       </c>
       <c r="BJ72" s="2" t="inlineStr">
@@ -13414,14 +12101,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW72" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX72" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY72" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -13463,14 +12142,6 @@
       <c r="CK72" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL72" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM72" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN72" s="2" t="inlineStr">
@@ -13555,14 +12226,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD73" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE73" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF73" s="2" t="inlineStr">
         <is>
           <t>01101</t>
@@ -13606,14 +12269,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS73" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT73" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU73" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -13655,14 +12310,6 @@
       <c r="BG73" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH73" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI73" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ73" s="2" t="inlineStr">
@@ -13706,14 +12353,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW73" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX73" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY73" s="2" t="inlineStr">
         <is>
           <t>010</t>
@@ -13755,14 +12394,6 @@
       <c r="CK73" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL73" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM73" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN73" s="2" t="inlineStr">
@@ -13821,10 +12452,8 @@
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="2" t="inlineStr"/>
-      <c r="AD74" s="28" t="n"/>
-      <c r="AE74" s="5" t="n"/>
-      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="n"/>
+      <c r="AF74" s="2" t="n"/>
       <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n"/>
       <c r="AI74" s="4" t="n"/>
@@ -13836,10 +12465,8 @@
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
-      <c r="AR74" s="2" t="inlineStr"/>
-      <c r="AS74" s="28" t="n"/>
-      <c r="AT74" s="5" t="n"/>
-      <c r="AU74" s="2" t="inlineStr"/>
+      <c r="AR74" s="2" t="n"/>
+      <c r="AU74" s="2" t="n"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
@@ -13851,10 +12478,8 @@
       <c r="BD74" s="4" t="n"/>
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
-      <c r="BG74" s="2" t="inlineStr"/>
-      <c r="BH74" s="28" t="n"/>
-      <c r="BI74" s="5" t="n"/>
-      <c r="BJ74" s="2" t="inlineStr"/>
+      <c r="BG74" s="2" t="n"/>
+      <c r="BJ74" s="2" t="n"/>
       <c r="BK74" s="4" t="n"/>
       <c r="BL74" s="4" t="n"/>
       <c r="BM74" s="4" t="n"/>
@@ -13866,10 +12491,8 @@
       <c r="BS74" s="4" t="n"/>
       <c r="BT74" s="4" t="n"/>
       <c r="BU74" s="4" t="n"/>
-      <c r="BV74" s="2" t="inlineStr"/>
-      <c r="BW74" s="28" t="n"/>
-      <c r="BX74" s="5" t="n"/>
-      <c r="BY74" s="2" t="inlineStr"/>
+      <c r="BV74" s="2" t="n"/>
+      <c r="BY74" s="2" t="n"/>
       <c r="BZ74" s="4" t="n"/>
       <c r="CA74" s="4" t="n"/>
       <c r="CB74" s="4" t="n"/>
@@ -13881,12 +12504,21 @@
       <c r="CH74" s="4" t="n"/>
       <c r="CI74" s="4" t="n"/>
       <c r="CJ74" s="4" t="n"/>
-      <c r="CK74" s="2" t="inlineStr"/>
-      <c r="CL74" s="28" t="n"/>
-      <c r="CN74" s="2" t="inlineStr"/>
+      <c r="CK74" s="2" t="n"/>
+      <c r="CN74" s="2" t="n"/>
       <c r="CP74" s="11" t="n"/>
       <c r="CQ74" s="7" t="n"/>
       <c r="CR74" s="12" t="n"/>
+      <c r="CS74" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU74" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13961,14 +12593,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD75" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE75" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF75" s="2" t="inlineStr">
         <is>
           <t>00011</t>
@@ -14012,14 +12636,6 @@
           <t>C2&lt;</t>
         </is>
       </c>
-      <c r="AS75" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT75" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU75" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -14061,14 +12677,6 @@
       <c r="BG75" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH75" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI75" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ75" s="2" t="inlineStr">
@@ -14110,14 +12718,6 @@
       <c r="BV75" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BW75" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX75" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BY75" s="2" t="inlineStr">
@@ -14137,14 +12737,6 @@
       <c r="CI75" s="4" t="n"/>
       <c r="CJ75" s="4" t="n"/>
       <c r="CK75" s="2" t="inlineStr"/>
-      <c r="CL75" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM75" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="CN75" s="2" t="inlineStr">
         <is>
           <t>011</t>
@@ -14197,10 +12789,8 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="2" t="inlineStr"/>
-      <c r="AD76" s="28" t="n"/>
-      <c r="AE76" s="5" t="n"/>
-      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="n"/>
+      <c r="AF76" s="2" t="n"/>
       <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
@@ -14212,10 +12802,8 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="2" t="inlineStr"/>
-      <c r="AS76" s="28" t="n"/>
-      <c r="AT76" s="5" t="n"/>
-      <c r="AU76" s="2" t="inlineStr"/>
+      <c r="AR76" s="2" t="n"/>
+      <c r="AU76" s="2" t="n"/>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
@@ -14227,10 +12815,8 @@
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
-      <c r="BG76" s="2" t="inlineStr"/>
-      <c r="BH76" s="28" t="n"/>
-      <c r="BI76" s="5" t="n"/>
-      <c r="BJ76" s="2" t="inlineStr"/>
+      <c r="BG76" s="2" t="n"/>
+      <c r="BJ76" s="2" t="n"/>
       <c r="BK76" s="4" t="n"/>
       <c r="BL76" s="4" t="n"/>
       <c r="BM76" s="4" t="n"/>
@@ -14242,10 +12828,8 @@
       <c r="BS76" s="4" t="n"/>
       <c r="BT76" s="4" t="n"/>
       <c r="BU76" s="4" t="n"/>
-      <c r="BV76" s="2" t="inlineStr"/>
-      <c r="BW76" s="28" t="n"/>
-      <c r="BX76" s="5" t="n"/>
-      <c r="BY76" s="2" t="inlineStr"/>
+      <c r="BV76" s="2" t="n"/>
+      <c r="BY76" s="2" t="n"/>
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="n"/>
@@ -14257,12 +12841,21 @@
       <c r="CH76" s="4" t="n"/>
       <c r="CI76" s="4" t="n"/>
       <c r="CJ76" s="4" t="n"/>
-      <c r="CK76" s="2" t="inlineStr"/>
-      <c r="CL76" s="28" t="n"/>
-      <c r="CN76" s="2" t="inlineStr"/>
+      <c r="CK76" s="2" t="n"/>
+      <c r="CN76" s="2" t="n"/>
       <c r="CP76" s="11" t="n"/>
       <c r="CQ76" s="7" t="n"/>
       <c r="CR76" s="12" t="n"/>
+      <c r="CS76" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU76" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14300,10 +12893,8 @@
       <c r="Z77" s="4" t="n"/>
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="2" t="inlineStr"/>
-      <c r="AD77" s="28" t="n"/>
-      <c r="AE77" s="5" t="n"/>
-      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="n"/>
+      <c r="AF77" s="2" t="n"/>
       <c r="AG77" s="4" t="n"/>
       <c r="AH77" s="4" t="n"/>
       <c r="AI77" s="4" t="n"/>
@@ -14315,10 +12906,8 @@
       <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
-      <c r="AR77" s="2" t="inlineStr"/>
-      <c r="AS77" s="28" t="n"/>
-      <c r="AT77" s="5" t="n"/>
-      <c r="AU77" s="2" t="inlineStr"/>
+      <c r="AR77" s="2" t="n"/>
+      <c r="AU77" s="2" t="n"/>
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
@@ -14330,10 +12919,8 @@
       <c r="BD77" s="4" t="n"/>
       <c r="BE77" s="4" t="n"/>
       <c r="BF77" s="4" t="n"/>
-      <c r="BG77" s="2" t="inlineStr"/>
-      <c r="BH77" s="28" t="n"/>
-      <c r="BI77" s="5" t="n"/>
-      <c r="BJ77" s="2" t="inlineStr"/>
+      <c r="BG77" s="2" t="n"/>
+      <c r="BJ77" s="2" t="n"/>
       <c r="BK77" s="4" t="n"/>
       <c r="BL77" s="4" t="n"/>
       <c r="BM77" s="4" t="n"/>
@@ -14345,10 +12932,8 @@
       <c r="BS77" s="4" t="n"/>
       <c r="BT77" s="4" t="n"/>
       <c r="BU77" s="4" t="n"/>
-      <c r="BV77" s="2" t="inlineStr"/>
-      <c r="BW77" s="28" t="n"/>
-      <c r="BX77" s="5" t="n"/>
-      <c r="BY77" s="2" t="inlineStr"/>
+      <c r="BV77" s="2" t="n"/>
+      <c r="BY77" s="2" t="n"/>
       <c r="BZ77" s="4" t="n"/>
       <c r="CA77" s="4" t="n"/>
       <c r="CB77" s="4" t="n"/>
@@ -14360,13 +12945,21 @@
       <c r="CH77" s="4" t="n"/>
       <c r="CI77" s="4" t="n"/>
       <c r="CJ77" s="4" t="n"/>
-      <c r="CK77" s="2" t="inlineStr"/>
-      <c r="CL77" s="28" t="n"/>
-      <c r="CM77" s="5" t="n"/>
-      <c r="CN77" s="2" t="inlineStr"/>
+      <c r="CK77" s="2" t="n"/>
+      <c r="CN77" s="2" t="n"/>
       <c r="CP77" s="11" t="n"/>
       <c r="CQ77" s="7" t="n"/>
       <c r="CR77" s="12" t="n"/>
+      <c r="CS77" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU77" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14441,14 +13034,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD78" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE78" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF78" s="2" t="inlineStr">
         <is>
           <t>10111</t>
@@ -14492,14 +13077,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS78" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT78" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU78" s="2" t="inlineStr">
         <is>
           <t>001001</t>
@@ -14541,14 +13118,6 @@
       <c r="BG78" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH78" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI78" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ78" s="2" t="inlineStr">
@@ -14592,14 +13161,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW78" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX78" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY78" s="2" t="inlineStr">
         <is>
           <t>011</t>
@@ -14641,14 +13202,6 @@
       <c r="CK78" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL78" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM78" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN78" s="2" t="inlineStr">
@@ -14745,14 +13298,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD79" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE79" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF79" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -14796,14 +13341,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS79" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT79" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU79" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -14845,14 +13382,6 @@
       <c r="BG79" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH79" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI79" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ79" s="2" t="inlineStr">
@@ -14896,14 +13425,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW79" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX79" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY79" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -14945,14 +13466,6 @@
       <c r="CK79" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL79" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM79" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN79" s="2" t="inlineStr">
@@ -15009,10 +13522,8 @@
       <c r="Z80" s="4" t="n"/>
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="28" t="n"/>
-      <c r="AE80" s="5" t="n"/>
-      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="n"/>
+      <c r="AF80" s="2" t="n"/>
       <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n"/>
       <c r="AI80" s="4" t="n"/>
@@ -15024,10 +13535,8 @@
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
-      <c r="AR80" s="2" t="inlineStr"/>
-      <c r="AS80" s="28" t="n"/>
-      <c r="AT80" s="5" t="n"/>
-      <c r="AU80" s="2" t="inlineStr"/>
+      <c r="AR80" s="2" t="n"/>
+      <c r="AU80" s="2" t="n"/>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
@@ -15039,10 +13548,8 @@
       <c r="BD80" s="4" t="n"/>
       <c r="BE80" s="4" t="n"/>
       <c r="BF80" s="4" t="n"/>
-      <c r="BG80" s="2" t="inlineStr"/>
-      <c r="BH80" s="28" t="n"/>
-      <c r="BI80" s="5" t="n"/>
-      <c r="BJ80" s="2" t="inlineStr"/>
+      <c r="BG80" s="2" t="n"/>
+      <c r="BJ80" s="2" t="n"/>
       <c r="BK80" s="4" t="n"/>
       <c r="BL80" s="4" t="n"/>
       <c r="BM80" s="4" t="n"/>
@@ -15054,10 +13561,8 @@
       <c r="BS80" s="4" t="n"/>
       <c r="BT80" s="4" t="n"/>
       <c r="BU80" s="4" t="n"/>
-      <c r="BV80" s="2" t="inlineStr"/>
-      <c r="BW80" s="28" t="n"/>
-      <c r="BX80" s="5" t="n"/>
-      <c r="BY80" s="2" t="inlineStr"/>
+      <c r="BV80" s="2" t="n"/>
+      <c r="BY80" s="2" t="n"/>
       <c r="BZ80" s="4" t="n"/>
       <c r="CA80" s="4" t="n"/>
       <c r="CB80" s="4" t="n"/>
@@ -15069,12 +13574,21 @@
       <c r="CH80" s="4" t="n"/>
       <c r="CI80" s="4" t="n"/>
       <c r="CJ80" s="4" t="n"/>
-      <c r="CK80" s="2" t="inlineStr"/>
-      <c r="CL80" s="28" t="n"/>
-      <c r="CN80" s="2" t="inlineStr"/>
+      <c r="CK80" s="2" t="n"/>
+      <c r="CN80" s="2" t="n"/>
       <c r="CP80" s="11" t="n"/>
       <c r="CQ80" s="7" t="n"/>
       <c r="CR80" s="12" t="n"/>
+      <c r="CS80" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU80" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15151,14 +13665,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD81" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF81" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -15202,14 +13708,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS81" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT81" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU81" s="2" t="inlineStr">
         <is>
           <t>000100</t>
@@ -15251,14 +13749,6 @@
       <c r="BG81" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH81" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI81" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ81" s="2" t="inlineStr">
@@ -15302,14 +13792,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW81" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX81" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY81" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -15351,14 +13833,6 @@
       <c r="CK81" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL81" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM81" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN81" s="2" t="inlineStr">
@@ -15420,14 +13894,14 @@
         <v>4</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="S82" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V82" s="4" t="n">
         <v>97.7</v>
@@ -15455,14 +13929,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD82" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE82" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF82" s="2" t="inlineStr">
         <is>
           <t>00000</t>
@@ -15506,14 +13972,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS82" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT82" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU82" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -15555,14 +14013,6 @@
       <c r="BG82" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH82" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI82" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ82" s="2" t="inlineStr">
@@ -15606,14 +14056,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW82" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX82" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY82" s="2" t="inlineStr">
         <is>
           <t>000</t>
@@ -15655,14 +14097,6 @@
       <c r="CK82" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL82" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM82" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN82" s="2" t="inlineStr">
@@ -15757,14 +14191,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AD83" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AF83" s="2" t="inlineStr">
         <is>
           <t>10001</t>
@@ -15808,14 +14234,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="AS83" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT83" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="AU83" s="2" t="inlineStr">
         <is>
           <t>000000</t>
@@ -15857,14 +14275,6 @@
       <c r="BG83" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="BH83" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI83" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="BJ83" s="2" t="inlineStr">
@@ -15908,14 +14318,6 @@
           <t>_</t>
         </is>
       </c>
-      <c r="BW83" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX83" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="BY83" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -15957,14 +14359,6 @@
       <c r="CK83" s="2" t="inlineStr">
         <is>
           <t>_</t>
-        </is>
-      </c>
-      <c r="CL83" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM83" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
       <c r="CN83" s="2" t="inlineStr">
@@ -16018,10 +14412,8 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="2" t="inlineStr"/>
-      <c r="AD84" s="28" t="n"/>
-      <c r="AE84" s="5" t="n"/>
-      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="n"/>
+      <c r="AF84" s="2" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
       <c r="AI84" s="4" t="n"/>
@@ -16033,10 +14425,8 @@
       <c r="AO84" s="4" t="n"/>
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>
-      <c r="AR84" s="2" t="inlineStr"/>
-      <c r="AS84" s="28" t="n"/>
-      <c r="AT84" s="5" t="n"/>
-      <c r="AU84" s="2" t="inlineStr"/>
+      <c r="AR84" s="2" t="n"/>
+      <c r="AU84" s="2" t="n"/>
       <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
@@ -16048,10 +14438,8 @@
       <c r="BD84" s="4" t="n"/>
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
-      <c r="BG84" s="2" t="inlineStr"/>
-      <c r="BH84" s="28" t="n"/>
-      <c r="BI84" s="5" t="n"/>
-      <c r="BJ84" s="2" t="inlineStr"/>
+      <c r="BG84" s="2" t="n"/>
+      <c r="BJ84" s="2" t="n"/>
       <c r="BK84" s="4" t="n"/>
       <c r="BL84" s="4" t="n"/>
       <c r="BM84" s="4" t="n"/>
@@ -16063,10 +14451,8 @@
       <c r="BS84" s="4" t="n"/>
       <c r="BT84" s="4" t="n"/>
       <c r="BU84" s="4" t="n"/>
-      <c r="BV84" s="2" t="inlineStr"/>
-      <c r="BW84" s="2" t="n"/>
-      <c r="BX84" s="2" t="n"/>
-      <c r="BY84" s="2" t="inlineStr"/>
+      <c r="BV84" s="2" t="n"/>
+      <c r="BY84" s="2" t="n"/>
       <c r="BZ84" s="4" t="n"/>
       <c r="CA84" s="4" t="n"/>
       <c r="CB84" s="4" t="n"/>
@@ -16078,12 +14464,21 @@
       <c r="CH84" s="4" t="n"/>
       <c r="CI84" s="4" t="n"/>
       <c r="CJ84" s="4" t="n"/>
-      <c r="CK84" s="2" t="inlineStr"/>
-      <c r="CL84" s="28" t="n"/>
-      <c r="CN84" s="2" t="inlineStr"/>
+      <c r="CK84" s="2" t="n"/>
+      <c r="CN84" s="2" t="n"/>
       <c r="CP84" s="11" t="n"/>
       <c r="CQ84" s="7" t="n"/>
       <c r="CR84" s="12" t="n"/>
+      <c r="CS84" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU84" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -16124,10 +14519,8 @@
       <c r="Z85" s="4" t="n"/>
       <c r="AA85" s="4" t="n"/>
       <c r="AB85" s="4" t="n"/>
-      <c r="AC85" s="2" t="inlineStr"/>
-      <c r="AD85" s="28" t="n"/>
-      <c r="AE85" s="5" t="n"/>
-      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="n"/>
+      <c r="AF85" s="2" t="n"/>
       <c r="AG85" s="4" t="n"/>
       <c r="AH85" s="4" t="n"/>
       <c r="AI85" s="4" t="n"/>
@@ -16139,10 +14532,8 @@
       <c r="AO85" s="4" t="n"/>
       <c r="AP85" s="4" t="n"/>
       <c r="AQ85" s="4" t="n"/>
-      <c r="AR85" s="2" t="inlineStr"/>
-      <c r="AS85" s="28" t="n"/>
-      <c r="AT85" s="30" t="n"/>
-      <c r="AU85" s="2" t="inlineStr"/>
+      <c r="AR85" s="2" t="n"/>
+      <c r="AU85" s="2" t="n"/>
       <c r="AV85" s="4" t="n"/>
       <c r="AW85" s="4" t="n"/>
       <c r="AX85" s="4" t="n"/>
@@ -16154,10 +14545,8 @@
       <c r="BD85" s="4" t="n"/>
       <c r="BE85" s="4" t="n"/>
       <c r="BF85" s="4" t="n"/>
-      <c r="BG85" s="2" t="inlineStr"/>
-      <c r="BH85" s="28" t="n"/>
-      <c r="BI85" s="5" t="n"/>
-      <c r="BJ85" s="2" t="inlineStr"/>
+      <c r="BG85" s="2" t="n"/>
+      <c r="BJ85" s="2" t="n"/>
       <c r="BK85" s="4" t="n"/>
       <c r="BL85" s="4" t="n"/>
       <c r="BM85" s="4" t="n"/>
@@ -16169,10 +14558,8 @@
       <c r="BS85" s="4" t="n"/>
       <c r="BT85" s="4" t="n"/>
       <c r="BU85" s="4" t="n"/>
-      <c r="BV85" s="2" t="inlineStr"/>
-      <c r="BW85" s="2" t="n"/>
-      <c r="BX85" s="2" t="n"/>
-      <c r="BY85" s="2" t="inlineStr"/>
+      <c r="BV85" s="2" t="n"/>
+      <c r="BY85" s="2" t="n"/>
       <c r="BZ85" s="4" t="n"/>
       <c r="CA85" s="4" t="n"/>
       <c r="CB85" s="4" t="n"/>
@@ -16184,13 +14571,22 @@
       <c r="CH85" s="4" t="n"/>
       <c r="CI85" s="4" t="n"/>
       <c r="CJ85" s="4" t="n"/>
-      <c r="CK85" s="2" t="inlineStr"/>
-      <c r="CL85" s="28" t="n"/>
-      <c r="CN85" s="2" t="inlineStr"/>
+      <c r="CK85" s="2" t="n"/>
+      <c r="CN85" s="2" t="n"/>
       <c r="CO85" s="17" t="n"/>
       <c r="CP85" s="18" t="n"/>
       <c r="CQ85" s="19" t="n"/>
       <c r="CR85" s="19" t="n"/>
+      <c r="CS85" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="CU85" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -16206,6 +14602,11 @@
       <c r="D86" s="3" t="inlineStr">
         <is>
           <t>1000001</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R86" s="4" t="n"/>
@@ -16271,8 +14672,6 @@
       <c r="BT86" s="4" t="n"/>
       <c r="BU86" s="4" t="n"/>
       <c r="BV86" s="2" t="inlineStr"/>
-      <c r="BW86" s="2" t="n"/>
-      <c r="BX86" s="2" t="n"/>
       <c r="BY86" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -16295,6 +14694,16 @@
           <t>011</t>
         </is>
       </c>
+      <c r="CS86" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU86" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16310,6 +14719,11 @@
       <c r="D87" s="3" t="inlineStr">
         <is>
           <t>1000002</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R87" s="4" t="n"/>
@@ -16375,8 +14789,6 @@
       <c r="BT87" s="4" t="n"/>
       <c r="BU87" s="4" t="n"/>
       <c r="BV87" s="2" t="inlineStr"/>
-      <c r="BW87" s="2" t="n"/>
-      <c r="BX87" s="2" t="n"/>
       <c r="BY87" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -16399,6 +14811,16 @@
           <t>011</t>
         </is>
       </c>
+      <c r="CS87" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU87" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -16414,6 +14836,11 @@
       <c r="D88" s="3" t="inlineStr">
         <is>
           <t>1000003</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R88" s="4" t="n"/>
@@ -16479,8 +14906,6 @@
       <c r="BT88" s="4" t="n"/>
       <c r="BU88" s="4" t="n"/>
       <c r="BV88" s="2" t="inlineStr"/>
-      <c r="BW88" s="2" t="n"/>
-      <c r="BX88" s="2" t="n"/>
       <c r="BY88" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -16503,6 +14928,16 @@
           <t>010</t>
         </is>
       </c>
+      <c r="CS88" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU88" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -16518,6 +14953,11 @@
       <c r="D89" s="3" t="inlineStr">
         <is>
           <t>1000004</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R89" s="4" t="n"/>
@@ -16579,8 +15019,6 @@
       <c r="BT89" s="4" t="n"/>
       <c r="BU89" s="4" t="n"/>
       <c r="BV89" s="2" t="inlineStr"/>
-      <c r="BW89" s="2" t="n"/>
-      <c r="BX89" s="2" t="n"/>
       <c r="BY89" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -16603,6 +15041,16 @@
           <t>010</t>
         </is>
       </c>
+      <c r="CS89" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU89" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -16618,6 +15066,11 @@
       <c r="D90" s="3" t="inlineStr">
         <is>
           <t>1000005</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R90" s="4" t="n"/>
@@ -16683,8 +15136,6 @@
       <c r="BT90" s="4" t="n"/>
       <c r="BU90" s="4" t="n"/>
       <c r="BV90" s="2" t="inlineStr"/>
-      <c r="BW90" s="2" t="n"/>
-      <c r="BX90" s="2" t="n"/>
       <c r="BY90" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -16707,6 +15158,16 @@
           <t>010</t>
         </is>
       </c>
+      <c r="CS90" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU90" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -16722,6 +15183,11 @@
       <c r="D91" s="3" t="inlineStr">
         <is>
           <t>1000006</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R91" s="4" t="n"/>
@@ -16787,8 +15253,6 @@
       <c r="BT91" s="4" t="n"/>
       <c r="BU91" s="4" t="n"/>
       <c r="BV91" s="2" t="inlineStr"/>
-      <c r="BW91" s="2" t="n"/>
-      <c r="BX91" s="2" t="n"/>
       <c r="BY91" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -16811,6 +15275,16 @@
           <t>011</t>
         </is>
       </c>
+      <c r="CS91" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU91" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -16826,6 +15300,11 @@
       <c r="D92" s="3" t="inlineStr">
         <is>
           <t>1000007</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R92" s="4" t="n"/>
@@ -16891,8 +15370,6 @@
       <c r="BT92" s="4" t="n"/>
       <c r="BU92" s="4" t="n"/>
       <c r="BV92" s="2" t="inlineStr"/>
-      <c r="BW92" s="2" t="n"/>
-      <c r="BX92" s="2" t="n"/>
       <c r="BY92" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -16915,6 +15392,16 @@
           <t>010</t>
         </is>
       </c>
+      <c r="CS92" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU92" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -16930,6 +15417,11 @@
       <c r="D93" s="3" t="inlineStr">
         <is>
           <t>1000008</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R93" s="4" t="n"/>
@@ -16991,8 +15483,6 @@
       <c r="BT93" s="4" t="n"/>
       <c r="BU93" s="4" t="n"/>
       <c r="BV93" s="2" t="inlineStr"/>
-      <c r="BW93" s="2" t="n"/>
-      <c r="BX93" s="2" t="n"/>
       <c r="BY93" s="2" t="inlineStr"/>
       <c r="BZ93" s="4" t="n"/>
       <c r="CA93" s="4" t="n"/>
@@ -17011,6 +15501,16 @@
           <t>001</t>
         </is>
       </c>
+      <c r="CS93" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU93" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -17026,6 +15526,11 @@
       <c r="D94" s="3" t="inlineStr">
         <is>
           <t>1000009</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R94" s="4" t="n"/>
@@ -17087,8 +15592,6 @@
       <c r="BT94" s="4" t="n"/>
       <c r="BU94" s="4" t="n"/>
       <c r="BV94" s="2" t="inlineStr"/>
-      <c r="BW94" s="2" t="n"/>
-      <c r="BX94" s="2" t="n"/>
       <c r="BY94" s="2" t="inlineStr"/>
       <c r="BZ94" s="4" t="n"/>
       <c r="CA94" s="4" t="n"/>
@@ -17107,6 +15610,16 @@
           <t>001</t>
         </is>
       </c>
+      <c r="CS94" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU94" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -17122,6 +15635,11 @@
       <c r="D95" s="3" t="inlineStr">
         <is>
           <t>1000010</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R95" s="4" t="n"/>
@@ -17183,8 +15701,6 @@
       <c r="BT95" s="4" t="n"/>
       <c r="BU95" s="4" t="n"/>
       <c r="BV95" s="2" t="inlineStr"/>
-      <c r="BW95" s="2" t="n"/>
-      <c r="BX95" s="2" t="n"/>
       <c r="BY95" s="2" t="inlineStr"/>
       <c r="BZ95" s="4" t="n"/>
       <c r="CA95" s="4" t="n"/>
@@ -17203,6 +15719,16 @@
           <t>000</t>
         </is>
       </c>
+      <c r="CS95" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU95" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -17218,6 +15744,11 @@
       <c r="D96" s="3" t="inlineStr">
         <is>
           <t>1000011</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R96" s="4" t="n"/>
@@ -17279,8 +15810,6 @@
       <c r="BT96" s="4" t="n"/>
       <c r="BU96" s="4" t="n"/>
       <c r="BV96" s="2" t="inlineStr"/>
-      <c r="BW96" s="2" t="n"/>
-      <c r="BX96" s="2" t="n"/>
       <c r="BY96" s="2" t="inlineStr"/>
       <c r="BZ96" s="4" t="n"/>
       <c r="CA96" s="4" t="n"/>
@@ -17299,6 +15828,16 @@
           <t>000</t>
         </is>
       </c>
+      <c r="CS96" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU96" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -17314,6 +15853,11 @@
       <c r="D97" s="3" t="inlineStr">
         <is>
           <t>1000012</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R97" s="4" t="n"/>
@@ -17375,8 +15919,6 @@
       <c r="BT97" s="4" t="n"/>
       <c r="BU97" s="4" t="n"/>
       <c r="BV97" s="2" t="inlineStr"/>
-      <c r="BW97" s="2" t="n"/>
-      <c r="BX97" s="2" t="n"/>
       <c r="BY97" s="2" t="inlineStr"/>
       <c r="BZ97" s="4" t="n"/>
       <c r="CA97" s="4" t="n"/>
@@ -17395,6 +15937,16 @@
           <t>011</t>
         </is>
       </c>
+      <c r="CS97" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU97" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -17410,6 +15962,11 @@
       <c r="D98" s="3" t="inlineStr">
         <is>
           <t>1000013</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R98" s="4" t="n"/>
@@ -17467,8 +16024,6 @@
       <c r="BT98" s="4" t="n"/>
       <c r="BU98" s="4" t="n"/>
       <c r="BV98" s="2" t="inlineStr"/>
-      <c r="BW98" s="2" t="n"/>
-      <c r="BX98" s="2" t="n"/>
       <c r="BY98" s="2" t="inlineStr"/>
       <c r="BZ98" s="4" t="n"/>
       <c r="CA98" s="4" t="n"/>
@@ -17483,6 +16038,16 @@
       <c r="CJ98" s="4" t="n"/>
       <c r="CK98" s="2" t="inlineStr"/>
       <c r="CN98" s="2" t="inlineStr"/>
+      <c r="CS98" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU98" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -17498,6 +16063,11 @@
       <c r="D99" s="3" t="inlineStr">
         <is>
           <t>1000014</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R99" s="4" t="n"/>
@@ -17555,8 +16125,6 @@
       <c r="BT99" s="4" t="n"/>
       <c r="BU99" s="4" t="n"/>
       <c r="BV99" s="2" t="inlineStr"/>
-      <c r="BW99" s="2" t="n"/>
-      <c r="BX99" s="2" t="n"/>
       <c r="BY99" s="2" t="inlineStr"/>
       <c r="BZ99" s="4" t="n"/>
       <c r="CA99" s="4" t="n"/>
@@ -17571,6 +16139,16 @@
       <c r="CJ99" s="4" t="n"/>
       <c r="CK99" s="2" t="inlineStr"/>
       <c r="CN99" s="2" t="inlineStr"/>
+      <c r="CS99" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU99" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -17586,6 +16164,11 @@
       <c r="D100" t="inlineStr">
         <is>
           <t>1000015</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LLM</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -17602,6 +16185,16 @@
       <c r="BY100" t="inlineStr"/>
       <c r="CK100" t="inlineStr"/>
       <c r="CN100" t="inlineStr"/>
+      <c r="CS100" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="CU100" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K84">
@@ -17639,14 +16232,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M84">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -17657,9 +16242,7 @@
         <color rgb="FF5A8AC6"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P84">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -17667,6 +16250,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P84">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -17675,6 +16260,14 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -17822,21 +16415,21 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AD85">
+  <conditionalFormatting sqref="BW2 CL2">
     <cfRule type="expression" priority="21" dxfId="4">
-      <formula>AE2="Pass"</formula>
+      <formula>BX2="Pass"</formula>
     </cfRule>
     <cfRule type="expression" priority="22" dxfId="3">
-      <formula>AE2="Pass'"</formula>
+      <formula>BX2="Pass'"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" dxfId="2">
-      <formula>AE2="Pass*"</formula>
+      <formula>BX2="Pass*"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="0">
-      <formula>AE2="Fail"</formula>
+    <cfRule type="expression" priority="24" dxfId="1">
+      <formula>BX2="Fail"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" dxfId="1">
-      <formula>AE2="Fail*"</formula>
+    <cfRule type="expression" priority="25" dxfId="0">
+      <formula>BX2="Fail*"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG99">
@@ -17961,23 +16554,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS85">
-    <cfRule type="expression" priority="20" dxfId="1">
-      <formula>AT2="Fail*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="19" dxfId="0">
-      <formula>AT2="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="2">
-      <formula>AT2="Pass*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="17" dxfId="3">
-      <formula>AT2="Pass'"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="4">
-      <formula>AT2="Pass"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV99">
     <cfRule type="colorScale" priority="75">
       <colorScale>
@@ -18098,23 +16674,6 @@
         <color rgb="FFFCFFFF"/>
         <color rgb="FF5A8CC6"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH85">
-    <cfRule type="expression" priority="14" dxfId="0">
-      <formula>BI2="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="1">
-      <formula>BI2="Fail*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="2">
-      <formula>BI2="Pass*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="4">
-      <formula>BI2="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="3">
-      <formula>BI2="Pass'"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BK2:BK99">
@@ -18239,23 +16798,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW99">
-    <cfRule type="expression" priority="8" dxfId="2">
-      <formula>BX2="Pass*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="3">
-      <formula>BX2="Pass'"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="4">
-      <formula>BX2="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="1">
-      <formula>BX2="Fail*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="0">
-      <formula>BX2="Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BZ2:BZ99">
     <cfRule type="colorScale" priority="107">
       <colorScale>
@@ -18378,23 +16920,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL85">
-    <cfRule type="expression" priority="1" dxfId="4">
-      <formula>CM2="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>CM2="Pass'"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>CM2="Pass*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>CM2="Fail*"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>CM2="Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="CP2:CP85">
     <cfRule type="colorScale" priority="39">
       <colorScale>
@@ -18428,14 +16953,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CR2:CR84">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -18444,6 +16961,14 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -18660,10 +17185,10 @@
         <v>66.66</v>
       </c>
       <c r="C2" t="n">
-        <v>15.77</v>
+        <v>15.74</v>
       </c>
       <c r="D2" t="n">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E2" t="n">
         <v>702</v>
@@ -18672,7 +17197,7 @@
         <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
         <v>26</v>
@@ -18690,13 +17215,13 @@
         <v>7.83</v>
       </c>
       <c r="M2" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="N2" t="n">
         <v>12.5</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
         <v>26</v>
@@ -18745,7 +17270,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>t:46.57:13;p:50.44:0;t:40.26:19;p:33.49:0;t:8.89:12;p:324.75:0;t:3.00:11;p:628.48:0;t:17.23:7;p:62.80:0;t:6.54:9;p:59.23:0;t:5.10:4;p:73.54:0;t:41.37:10;p:25.74:0;t:106.09:15;p:69.39:0;t:67.04:17;p:37.07:0;t:23.96:1;p:76.59:0;t:36.25:8;p:69.75:0;t:15.63:6;p:38.73:0;t:38.75:3;p:22.14:0;t:103.16:18;p:221.93:0;t:9.14:21;p:132.79:0;t:45.63:16;p:30.25:0;t:13.33:1;p:70.35:0;t:96.37:38;p:167.35:0;t:6.32:3;p:39.72:0;t:40.24:21;p:72.21:0;t:11.94:13;p:47.54:0;t:4.94:1;p:89.78:0;t:102.90:35;p:410.29:0;t:0.75:0;p:152.28:0;t:10.14:16;p:46.76:0;t:44.58:5</t>
+          <t>t:46.57:13;p:50.44:0;t:40.26:19;p:33.49:0;t:8.89:12;p:324.75:0;t:3.00:11;p:628.48:0;t:17.23:7;p:62.80:0;t:6.54:9;p:59.23:0;t:5.10:4;p:73.54:0;t:41.37:10;p:25.74:0;t:106.09:15;p:69.39:0;t:67.04:17;p:37.07:0;t:23.96:1;p:76.59:0;t:36.25:8;p:69.75:0;t:15.63:6;p:38.73:0;t:38.75:3;p:22.14:0;t:103.16:18;p:221.93:0;t:9.14:21;p:132.79:0;t:45.63:16;p:30.25:0;t:13.33:1;p:70.35:0;t:96.37:38;p:167.35:0;t:6.32:3;p:39.72:0;t:40.24:21;p:72.21:0;t:11.94:13;p:47.54:0;t:4.94:1;p:89.78:0;t:89.82:32;p:42.41:0;t:11.54:3;p:369.42:0;t:0.75:0;p:152.28:0;t:10.14:16;p:46.76:0;t:44.58:5</t>
         </is>
       </c>
     </row>

--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -2981,7 +2981,7 @@
       <c r="AR14" s="2" t="inlineStr"/>
       <c r="AU14" s="2" t="inlineStr">
         <is>
-          <t>000001</t>
+          <t>001001</t>
         </is>
       </c>
       <c r="AV14" s="4" t="n"/>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="CN25" s="2" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="CO25" s="10" t="n">
@@ -7026,7 +7026,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AF42" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="AG42" s="4" t="n"/>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AU59" s="2" t="inlineStr">
         <is>
-          <t>000000</t>
+          <t>000100</t>
         </is>
       </c>
       <c r="AV59" s="4" t="n">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="AF68" s="2" t="inlineStr">
         <is>
-          <t>00111</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="AG68" s="4" t="n">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="BJ72" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="BK72" s="4" t="n">
@@ -15121,7 +15121,7 @@
       <c r="BG90" s="2" t="inlineStr"/>
       <c r="BJ90" s="2" t="inlineStr">
         <is>
-          <t>01100</t>
+          <t>01101</t>
         </is>
       </c>
       <c r="BK90" s="4" t="n"/>
@@ -15155,7 +15155,7 @@
       <c r="CK90" s="2" t="inlineStr"/>
       <c r="CN90" s="2" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="CS90" t="inlineStr">
@@ -15451,7 +15451,7 @@
       <c r="AR93" s="2" t="inlineStr"/>
       <c r="AU93" s="2" t="inlineStr">
         <is>
-          <t>010011</t>
+          <t>011011</t>
         </is>
       </c>
       <c r="AV93" s="4" t="n"/>
@@ -15560,7 +15560,7 @@
       <c r="AR94" s="2" t="inlineStr"/>
       <c r="AU94" s="2" t="inlineStr">
         <is>
-          <t>010011</t>
+          <t>011011</t>
         </is>
       </c>
       <c r="AV94" s="4" t="n"/>
@@ -15795,7 +15795,7 @@
       <c r="BG96" s="2" t="inlineStr"/>
       <c r="BJ96" s="2" t="inlineStr">
         <is>
-          <t>00110</t>
+          <t>00111</t>
         </is>
       </c>
       <c r="BK96" s="4" t="n"/>

--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -1419,14 +1419,14 @@
         <v>1.5</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>60.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n">
-        <v>92.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V4" s="4" t="n">
         <v>94.90000000000001</v>
@@ -1441,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>38</v>
+        <v>-73</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1683,14 +1683,14 @@
         <v>2</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0</v>
+        <v>99.3</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>2.6</v>
+        <v>100</v>
       </c>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n">
-        <v>0</v>
+        <v>99.3</v>
       </c>
       <c r="V5" s="4" t="n">
         <v>17.8</v>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>-62</v>
+        <v>-53</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>C2&gt;</t>
+          <t>C1&gt;</t>
         </is>
       </c>
       <c r="AU5" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>C1&gt;</t>
+          <t>_</t>
         </is>
       </c>
       <c r="AU12" s="2" t="inlineStr">
@@ -3516,14 +3516,14 @@
         <v>2</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>18.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n">
-        <v>16.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>21.4</v>
@@ -3538,13 +3538,13 @@
         <v>0</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>-14</v>
+        <v>-54</v>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
@@ -3881,14 +3881,14 @@
         <v>2</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>69.2</v>
+        <v>98.7</v>
       </c>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n">
-        <v>79.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>98</v>
@@ -3903,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>-46</v>
+        <v>-68</v>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
       </c>
       <c r="BL21" s="4" t="n"/>
       <c r="BM21" s="4" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="BN21" s="4" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="BO21" s="4" t="n">
         <v>92.8</v>
@@ -4342,14 +4342,14 @@
         <v>3</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>98.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n">
-        <v>96.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>97.90000000000001</v>
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
@@ -4606,14 +4606,14 @@
         <v>2.5</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V25" s="4" t="n">
         <v>83.09999999999999</v>
@@ -4631,10 +4631,10 @@
         <v>6</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>-36</v>
+        <v>-73</v>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
       </c>
       <c r="BL25" s="4" t="n"/>
       <c r="BM25" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="BN25" s="4" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="BO25" s="4" t="n">
         <v>94.8</v>
@@ -5516,14 +5516,14 @@
         <v>2</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0</v>
+        <v>99.8</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n">
-        <v>1.7</v>
+        <v>99.8</v>
       </c>
       <c r="V31" s="4" t="n">
         <v>9.1</v>
@@ -5538,13 +5538,13 @@
         <v>0</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>-50</v>
+        <v>180</v>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AR36" s="2" t="inlineStr">
         <is>
-          <t>C3&lt;</t>
+          <t>C2&lt;</t>
         </is>
       </c>
       <c r="AU36" s="2" t="inlineStr">
@@ -6821,16 +6821,10 @@
       <c r="Q41" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R41" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S41" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="R41" s="4" t="n"/>
+      <c r="S41" s="4" t="n"/>
       <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="U41" s="4" t="n"/>
       <c r="V41" s="4" t="n">
         <v>4.5</v>
       </c>
@@ -7094,10 +7088,10 @@
       </c>
       <c r="BL42" s="4" t="n"/>
       <c r="BM42" s="4" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="BN42" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="BO42" s="4" t="n">
         <v>97.8</v>
@@ -7718,7 +7712,7 @@
       </c>
       <c r="AR46" s="2" t="inlineStr">
         <is>
-          <t>C2&lt;</t>
+          <t>C1&lt;</t>
         </is>
       </c>
       <c r="AU46" s="2" t="inlineStr">
@@ -8032,7 +8026,7 @@
         </is>
       </c>
       <c r="AG48" s="4" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AH48" s="4" t="n">
         <v>85.7</v>
@@ -8041,7 +8035,7 @@
         <v>95.3</v>
       </c>
       <c r="AJ48" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AK48" s="4" t="n">
         <v>97.09999999999999</v>
@@ -8162,13 +8156,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="CA48" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="CB48" s="4" t="n">
         <v>97.3</v>
       </c>
       <c r="CC48" s="4" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="CD48" s="4" t="n">
         <v>65.59999999999999</v>
@@ -8583,14 +8577,14 @@
         <v>2.5</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="V51" s="4" t="n">
         <v>97.90000000000001</v>
@@ -8605,13 +8599,13 @@
         <v>0</v>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
@@ -9262,14 +9256,14 @@
         <v>1</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>91.8</v>
+        <v>99</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>98.5</v>
@@ -9284,13 +9278,13 @@
         <v>0</v>
       </c>
       <c r="Z56" s="4" t="n">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
@@ -10846,7 +10840,7 @@
       </c>
       <c r="AR66" s="2" t="inlineStr">
         <is>
-          <t>C2&lt;</t>
+          <t>C1&lt;</t>
         </is>
       </c>
       <c r="AU66" s="2" t="inlineStr">
@@ -11110,14 +11104,14 @@
         <v>1</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>4.4</v>
+        <v>97</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
-        <v>3.1</v>
+        <v>97</v>
       </c>
       <c r="V68" s="4" t="n">
         <v>6.4</v>
@@ -11132,13 +11126,13 @@
         <v>0</v>
       </c>
       <c r="Z68" s="4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>-84</v>
+        <v>17</v>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
@@ -11237,14 +11231,14 @@
         </is>
       </c>
       <c r="BK68" s="4" t="n">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="BL68" s="4" t="n"/>
       <c r="BM68" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BN68" s="4" t="n">
-        <v>89.2</v>
+        <v>89.7</v>
       </c>
       <c r="BO68" s="4" t="n">
         <v>90.90000000000001</v>
@@ -11512,7 +11506,7 @@
       </c>
       <c r="AR70" s="2" t="inlineStr">
         <is>
-          <t>C3&gt;</t>
+          <t>C2&gt;</t>
         </is>
       </c>
       <c r="AU70" s="2" t="inlineStr">
@@ -11701,14 +11695,14 @@
         <v>1</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>58.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n">
-        <v>57.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V71" s="4" t="n">
         <v>60.1</v>
@@ -11723,13 +11717,13 @@
         <v>0</v>
       </c>
       <c r="Z71" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
@@ -12191,14 +12185,14 @@
         <v>1</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>16.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n">
-        <v>15.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V73" s="4" t="n">
         <v>26.4</v>
@@ -12213,13 +12207,13 @@
         <v>0</v>
       </c>
       <c r="Z73" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA73" s="4" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>-57</v>
+        <v>-54</v>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
@@ -12558,14 +12552,14 @@
         <v>1</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>12.2</v>
+        <v>94.8</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>55.1</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n">
-        <v>15.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V75" s="4" t="n">
         <v>18.4</v>
@@ -12580,13 +12574,13 @@
         <v>0</v>
       </c>
       <c r="Z75" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>-84</v>
+        <v>-54</v>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
@@ -12633,7 +12627,7 @@
       </c>
       <c r="AR75" s="2" t="inlineStr">
         <is>
-          <t>C2&lt;</t>
+          <t>C1&lt;</t>
         </is>
       </c>
       <c r="AU75" s="2" t="inlineStr">
@@ -12689,10 +12683,10 @@
       </c>
       <c r="BL75" s="4" t="n"/>
       <c r="BM75" s="4" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="BN75" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="BO75" s="4" t="n">
         <v>89.8</v>
@@ -12999,14 +12993,14 @@
         <v>1</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>48.6</v>
+        <v>99.8</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>44.9</v>
+        <v>100</v>
       </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n">
-        <v>48.3</v>
+        <v>99.8</v>
       </c>
       <c r="V78" s="4" t="n">
         <v>54.7</v>
@@ -13021,13 +13015,13 @@
         <v>0</v>
       </c>
       <c r="Z78" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AA78" s="4" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>-40</v>
+        <v>-54</v>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
@@ -13263,14 +13257,14 @@
         <v>1</v>
       </c>
       <c r="R79" s="4" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="S79" s="4" t="n">
         <v>100</v>
-      </c>
-      <c r="S79" s="4" t="n">
-        <v>91</v>
       </c>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n">
-        <v>99.3</v>
+        <v>99.7</v>
       </c>
       <c r="V79" s="4" t="n">
         <v>99.90000000000001</v>
@@ -13285,13 +13279,13 @@
         <v>0</v>
       </c>
       <c r="Z79" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AA79" s="4" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
@@ -13630,14 +13624,14 @@
         <v>3</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="T81" s="4" t="n"/>
       <c r="U81" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="V81" s="4" t="n">
         <v>97.40000000000001</v>
@@ -13652,13 +13646,13 @@
         <v>0</v>
       </c>
       <c r="Z81" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>20</v>
+        <v>-56</v>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
@@ -13894,14 +13888,14 @@
         <v>4</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="S82" s="4" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="V82" s="4" t="n">
         <v>97.7</v>
@@ -13916,13 +13910,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>-20</v>
+        <v>-46</v>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
@@ -14156,14 +14150,14 @@
         <v>1</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="S83" s="4" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n">
-        <v>85.2</v>
+        <v>99.3</v>
       </c>
       <c r="V83" s="4" t="n">
         <v>97.7</v>
@@ -14178,13 +14172,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>2</v>
+        <v>-52</v>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>

--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -1419,14 +1419,14 @@
         <v>1.5</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>92.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>82.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="V4" s="4" t="n">
         <v>94.90000000000001</v>
@@ -1441,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>-73</v>
+        <v>38</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1683,14 +1683,14 @@
         <v>2</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>99.3</v>
+        <v>16.1</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n">
-        <v>99.3</v>
+        <v>15</v>
       </c>
       <c r="V5" s="4" t="n">
         <v>17.8</v>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>-53</v>
+        <v>-62</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -3516,14 +3516,14 @@
         <v>2</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>21.4</v>
@@ -3538,13 +3538,13 @@
         <v>0</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>-54</v>
+        <v>-14</v>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
@@ -3881,14 +3881,14 @@
         <v>2</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>99.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>98.7</v>
+        <v>69.2</v>
       </c>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>98</v>
@@ -3903,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>-68</v>
+        <v>-46</v>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
@@ -4342,14 +4342,14 @@
         <v>3</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>97.90000000000001</v>
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
@@ -4606,14 +4606,14 @@
         <v>2.5</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>96.2</v>
+        <v>66.7</v>
       </c>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="V25" s="4" t="n">
         <v>83.09999999999999</v>
@@ -4631,10 +4631,10 @@
         <v>6</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>-73</v>
+        <v>-36</v>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
@@ -5516,14 +5516,14 @@
         <v>2</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>100</v>
+        <v>46.2</v>
       </c>
       <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n">
-        <v>99.8</v>
+        <v>1.7</v>
       </c>
       <c r="V31" s="4" t="n">
         <v>9.1</v>
@@ -5538,13 +5538,13 @@
         <v>0</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>223</v>
+        <v>2</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>180</v>
+        <v>-50</v>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
@@ -6821,10 +6821,16 @@
       <c r="Q41" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R41" s="4" t="n"/>
-      <c r="S41" s="4" t="n"/>
+      <c r="R41" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="n"/>
+      <c r="U41" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="V41" s="4" t="n">
         <v>4.5</v>
       </c>
@@ -8577,14 +8583,14 @@
         <v>2.5</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="V51" s="4" t="n">
         <v>97.90000000000001</v>
@@ -8599,13 +8605,13 @@
         <v>0</v>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
@@ -9256,14 +9262,14 @@
         <v>1</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>99</v>
+        <v>91.8</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>100</v>
+        <v>79.5</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>98.5</v>
@@ -9278,13 +9284,13 @@
         <v>0</v>
       </c>
       <c r="Z56" s="4" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
@@ -11104,14 +11110,14 @@
         <v>1</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>97</v>
+        <v>4.4</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
-        <v>97</v>
+        <v>3.1</v>
       </c>
       <c r="V68" s="4" t="n">
         <v>6.4</v>
@@ -11126,13 +11132,13 @@
         <v>0</v>
       </c>
       <c r="Z68" s="4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>17</v>
+        <v>-84</v>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
@@ -11695,14 +11701,14 @@
         <v>1</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>100</v>
+        <v>46.2</v>
       </c>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="V71" s="4" t="n">
         <v>60.1</v>
@@ -11717,13 +11723,13 @@
         <v>0</v>
       </c>
       <c r="Z71" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
@@ -12185,14 +12191,14 @@
         <v>1</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="V73" s="4" t="n">
         <v>26.4</v>
@@ -12207,13 +12213,13 @@
         <v>0</v>
       </c>
       <c r="Z73" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="4" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>-54</v>
+        <v>-57</v>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
@@ -12552,14 +12558,14 @@
         <v>1</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>94.8</v>
+        <v>12.2</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="V75" s="4" t="n">
         <v>18.4</v>
@@ -12574,13 +12580,13 @@
         <v>0</v>
       </c>
       <c r="Z75" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>-54</v>
+        <v>-84</v>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
@@ -12993,14 +12999,14 @@
         <v>1</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>99.8</v>
+        <v>48.6</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>100</v>
+        <v>44.9</v>
       </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n">
-        <v>99.8</v>
+        <v>48.3</v>
       </c>
       <c r="V78" s="4" t="n">
         <v>54.7</v>
@@ -13015,13 +13021,13 @@
         <v>0</v>
       </c>
       <c r="Z78" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AA78" s="4" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>-54</v>
+        <v>-40</v>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
@@ -13257,14 +13263,14 @@
         <v>1</v>
       </c>
       <c r="R79" s="4" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="S79" s="4" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="V79" s="4" t="n">
         <v>99.90000000000001</v>
@@ -13279,13 +13285,13 @@
         <v>0</v>
       </c>
       <c r="Z79" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AA79" s="4" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
@@ -13624,14 +13630,14 @@
         <v>3</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>99.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="T81" s="4" t="n"/>
       <c r="U81" s="4" t="n">
-        <v>99.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V81" s="4" t="n">
         <v>97.40000000000001</v>
@@ -13646,13 +13652,13 @@
         <v>0</v>
       </c>
       <c r="Z81" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>-56</v>
+        <v>20</v>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
@@ -13888,14 +13894,14 @@
         <v>4</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S82" s="4" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V82" s="4" t="n">
         <v>97.7</v>
@@ -13910,13 +13916,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>-46</v>
+        <v>-20</v>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
@@ -14150,14 +14156,14 @@
         <v>1</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>99.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="S83" s="4" t="n">
-        <v>100</v>
+        <v>57.7</v>
       </c>
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n">
-        <v>99.3</v>
+        <v>85.2</v>
       </c>
       <c r="V83" s="4" t="n">
         <v>97.7</v>
@@ -14172,13 +14178,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="4" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>-52</v>
+        <v>2</v>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>

--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="AG48" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AH48" s="4" t="n">
         <v>85.7</v>
@@ -8041,7 +8041,7 @@
         <v>95.3</v>
       </c>
       <c r="AJ48" s="4" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AK48" s="4" t="n">
         <v>97.09999999999999</v>
@@ -11241,10 +11241,10 @@
       </c>
       <c r="BL68" s="4" t="n"/>
       <c r="BM68" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BN68" s="4" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
       <c r="BO68" s="4" t="n">
         <v>90.90000000000001</v>
